--- a/static/excel_files/ST_WEB.xlsx
+++ b/static/excel_files/ST_WEB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jesusalberca/Desktop/qc_matrix_generator/static/excel_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabinol\Documents\matrices\excel_files\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007A1294-88B1-C541-BF62-AE5FFC646403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8CAF91-242B-4CA9-AFFF-CFCB7C17E0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28200" yWindow="660" windowWidth="22840" windowHeight="20780" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WEB" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="93">
   <si>
     <t>caso de prueba</t>
   </si>
@@ -45,232 +45,34 @@
     <t>Acceso</t>
   </si>
   <si>
-    <t>Anónimo|Cerrar sesión</t>
-  </si>
-  <si>
     <t>Por ejecutar</t>
   </si>
   <si>
     <t>Bloqueante</t>
   </si>
   <si>
-    <t>Suscrito|Hace registro de credenciales flujo Telmex</t>
-  </si>
-  <si>
-    <t>Suscrito|Ingreso a la aplicación Usuario y Contraseña (validos)</t>
-  </si>
-  <si>
-    <t>Suscrito|Porbar autologin IP TELMEX</t>
-  </si>
-  <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>Suscrito|Probar login con credenciales TELMEX</t>
-  </si>
-  <si>
-    <t>Suscrito|Registro</t>
   </si>
   <si>
     <t>Cancelación</t>
   </si>
   <si>
-    <t>Suscrito|Cancelación de todas las susripciones hechas</t>
-  </si>
-  <si>
     <t>Claro Música</t>
-  </si>
-  <si>
-    <t>Registrado|Reproducir Claro Musica con usuario sin susc</t>
   </si>
   <si>
     <t>Navegación</t>
   </si>
   <si>
-    <t>Registrado|Validar 1 vcard por Addon y validar landing y botones</t>
-  </si>
-  <si>
-    <t>Registrado|Validar la correcta visualización del HOME de todos los Addons</t>
-  </si>
-  <si>
-    <t>Registrado|Validar que todas las ofertas del carrusel premium tengan accionable</t>
-  </si>
-  <si>
-    <t>Registrado|Validar que todos los nodos/ subnodos tengan accionable</t>
-  </si>
-  <si>
-    <t>Suscrito|Dentro de Nodo Mis contenidos validar el funcionamiento de Carrusel Continua Viendo</t>
-  </si>
-  <si>
-    <t>Suscrito|Dentro de Nodo Mis contenidos validar el funcionamiento de Carrusel Mi lista</t>
-  </si>
-  <si>
-    <t>Suscrito|Dentro de Nodo Mis contenidos validar el funcionamiento de Carrusel Mis compras y Rentas</t>
-  </si>
-  <si>
-    <t>Suscrito|Plan selector; validar landing de todas las ofertas</t>
-  </si>
-  <si>
-    <t>Suscrito|Plan selector; validar que todos los botones interactuen correctamente</t>
-  </si>
-  <si>
-    <t>Suscrito|Validar que en EPG no haya canales con programacion NA</t>
-  </si>
-  <si>
-    <t>Suscrito|Validar que las categorias filtren y tengan canales</t>
-  </si>
-  <si>
-    <t>Suscrito|Validar que se vean todos los logos en EPG</t>
-  </si>
-  <si>
-    <t>Suscrito|Validar que se vean todos los logos en Mosaico</t>
-  </si>
-  <si>
     <t>Perfiles</t>
-  </si>
-  <si>
-    <t>Suscrito|Cambiar el Nombre e imagen de cada perfil creado</t>
-  </si>
-  <si>
-    <t>Suscrito|Completar Datos del administrador (Nombre e Imagen)</t>
-  </si>
-  <si>
-    <t>Suscrito|Crear hasta el número máximo de Perfiles (5 por el momento)</t>
-  </si>
-  <si>
-    <t>Suscrito|Eliminar Perfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suscrito|Reproducir Segundo Perfil AddOn </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suscrito|Reproducir Segundo Perfil Canal Lineal suscrito </t>
   </si>
   <si>
     <t>Rep. Canal Líneal</t>
   </si>
   <si>
-    <t xml:space="preserve">Suscrito| Validar reproduccion de canales lineales </t>
-  </si>
-  <si>
-    <t>Suscrito|Validar player de lineales basico, pausa, volumen, ampliar, opciones</t>
-  </si>
-  <si>
-    <t>Suscrito|Validar player de lineales cambio de idioma</t>
-  </si>
-  <si>
-    <t>Suscrito|Validar player de lineales opciones Bloquear canal y Desbloquear canal</t>
-  </si>
-  <si>
-    <t>Suscrito|Validar player de lineales opciones favorito y quitar favorito</t>
-  </si>
-  <si>
     <t>Reproducción</t>
   </si>
   <si>
-    <t>Anónimo|Reproducir contenido VOD y Lineal Free</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suscrito|Dentro de Player de Addon validar audios y subtitulos </t>
-  </si>
-  <si>
-    <t>Suscrito|Dentro de Player de Addon validar boton Agregar a mi Lista</t>
-  </si>
-  <si>
-    <t>Suscrito|Dentro de Player de Addon validar boton Temporadas</t>
-  </si>
-  <si>
-    <t>Suscrito|Dentro de Player de un Addon validar player basico (Adelantar, Atrasar,mover la barra de repro ,pausar, volumen, ampliar. PIP)</t>
-  </si>
-  <si>
-    <t>Suscrito|Reproduce inmediatamente después de la Compra</t>
-  </si>
-  <si>
-    <t>Suscrito|Reproduce inmediatamente después de la Renta</t>
-  </si>
-  <si>
-    <t>Suscrito|Reproducir VOD de ATRESplayer Serie y Pelicula</t>
-  </si>
-  <si>
-    <t>Suscrito|Reproducir VOD de EDYE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suscrito|Reproducir VOD de FOX SPORTS </t>
-  </si>
-  <si>
-    <t>Suscrito|Reproducir VOD de HBO Serie y Pelicula</t>
-  </si>
-  <si>
-    <t>Suscrito|Reproducir VOD de MGM Serie y Pelicula</t>
-  </si>
-  <si>
-    <t>Suscrito|Reproducir VOD de PARAMOUNT  Serie y Pelicula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suscrito|Reproducir VOD de PICARDIA NACIONAL </t>
-  </si>
-  <si>
-    <t>Suscrito|Reproducir VOD de RTVEplay Serie y Pelicula</t>
-  </si>
-  <si>
-    <t>Suscrito|Reproducir VOD de SONY ONE Serie y Pelicula</t>
-  </si>
-  <si>
-    <t>Suscrito|Reproducir VOD de UNIVERSAL Serie y Pelicula</t>
-  </si>
-  <si>
-    <t>Suscrito|Reproducir VOD FOX ONE</t>
-  </si>
-  <si>
-    <t>Suscrito|Reproducir VOD QELLO CONCERTS</t>
-  </si>
-  <si>
-    <t>Suscrito|Reproducir VOD STINGRAY KARAOKE</t>
-  </si>
-  <si>
     <t>Transacción</t>
-  </si>
-  <si>
-    <t>Suscrito|Compra con Fija</t>
-  </si>
-  <si>
-    <t>Suscrito|Renta con Movil</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripción AMCO Claro video desde formulario lineales epg</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripcion AMCO FOX ONE desde Vcard</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripcion AMCO RTVEPLAY desde plan selector</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripción TDC Edye desde landing vcard</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripción TDC UNIVERSAL desde Formulario desde carrusel addon</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripción Telcel ATRESplayer desde formulario lineales desde carrusel addon</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripcion Telcel MGM+ desde Mi perfil</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripción Telcel Picardia Nacional desde Vcard</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripcion Telcel SONY ONE desde Plan selector</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripcion Telmex FOX SPORTS desde landing de formulario lineales epg</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripcion Telmex Qello Concerts desde Mi perfil</t>
-  </si>
-  <si>
-    <t>Suscrito|Suscripción Telmex Stingray karaoke desde vcard</t>
   </si>
   <si>
     <t>alcance de evaluación</t>
@@ -295,6 +97,213 @@
   </si>
   <si>
     <t>comentarios y datos de prueba</t>
+  </si>
+  <si>
+    <t>Anonimo</t>
+  </si>
+  <si>
+    <t>Suscrito</t>
+  </si>
+  <si>
+    <t>Registrado</t>
+  </si>
+  <si>
+    <t>Cerrar sesión</t>
+  </si>
+  <si>
+    <t>Hace registro de credenciales flujo Telmex</t>
+  </si>
+  <si>
+    <t>Ingreso a la aplicación Usuario y Contraseña (validos)</t>
+  </si>
+  <si>
+    <t>Porbar autologin IP TELMEX</t>
+  </si>
+  <si>
+    <t>Probar login con credenciales TELMEX</t>
+  </si>
+  <si>
+    <t>Registro</t>
+  </si>
+  <si>
+    <t>Cancelación de todas las susripciones hechas</t>
+  </si>
+  <si>
+    <t>Reproducir Claro Musica con usuario sin susc</t>
+  </si>
+  <si>
+    <t>Validar 1 vcard por Addon y validar landing y botones</t>
+  </si>
+  <si>
+    <t>Validar la correcta visualización del HOME de todos los Addons</t>
+  </si>
+  <si>
+    <t>Validar que todas las ofertas del carrusel premium tengan accionable</t>
+  </si>
+  <si>
+    <t>Validar que todos los nodos/ subnodos tengan accionable</t>
+  </si>
+  <si>
+    <t>Dentro de Nodo Mis contenidos validar el funcionamiento de Carrusel Continua Viendo</t>
+  </si>
+  <si>
+    <t>Dentro de Nodo Mis contenidos validar el funcionamiento de Carrusel Mi lista</t>
+  </si>
+  <si>
+    <t>Dentro de Nodo Mis contenidos validar el funcionamiento de Carrusel Mis compras y Rentas</t>
+  </si>
+  <si>
+    <t>Plan selector; validar landing de todas las ofertas</t>
+  </si>
+  <si>
+    <t>Plan selector; validar que todos los botones interactuen correctamente</t>
+  </si>
+  <si>
+    <t>Validar que en EPG no haya canales con programacion NA</t>
+  </si>
+  <si>
+    <t>Validar que las categorias filtren y tengan canales</t>
+  </si>
+  <si>
+    <t>Validar que se vean todos los logos en EPG</t>
+  </si>
+  <si>
+    <t>Validar que se vean todos los logos en Mosaico</t>
+  </si>
+  <si>
+    <t>Cambiar el Nombre e imagen de cada perfil creado</t>
+  </si>
+  <si>
+    <t>Completar Datos del administrador (Nombre e Imagen)</t>
+  </si>
+  <si>
+    <t>Crear hasta el número máximo de Perfiles (5 por el momento)</t>
+  </si>
+  <si>
+    <t>Eliminar Perfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reproducir Segundo Perfil AddOn </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reproducir Segundo Perfil Canal Lineal suscrito </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validar reproduccion de canales lineales </t>
+  </si>
+  <si>
+    <t>Validar player de lineales basico, pausa, volumen, ampliar, opciones</t>
+  </si>
+  <si>
+    <t>Validar player de lineales cambio de idioma</t>
+  </si>
+  <si>
+    <t>Validar player de lineales opciones Bloquear canal y Desbloquear canal</t>
+  </si>
+  <si>
+    <t>Validar player de lineales opciones favorito y quitar favorito</t>
+  </si>
+  <si>
+    <t>Reproducir contenido VOD y Lineal Free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dentro de Player de Addon validar audios y subtitulos </t>
+  </si>
+  <si>
+    <t>Dentro de Player de Addon validar boton Agregar a mi Lista</t>
+  </si>
+  <si>
+    <t>Dentro de Player de Addon validar boton Temporadas</t>
+  </si>
+  <si>
+    <t>Dentro de Player de un Addon validar player basico (Adelantar, Atrasar,mover la barra de repro ,pausar, volumen, ampliar. PIP)</t>
+  </si>
+  <si>
+    <t>Reproduce inmediatamente después de la Compra</t>
+  </si>
+  <si>
+    <t>Reproduce inmediatamente después de la Renta</t>
+  </si>
+  <si>
+    <t>Reproducir VOD de ATRESplayer Serie y Pelicula</t>
+  </si>
+  <si>
+    <t>Reproducir VOD de EDYE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reproducir VOD de FOX SPORTS </t>
+  </si>
+  <si>
+    <t>Reproducir VOD de HBO Serie y Pelicula</t>
+  </si>
+  <si>
+    <t>Reproducir VOD de MGM Serie y Pelicula</t>
+  </si>
+  <si>
+    <t>Reproducir VOD de PARAMOUNT  Serie y Pelicula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reproducir VOD de PICARDIA NACIONAL </t>
+  </si>
+  <si>
+    <t>Reproducir VOD de RTVEplay Serie y Pelicula</t>
+  </si>
+  <si>
+    <t>Reproducir VOD de SONY ONE Serie y Pelicula</t>
+  </si>
+  <si>
+    <t>Reproducir VOD de UNIVERSAL Serie y Pelicula</t>
+  </si>
+  <si>
+    <t>Reproducir VOD FOX ONE</t>
+  </si>
+  <si>
+    <t>Reproducir VOD QELLO CONCERTS</t>
+  </si>
+  <si>
+    <t>Reproducir VOD STINGRAY KARAOKE</t>
+  </si>
+  <si>
+    <t>Compra con Fija</t>
+  </si>
+  <si>
+    <t>Renta con Movil</t>
+  </si>
+  <si>
+    <t>Suscripción AMCO Claro video desde formulario lineales epg</t>
+  </si>
+  <si>
+    <t>Suscripcion AMCO FOX ONE desde Vcard</t>
+  </si>
+  <si>
+    <t>Suscripcion AMCO RTVEPLAY desde plan selector</t>
+  </si>
+  <si>
+    <t>Suscripción TDC Edye desde landing vcard</t>
+  </si>
+  <si>
+    <t>Suscripción TDC UNIVERSAL desde Formulario desde carrusel addon</t>
+  </si>
+  <si>
+    <t>Suscripción Telcel ATRESplayer desde formulario lineales desde carrusel addon</t>
+  </si>
+  <si>
+    <t>Suscripcion Telcel MGM+ desde Mi perfil</t>
+  </si>
+  <si>
+    <t>Suscripción Telcel Picardia Nacional desde Vcard</t>
+  </si>
+  <si>
+    <t>Suscripcion Telcel SONY ONE desde Plan selector</t>
+  </si>
+  <si>
+    <t>Suscripcion Telmex FOX SPORTS desde landing de formulario lineales epg</t>
+  </si>
+  <si>
+    <t>Suscripcion Telmex Qello Concerts desde Mi perfil</t>
+  </si>
+  <si>
+    <t>Suscripción Telmex Stingray karaoke desde vcard</t>
   </si>
 </sst>
 </file>
@@ -774,15 +783,15 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="19.6640625" customWidth="1"/>
-    <col min="5" max="5" width="92.5" customWidth="1"/>
-    <col min="6" max="7" width="21.6640625" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" customWidth="1"/>
+    <col min="3" max="4" width="19.6328125" customWidth="1"/>
+    <col min="5" max="5" width="92.453125" customWidth="1"/>
+    <col min="6" max="7" width="21.6328125" customWidth="1"/>
+    <col min="8" max="8" width="15.81640625" customWidth="1"/>
+    <col min="9" max="9" width="16.36328125" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25" customHeight="1">
@@ -790,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -802,1408 +811,1540 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="17">
+    <row r="2" spans="1:12" ht="15.5">
       <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="E2" s="5" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:12" ht="17">
+    <row r="3" spans="1:12" ht="15.5">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E3" s="5" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:12" ht="17">
+    <row r="4" spans="1:12" ht="15.5">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E4" s="5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:12" ht="17">
+    <row r="5" spans="1:12" ht="15.5">
       <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E5" s="5" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.5">
+      <c r="B6" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" s="8"/>
-    </row>
-    <row r="6" spans="1:12" ht="17">
-      <c r="B6" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E6" s="5" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.5">
+      <c r="B7" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="7"/>
-    </row>
-    <row r="7" spans="1:12" ht="17">
-      <c r="B7" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E7" s="5" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.5">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7" s="8"/>
-    </row>
-    <row r="8" spans="1:12" ht="17">
-      <c r="B8" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="9"/>
+        <v>9</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E8" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.5">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K8" s="7"/>
-    </row>
-    <row r="9" spans="1:12" ht="17">
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="E9" s="5" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.5">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K9" s="8"/>
-    </row>
-    <row r="10" spans="1:12" ht="17">
-      <c r="B10" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="E10" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:12" ht="17">
+    <row r="11" spans="1:12" ht="15.5">
       <c r="B11" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="E11" s="5" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K11" s="8"/>
     </row>
-    <row r="12" spans="1:12" ht="17">
+    <row r="12" spans="1:12" ht="15.5">
       <c r="B12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="E12" s="5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="1:12" ht="17">
+    <row r="13" spans="1:12" ht="15.5">
       <c r="B13" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="E13" s="5" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K13" s="10"/>
     </row>
-    <row r="14" spans="1:12" ht="17">
+    <row r="14" spans="1:12" ht="15.5">
       <c r="B14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E14" s="5" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K14" s="11"/>
     </row>
-    <row r="15" spans="1:12" ht="17">
+    <row r="15" spans="1:12" ht="15.5">
       <c r="B15" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E15" s="5" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K15" s="12"/>
     </row>
-    <row r="16" spans="1:12" ht="17">
+    <row r="16" spans="1:12" ht="15.5">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E16" s="5" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="2:11" ht="17">
+    <row r="17" spans="2:11" ht="15.5">
       <c r="B17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E17" s="5" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K17" s="10"/>
     </row>
-    <row r="18" spans="2:11" ht="17">
+    <row r="18" spans="2:11" ht="15.5">
       <c r="B18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="9"/>
+        <v>11</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E18" s="5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K18" s="11"/>
     </row>
-    <row r="19" spans="2:11" ht="17">
+    <row r="19" spans="2:11" ht="15.5">
       <c r="B19" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E19" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="2:11" ht="17">
+    <row r="20" spans="2:11" ht="15.5">
       <c r="B20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E20" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="2:11" ht="17">
+    <row r="21" spans="2:11" ht="15.5">
       <c r="B21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E21" s="5" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K21" s="10"/>
     </row>
-    <row r="22" spans="2:11" ht="17">
+    <row r="22" spans="2:11" ht="15.5">
       <c r="B22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E22" s="5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K22" s="11"/>
     </row>
-    <row r="23" spans="2:11" ht="17">
+    <row r="23" spans="2:11" ht="15.5">
       <c r="B23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E23" s="5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K23" s="12"/>
     </row>
-    <row r="24" spans="2:11" ht="17">
+    <row r="24" spans="2:11" ht="15.5">
       <c r="B24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E24" s="5" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K24" s="11"/>
     </row>
-    <row r="25" spans="2:11" ht="17">
+    <row r="25" spans="2:11" ht="15.5">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E25" s="5" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="8"/>
+    </row>
+    <row r="26" spans="2:11" ht="15.5">
+      <c r="B26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K25" s="8"/>
-    </row>
-    <row r="26" spans="2:11" ht="17">
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E26" s="5" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" spans="2:11" ht="15.5">
+      <c r="B27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K26" s="8"/>
-    </row>
-    <row r="27" spans="2:11" ht="17">
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E27" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K27" s="8"/>
+    </row>
+    <row r="28" spans="2:11" ht="15.5">
+      <c r="B28" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K27" s="8"/>
-    </row>
-    <row r="28" spans="2:11" ht="17">
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E28" s="5" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K28" s="7"/>
+    </row>
+    <row r="29" spans="2:11" ht="15.5">
+      <c r="B29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K28" s="7"/>
-    </row>
-    <row r="29" spans="2:11" ht="17">
-      <c r="B29" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E29" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K29" s="8"/>
+    </row>
+    <row r="30" spans="2:11" ht="15.5">
+      <c r="B30" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K29" s="8"/>
-    </row>
-    <row r="30" spans="2:11" ht="17">
-      <c r="B30" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C30" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E30" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K30" s="7"/>
+    </row>
+    <row r="31" spans="2:11" ht="15.5">
+      <c r="B31" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K30" s="7"/>
-    </row>
-    <row r="31" spans="2:11" ht="17">
-      <c r="B31" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C31" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E31" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K31" s="8"/>
+    </row>
+    <row r="32" spans="2:11" ht="15.5">
+      <c r="B32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K31" s="8"/>
-    </row>
-    <row r="32" spans="2:11" ht="17">
-      <c r="B32" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C32" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E32" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K32" s="7"/>
     </row>
-    <row r="33" spans="2:11" ht="17">
+    <row r="33" spans="2:11" ht="15.5">
       <c r="B33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E33" s="5" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" spans="2:11" ht="17">
+    <row r="34" spans="2:11" ht="15.5">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="E34" s="5" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K34" s="7"/>
+    </row>
+    <row r="35" spans="2:11" ht="15.5">
+      <c r="B35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K34" s="7"/>
-    </row>
-    <row r="35" spans="2:11" ht="17">
-      <c r="B35" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C35" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E35" s="5" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K35" s="8"/>
+    </row>
+    <row r="36" spans="2:11" ht="15.5">
+      <c r="B36" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K35" s="8"/>
-    </row>
-    <row r="36" spans="2:11" ht="17">
-      <c r="B36" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C36" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E36" s="5" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K36" s="7"/>
+    </row>
+    <row r="37" spans="2:11" ht="15.5">
+      <c r="B37" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K36" s="7"/>
-    </row>
-    <row r="37" spans="2:11" ht="17">
-      <c r="B37" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C37" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E37" s="5" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K37" s="8"/>
     </row>
-    <row r="38" spans="2:11" ht="34">
+    <row r="38" spans="2:11" ht="31">
       <c r="B38" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E38" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K38" s="7"/>
+    </row>
+    <row r="39" spans="2:11" ht="15.5">
+      <c r="B39" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K38" s="7"/>
-    </row>
-    <row r="39" spans="2:11" ht="17">
-      <c r="B39" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C39" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" s="9"/>
+        <v>14</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E39" s="5" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K39" s="8"/>
     </row>
-    <row r="40" spans="2:11" ht="17">
+    <row r="40" spans="2:11" ht="15.5">
       <c r="B40" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="9"/>
+        <v>14</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E40" s="5" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K40" s="7"/>
+    </row>
+    <row r="41" spans="2:11" ht="15.5">
+      <c r="B41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K40" s="7"/>
-    </row>
-    <row r="41" spans="2:11" ht="17">
-      <c r="B41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C41" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D41" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E41" s="5" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K41" s="8"/>
     </row>
-    <row r="42" spans="2:11" ht="17">
+    <row r="42" spans="2:11" ht="15.5">
       <c r="B42" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D42" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E42" s="5" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K42" s="7"/>
     </row>
-    <row r="43" spans="2:11" ht="17">
+    <row r="43" spans="2:11" ht="15.5">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D43" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E43" s="5" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K43" s="8"/>
     </row>
-    <row r="44" spans="2:11" ht="17">
+    <row r="44" spans="2:11" ht="15.5">
       <c r="B44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D44" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E44" s="5" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K44" s="7"/>
     </row>
-    <row r="45" spans="2:11" ht="17">
+    <row r="45" spans="2:11" ht="15.5">
       <c r="B45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E45" s="5" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K45" s="8"/>
     </row>
-    <row r="46" spans="2:11" ht="17">
+    <row r="46" spans="2:11" ht="15.5">
       <c r="B46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D46" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E46" s="5" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K46" s="7"/>
     </row>
-    <row r="47" spans="2:11" ht="17">
+    <row r="47" spans="2:11" ht="15.5">
       <c r="B47" s="3"/>
       <c r="C47" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D47" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E47" s="5" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
       <c r="H47" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K47" s="8"/>
     </row>
-    <row r="48" spans="2:11" ht="17">
+    <row r="48" spans="2:11" ht="15.5">
       <c r="B48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D48" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E48" s="5" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K48" s="7"/>
     </row>
-    <row r="49" spans="2:11" ht="17">
+    <row r="49" spans="2:11" ht="15.5">
       <c r="B49" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D49" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E49" s="5" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K49" s="8"/>
     </row>
-    <row r="50" spans="2:11" ht="17">
+    <row r="50" spans="2:11" ht="15.5">
       <c r="B50" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D50" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E50" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K50" s="7"/>
     </row>
-    <row r="51" spans="2:11" ht="17">
+    <row r="51" spans="2:11" ht="15.5">
       <c r="B51" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D51" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E51" s="5" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="2:11" ht="17">
+    <row r="52" spans="2:11" ht="15.5">
       <c r="B52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D52" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E52" s="5" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
       <c r="H52" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K52" s="7"/>
     </row>
-    <row r="53" spans="2:11" ht="17">
+    <row r="53" spans="2:11" ht="15.5">
       <c r="B53" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D53" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E53" s="5" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
       <c r="H53" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K53" s="8"/>
     </row>
-    <row r="54" spans="2:11" ht="17">
+    <row r="54" spans="2:11" ht="15.5">
       <c r="B54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D54" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E54" s="5" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
       <c r="H54" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K54" s="7"/>
     </row>
-    <row r="55" spans="2:11" ht="17">
+    <row r="55" spans="2:11" ht="15.5">
       <c r="B55" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D55" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E55" s="5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="H55" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K55" s="8"/>
+    </row>
+    <row r="56" spans="2:11" ht="15.5">
+      <c r="B56" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K55" s="8"/>
-    </row>
-    <row r="56" spans="2:11" ht="17">
-      <c r="B56" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C56" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D56" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E56" s="5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
       <c r="H56" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K56" s="7"/>
+    </row>
+    <row r="57" spans="2:11" ht="15.5">
+      <c r="B57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K56" s="7"/>
-    </row>
-    <row r="57" spans="2:11" ht="17">
-      <c r="B57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C57" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E57" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
       <c r="H57" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K57" s="8"/>
+    </row>
+    <row r="58" spans="2:11" ht="15.5">
+      <c r="B58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K57" s="8"/>
-    </row>
-    <row r="58" spans="2:11" ht="17">
-      <c r="B58" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C58" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D58" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E58" s="5" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K58" s="7"/>
+    </row>
+    <row r="59" spans="2:11" ht="15.5">
+      <c r="B59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K58" s="7"/>
-    </row>
-    <row r="59" spans="2:11" ht="17">
-      <c r="B59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C59" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D59" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E59" s="5" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
       <c r="H59" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K59" s="8"/>
+    </row>
+    <row r="60" spans="2:11" ht="15.5">
+      <c r="B60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K59" s="8"/>
-    </row>
-    <row r="60" spans="2:11" ht="17">
-      <c r="B60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C60" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D60" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E60" s="5" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K60" s="7"/>
+    </row>
+    <row r="61" spans="2:11" ht="15.5">
+      <c r="B61" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K60" s="7"/>
-    </row>
-    <row r="61" spans="2:11" ht="17">
-      <c r="B61" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C61" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D61" s="13"/>
+        <v>15</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E61" s="5" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
       <c r="H61" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K61" s="8"/>
+    </row>
+    <row r="62" spans="2:11" ht="15.5">
+      <c r="B62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I61" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K61" s="8"/>
-    </row>
-    <row r="62" spans="2:11" ht="17">
-      <c r="B62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C62" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E62" s="5" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
       <c r="H62" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K62" s="7"/>
+    </row>
+    <row r="63" spans="2:11" ht="15.5">
+      <c r="B63" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K62" s="7"/>
-    </row>
-    <row r="63" spans="2:11" ht="17">
-      <c r="B63" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="C63" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D63" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E63" s="5" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
       <c r="H63" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K63" s="8"/>
     </row>
-    <row r="64" spans="2:11" ht="17">
+    <row r="64" spans="2:11" ht="15.5">
       <c r="B64" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D64" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E64" s="5" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K64" s="7"/>
     </row>
-    <row r="65" spans="2:11" ht="17">
+    <row r="65" spans="2:11" ht="15.5">
       <c r="B65" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D65" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E65" s="5" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K65" s="8"/>
     </row>
-    <row r="66" spans="2:11" ht="17">
+    <row r="66" spans="2:11" ht="15.5">
       <c r="B66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D66" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E66" s="5" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
       <c r="H66" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K66" s="7"/>
     </row>
-    <row r="67" spans="2:11" ht="17">
+    <row r="67" spans="2:11" ht="15.5">
       <c r="B67" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D67" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="E67" s="5" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K67" s="8"/>
     </row>
@@ -3009,178 +3150,178 @@
       <c r="H140" s="16"/>
       <c r="I140" s="3"/>
     </row>
-    <row r="141" spans="2:11" ht="13"/>
-    <row r="142" spans="2:11" ht="13"/>
-    <row r="143" spans="2:11" ht="13"/>
-    <row r="144" spans="2:11" ht="13"/>
-    <row r="145" ht="13"/>
-    <row r="146" ht="13"/>
-    <row r="147" ht="13"/>
-    <row r="148" ht="13"/>
-    <row r="149" ht="13"/>
-    <row r="150" ht="13"/>
-    <row r="151" ht="13"/>
-    <row r="152" ht="13"/>
-    <row r="153" ht="13"/>
-    <row r="154" ht="13"/>
-    <row r="155" ht="13"/>
-    <row r="156" ht="13"/>
-    <row r="157" ht="13"/>
-    <row r="158" ht="13"/>
-    <row r="159" ht="13"/>
-    <row r="160" ht="13"/>
-    <row r="161" ht="13"/>
-    <row r="162" ht="13"/>
-    <row r="163" ht="13"/>
-    <row r="164" ht="13"/>
-    <row r="165" ht="13"/>
-    <row r="166" ht="13"/>
-    <row r="167" ht="13"/>
-    <row r="168" ht="13"/>
-    <row r="169" ht="13"/>
-    <row r="170" ht="13"/>
-    <row r="171" ht="13"/>
-    <row r="172" ht="13"/>
-    <row r="173" ht="13"/>
-    <row r="174" ht="13"/>
-    <row r="175" ht="13"/>
-    <row r="176" ht="13"/>
-    <row r="177" ht="13"/>
-    <row r="178" ht="13"/>
-    <row r="179" ht="13"/>
-    <row r="180" ht="13"/>
-    <row r="181" ht="13"/>
-    <row r="182" ht="13"/>
-    <row r="183" ht="13"/>
-    <row r="184" ht="13"/>
-    <row r="185" ht="13"/>
-    <row r="186" ht="13"/>
-    <row r="187" ht="13"/>
-    <row r="188" ht="13"/>
-    <row r="189" ht="13"/>
-    <row r="190" ht="13"/>
-    <row r="191" ht="13"/>
-    <row r="192" ht="13"/>
-    <row r="193" ht="13"/>
-    <row r="194" ht="13"/>
-    <row r="195" ht="13"/>
-    <row r="196" ht="13"/>
-    <row r="197" ht="13"/>
-    <row r="198" ht="13"/>
-    <row r="199" ht="13"/>
-    <row r="200" ht="13"/>
-    <row r="201" ht="13"/>
-    <row r="202" ht="13"/>
-    <row r="203" ht="13"/>
-    <row r="204" ht="13"/>
-    <row r="205" ht="13"/>
-    <row r="206" ht="13"/>
-    <row r="207" ht="13"/>
-    <row r="208" ht="13"/>
-    <row r="209" ht="13"/>
-    <row r="210" ht="13"/>
-    <row r="211" ht="13"/>
-    <row r="212" ht="13"/>
-    <row r="213" ht="13"/>
-    <row r="214" ht="13"/>
-    <row r="215" ht="13"/>
-    <row r="216" ht="13"/>
-    <row r="217" ht="13"/>
-    <row r="218" ht="13"/>
-    <row r="219" ht="13"/>
-    <row r="220" ht="13"/>
-    <row r="221" ht="13"/>
-    <row r="222" ht="13"/>
-    <row r="223" ht="13"/>
-    <row r="224" ht="13"/>
-    <row r="225" ht="13"/>
-    <row r="226" ht="13"/>
-    <row r="227" ht="13"/>
-    <row r="228" ht="13"/>
-    <row r="229" ht="13"/>
-    <row r="230" ht="13"/>
-    <row r="231" ht="13"/>
-    <row r="232" ht="13"/>
-    <row r="233" ht="13"/>
-    <row r="234" ht="13"/>
-    <row r="235" ht="13"/>
-    <row r="236" ht="13"/>
-    <row r="237" ht="13"/>
-    <row r="238" ht="13"/>
-    <row r="239" ht="13"/>
-    <row r="240" ht="13"/>
-    <row r="241" ht="13"/>
-    <row r="242" ht="13"/>
-    <row r="243" ht="13"/>
-    <row r="244" ht="13"/>
-    <row r="245" ht="13"/>
-    <row r="246" ht="13"/>
-    <row r="247" ht="13"/>
-    <row r="248" ht="13"/>
-    <row r="249" ht="13"/>
-    <row r="250" ht="13"/>
-    <row r="251" ht="13"/>
-    <row r="252" ht="13"/>
-    <row r="253" ht="13"/>
-    <row r="254" ht="13"/>
-    <row r="255" ht="13"/>
-    <row r="256" ht="13"/>
-    <row r="257" ht="13"/>
-    <row r="258" ht="13"/>
-    <row r="259" ht="13"/>
-    <row r="260" ht="13"/>
-    <row r="261" ht="13"/>
-    <row r="262" ht="13"/>
-    <row r="263" ht="13"/>
-    <row r="264" ht="13"/>
-    <row r="265" ht="13"/>
-    <row r="266" ht="13"/>
-    <row r="267" ht="13"/>
-    <row r="268" ht="13"/>
-    <row r="269" ht="13"/>
-    <row r="270" ht="13"/>
-    <row r="271" ht="13"/>
-    <row r="272" ht="13"/>
-    <row r="273" ht="13"/>
-    <row r="274" ht="13"/>
-    <row r="275" ht="13"/>
-    <row r="276" ht="13"/>
-    <row r="277" ht="13"/>
-    <row r="278" ht="13"/>
-    <row r="279" ht="13"/>
-    <row r="280" ht="13"/>
-    <row r="281" ht="13"/>
-    <row r="282" ht="13"/>
-    <row r="283" ht="13"/>
-    <row r="284" ht="13"/>
-    <row r="285" ht="13"/>
-    <row r="286" ht="13"/>
-    <row r="287" ht="13"/>
-    <row r="288" ht="13"/>
-    <row r="289" ht="13"/>
-    <row r="290" ht="13"/>
-    <row r="291" ht="13"/>
-    <row r="292" ht="13"/>
-    <row r="293" ht="13"/>
-    <row r="294" ht="13"/>
-    <row r="295" ht="13"/>
-    <row r="296" ht="13"/>
-    <row r="297" ht="13"/>
-    <row r="298" ht="13"/>
-    <row r="299" ht="13"/>
-    <row r="300" ht="13"/>
-    <row r="301" ht="13"/>
-    <row r="302" ht="13"/>
-    <row r="303" ht="13"/>
-    <row r="304" ht="13"/>
-    <row r="305" spans="2:11" ht="13"/>
-    <row r="306" spans="2:11" ht="13"/>
-    <row r="307" spans="2:11" ht="13"/>
-    <row r="308" spans="2:11" ht="13"/>
-    <row r="309" spans="2:11" ht="13"/>
-    <row r="310" spans="2:11" ht="13"/>
-    <row r="311" spans="2:11" ht="13"/>
-    <row r="312" spans="2:11" ht="13">
+    <row r="141" spans="2:11" ht="12.5"/>
+    <row r="142" spans="2:11" ht="12.5"/>
+    <row r="143" spans="2:11" ht="12.5"/>
+    <row r="144" spans="2:11" ht="12.5"/>
+    <row r="145" ht="12.5"/>
+    <row r="146" ht="12.5"/>
+    <row r="147" ht="12.5"/>
+    <row r="148" ht="12.5"/>
+    <row r="149" ht="12.5"/>
+    <row r="150" ht="12.5"/>
+    <row r="151" ht="12.5"/>
+    <row r="152" ht="12.5"/>
+    <row r="153" ht="12.5"/>
+    <row r="154" ht="12.5"/>
+    <row r="155" ht="12.5"/>
+    <row r="156" ht="12.5"/>
+    <row r="157" ht="12.5"/>
+    <row r="158" ht="12.5"/>
+    <row r="159" ht="12.5"/>
+    <row r="160" ht="12.5"/>
+    <row r="161" ht="12.5"/>
+    <row r="162" ht="12.5"/>
+    <row r="163" ht="12.5"/>
+    <row r="164" ht="12.5"/>
+    <row r="165" ht="12.5"/>
+    <row r="166" ht="12.5"/>
+    <row r="167" ht="12.5"/>
+    <row r="168" ht="12.5"/>
+    <row r="169" ht="12.5"/>
+    <row r="170" ht="12.5"/>
+    <row r="171" ht="12.5"/>
+    <row r="172" ht="12.5"/>
+    <row r="173" ht="12.5"/>
+    <row r="174" ht="12.5"/>
+    <row r="175" ht="12.5"/>
+    <row r="176" ht="12.5"/>
+    <row r="177" ht="12.5"/>
+    <row r="178" ht="12.5"/>
+    <row r="179" ht="12.5"/>
+    <row r="180" ht="12.5"/>
+    <row r="181" ht="12.5"/>
+    <row r="182" ht="12.5"/>
+    <row r="183" ht="12.5"/>
+    <row r="184" ht="12.5"/>
+    <row r="185" ht="12.5"/>
+    <row r="186" ht="12.5"/>
+    <row r="187" ht="12.5"/>
+    <row r="188" ht="12.5"/>
+    <row r="189" ht="12.5"/>
+    <row r="190" ht="12.5"/>
+    <row r="191" ht="12.5"/>
+    <row r="192" ht="12.5"/>
+    <row r="193" ht="12.5"/>
+    <row r="194" ht="12.5"/>
+    <row r="195" ht="12.5"/>
+    <row r="196" ht="12.5"/>
+    <row r="197" ht="12.5"/>
+    <row r="198" ht="12.5"/>
+    <row r="199" ht="12.5"/>
+    <row r="200" ht="12.5"/>
+    <row r="201" ht="12.5"/>
+    <row r="202" ht="12.5"/>
+    <row r="203" ht="12.5"/>
+    <row r="204" ht="12.5"/>
+    <row r="205" ht="12.5"/>
+    <row r="206" ht="12.5"/>
+    <row r="207" ht="12.5"/>
+    <row r="208" ht="12.5"/>
+    <row r="209" ht="12.5"/>
+    <row r="210" ht="12.5"/>
+    <row r="211" ht="12.5"/>
+    <row r="212" ht="12.5"/>
+    <row r="213" ht="12.5"/>
+    <row r="214" ht="12.5"/>
+    <row r="215" ht="12.5"/>
+    <row r="216" ht="12.5"/>
+    <row r="217" ht="12.5"/>
+    <row r="218" ht="12.5"/>
+    <row r="219" ht="12.5"/>
+    <row r="220" ht="12.5"/>
+    <row r="221" ht="12.5"/>
+    <row r="222" ht="12.5"/>
+    <row r="223" ht="12.5"/>
+    <row r="224" ht="12.5"/>
+    <row r="225" ht="12.5"/>
+    <row r="226" ht="12.5"/>
+    <row r="227" ht="12.5"/>
+    <row r="228" ht="12.5"/>
+    <row r="229" ht="12.5"/>
+    <row r="230" ht="12.5"/>
+    <row r="231" ht="12.5"/>
+    <row r="232" ht="12.5"/>
+    <row r="233" ht="12.5"/>
+    <row r="234" ht="12.5"/>
+    <row r="235" ht="12.5"/>
+    <row r="236" ht="12.5"/>
+    <row r="237" ht="12.5"/>
+    <row r="238" ht="12.5"/>
+    <row r="239" ht="12.5"/>
+    <row r="240" ht="12.5"/>
+    <row r="241" ht="12.5"/>
+    <row r="242" ht="12.5"/>
+    <row r="243" ht="12.5"/>
+    <row r="244" ht="12.5"/>
+    <row r="245" ht="12.5"/>
+    <row r="246" ht="12.5"/>
+    <row r="247" ht="12.5"/>
+    <row r="248" ht="12.5"/>
+    <row r="249" ht="12.5"/>
+    <row r="250" ht="12.5"/>
+    <row r="251" ht="12.5"/>
+    <row r="252" ht="12.5"/>
+    <row r="253" ht="12.5"/>
+    <row r="254" ht="12.5"/>
+    <row r="255" ht="12.5"/>
+    <row r="256" ht="12.5"/>
+    <row r="257" ht="12.5"/>
+    <row r="258" ht="12.5"/>
+    <row r="259" ht="12.5"/>
+    <row r="260" ht="12.5"/>
+    <row r="261" ht="12.5"/>
+    <row r="262" ht="12.5"/>
+    <row r="263" ht="12.5"/>
+    <row r="264" ht="12.5"/>
+    <row r="265" ht="12.5"/>
+    <row r="266" ht="12.5"/>
+    <row r="267" ht="12.5"/>
+    <row r="268" ht="12.5"/>
+    <row r="269" ht="12.5"/>
+    <row r="270" ht="12.5"/>
+    <row r="271" ht="12.5"/>
+    <row r="272" ht="12.5"/>
+    <row r="273" ht="12.5"/>
+    <row r="274" ht="12.5"/>
+    <row r="275" ht="12.5"/>
+    <row r="276" ht="12.5"/>
+    <row r="277" ht="12.5"/>
+    <row r="278" ht="12.5"/>
+    <row r="279" ht="12.5"/>
+    <row r="280" ht="12.5"/>
+    <row r="281" ht="12.5"/>
+    <row r="282" ht="12.5"/>
+    <row r="283" ht="12.5"/>
+    <row r="284" ht="12.5"/>
+    <row r="285" ht="12.5"/>
+    <row r="286" ht="12.5"/>
+    <row r="287" ht="12.5"/>
+    <row r="288" ht="12.5"/>
+    <row r="289" ht="12.5"/>
+    <row r="290" ht="12.5"/>
+    <row r="291" ht="12.5"/>
+    <row r="292" ht="12.5"/>
+    <row r="293" ht="12.5"/>
+    <row r="294" ht="12.5"/>
+    <row r="295" ht="12.5"/>
+    <row r="296" ht="12.5"/>
+    <row r="297" ht="12.5"/>
+    <row r="298" ht="12.5"/>
+    <row r="299" ht="12.5"/>
+    <row r="300" ht="12.5"/>
+    <row r="301" ht="12.5"/>
+    <row r="302" ht="12.5"/>
+    <row r="303" ht="12.5"/>
+    <row r="304" ht="12.5"/>
+    <row r="305" spans="2:11" ht="12.5"/>
+    <row r="306" spans="2:11" ht="12.5"/>
+    <row r="307" spans="2:11" ht="12.5"/>
+    <row r="308" spans="2:11" ht="12.5"/>
+    <row r="309" spans="2:11" ht="12.5"/>
+    <row r="310" spans="2:11" ht="12.5"/>
+    <row r="311" spans="2:11" ht="12.5"/>
+    <row r="312" spans="2:11" ht="12.5">
       <c r="B312" s="20"/>
       <c r="C312" s="20"/>
       <c r="D312" s="20"/>
@@ -3191,7 +3332,7 @@
       <c r="I312" s="20"/>
       <c r="K312" s="20"/>
     </row>
-    <row r="313" spans="2:11" ht="13">
+    <row r="313" spans="2:11" ht="12.5">
       <c r="B313" s="20"/>
       <c r="C313" s="20"/>
       <c r="D313" s="20"/>
@@ -3202,7 +3343,7 @@
       <c r="I313" s="20"/>
       <c r="K313" s="20"/>
     </row>
-    <row r="314" spans="2:11" ht="13">
+    <row r="314" spans="2:11" ht="12.5">
       <c r="B314" s="20"/>
       <c r="C314" s="20"/>
       <c r="D314" s="20"/>
@@ -3213,7 +3354,7 @@
       <c r="I314" s="20"/>
       <c r="K314" s="20"/>
     </row>
-    <row r="315" spans="2:11" ht="13">
+    <row r="315" spans="2:11" ht="12.5">
       <c r="B315" s="20"/>
       <c r="C315" s="20"/>
       <c r="D315" s="20"/>
@@ -3224,7 +3365,7 @@
       <c r="I315" s="20"/>
       <c r="K315" s="20"/>
     </row>
-    <row r="316" spans="2:11" ht="13">
+    <row r="316" spans="2:11" ht="12.5">
       <c r="B316" s="20"/>
       <c r="C316" s="20"/>
       <c r="D316" s="20"/>
@@ -3235,7 +3376,7 @@
       <c r="I316" s="20"/>
       <c r="K316" s="20"/>
     </row>
-    <row r="317" spans="2:11" ht="13">
+    <row r="317" spans="2:11" ht="12.5">
       <c r="B317" s="20"/>
       <c r="C317" s="20"/>
       <c r="D317" s="20"/>
@@ -3246,7 +3387,7 @@
       <c r="I317" s="20"/>
       <c r="K317" s="20"/>
     </row>
-    <row r="318" spans="2:11" ht="13">
+    <row r="318" spans="2:11" ht="12.5">
       <c r="B318" s="20"/>
       <c r="C318" s="20"/>
       <c r="D318" s="20"/>
@@ -3257,7 +3398,7 @@
       <c r="I318" s="20"/>
       <c r="K318" s="20"/>
     </row>
-    <row r="319" spans="2:11" ht="13">
+    <row r="319" spans="2:11" ht="12.5">
       <c r="B319" s="20"/>
       <c r="C319" s="20"/>
       <c r="D319" s="20"/>
@@ -3268,7 +3409,7 @@
       <c r="I319" s="20"/>
       <c r="K319" s="20"/>
     </row>
-    <row r="320" spans="2:11" ht="13">
+    <row r="320" spans="2:11" ht="12.5">
       <c r="B320" s="20"/>
       <c r="C320" s="20"/>
       <c r="D320" s="20"/>
@@ -3279,7 +3420,7 @@
       <c r="I320" s="20"/>
       <c r="K320" s="20"/>
     </row>
-    <row r="321" spans="2:11" ht="13">
+    <row r="321" spans="2:11" ht="12.5">
       <c r="B321" s="20"/>
       <c r="C321" s="20"/>
       <c r="D321" s="20"/>
@@ -3290,7 +3431,7 @@
       <c r="I321" s="20"/>
       <c r="K321" s="20"/>
     </row>
-    <row r="322" spans="2:11" ht="13">
+    <row r="322" spans="2:11" ht="12.5">
       <c r="B322" s="20"/>
       <c r="C322" s="20"/>
       <c r="D322" s="20"/>
@@ -3301,7 +3442,7 @@
       <c r="I322" s="20"/>
       <c r="K322" s="20"/>
     </row>
-    <row r="323" spans="2:11" ht="13">
+    <row r="323" spans="2:11" ht="12.5">
       <c r="B323" s="20"/>
       <c r="C323" s="20"/>
       <c r="D323" s="20"/>
@@ -3312,7 +3453,7 @@
       <c r="I323" s="20"/>
       <c r="K323" s="20"/>
     </row>
-    <row r="324" spans="2:11" ht="13">
+    <row r="324" spans="2:11" ht="12.5">
       <c r="B324" s="20"/>
       <c r="C324" s="20"/>
       <c r="D324" s="20"/>
@@ -3323,7 +3464,7 @@
       <c r="I324" s="20"/>
       <c r="K324" s="20"/>
     </row>
-    <row r="325" spans="2:11" ht="13">
+    <row r="325" spans="2:11" ht="12.5">
       <c r="B325" s="20"/>
       <c r="C325" s="20"/>
       <c r="D325" s="20"/>
@@ -3334,7 +3475,7 @@
       <c r="I325" s="20"/>
       <c r="K325" s="20"/>
     </row>
-    <row r="326" spans="2:11" ht="13">
+    <row r="326" spans="2:11" ht="12.5">
       <c r="B326" s="20"/>
       <c r="C326" s="20"/>
       <c r="D326" s="20"/>
@@ -3345,7 +3486,7 @@
       <c r="I326" s="20"/>
       <c r="K326" s="20"/>
     </row>
-    <row r="327" spans="2:11" ht="13">
+    <row r="327" spans="2:11" ht="12.5">
       <c r="B327" s="20"/>
       <c r="C327" s="20"/>
       <c r="D327" s="20"/>
@@ -3356,7 +3497,7 @@
       <c r="I327" s="20"/>
       <c r="K327" s="20"/>
     </row>
-    <row r="328" spans="2:11" ht="13">
+    <row r="328" spans="2:11" ht="12.5">
       <c r="B328" s="20"/>
       <c r="C328" s="20"/>
       <c r="D328" s="20"/>
@@ -3367,7 +3508,7 @@
       <c r="I328" s="20"/>
       <c r="K328" s="20"/>
     </row>
-    <row r="329" spans="2:11" ht="13">
+    <row r="329" spans="2:11" ht="12.5">
       <c r="B329" s="20"/>
       <c r="C329" s="20"/>
       <c r="D329" s="20"/>
@@ -3378,7 +3519,7 @@
       <c r="I329" s="20"/>
       <c r="K329" s="20"/>
     </row>
-    <row r="330" spans="2:11" ht="13">
+    <row r="330" spans="2:11" ht="12.5">
       <c r="B330" s="20"/>
       <c r="C330" s="20"/>
       <c r="D330" s="20"/>
@@ -3389,7 +3530,7 @@
       <c r="I330" s="20"/>
       <c r="K330" s="20"/>
     </row>
-    <row r="331" spans="2:11" ht="13">
+    <row r="331" spans="2:11" ht="12.5">
       <c r="B331" s="20"/>
       <c r="C331" s="20"/>
       <c r="D331" s="20"/>
@@ -3400,7 +3541,7 @@
       <c r="I331" s="20"/>
       <c r="K331" s="20"/>
     </row>
-    <row r="332" spans="2:11" ht="13">
+    <row r="332" spans="2:11" ht="12.5">
       <c r="B332" s="20"/>
       <c r="C332" s="20"/>
       <c r="D332" s="20"/>
@@ -3411,7 +3552,7 @@
       <c r="I332" s="20"/>
       <c r="K332" s="20"/>
     </row>
-    <row r="333" spans="2:11" ht="13">
+    <row r="333" spans="2:11" ht="12.5">
       <c r="B333" s="20"/>
       <c r="C333" s="20"/>
       <c r="D333" s="20"/>
@@ -3422,7 +3563,7 @@
       <c r="I333" s="20"/>
       <c r="K333" s="20"/>
     </row>
-    <row r="334" spans="2:11" ht="13">
+    <row r="334" spans="2:11" ht="12.5">
       <c r="B334" s="20"/>
       <c r="C334" s="20"/>
       <c r="D334" s="20"/>
@@ -3433,7 +3574,7 @@
       <c r="I334" s="20"/>
       <c r="K334" s="20"/>
     </row>
-    <row r="335" spans="2:11" ht="13">
+    <row r="335" spans="2:11" ht="12.5">
       <c r="B335" s="20"/>
       <c r="C335" s="20"/>
       <c r="D335" s="20"/>
@@ -3444,7 +3585,7 @@
       <c r="I335" s="20"/>
       <c r="K335" s="20"/>
     </row>
-    <row r="336" spans="2:11" ht="13">
+    <row r="336" spans="2:11" ht="12.5">
       <c r="B336" s="20"/>
       <c r="C336" s="20"/>
       <c r="D336" s="20"/>
@@ -3455,7 +3596,7 @@
       <c r="I336" s="20"/>
       <c r="K336" s="20"/>
     </row>
-    <row r="337" spans="2:11" ht="13">
+    <row r="337" spans="2:11" ht="12.5">
       <c r="B337" s="20"/>
       <c r="C337" s="20"/>
       <c r="D337" s="20"/>
@@ -3466,7 +3607,7 @@
       <c r="I337" s="20"/>
       <c r="K337" s="20"/>
     </row>
-    <row r="338" spans="2:11" ht="13">
+    <row r="338" spans="2:11" ht="12.5">
       <c r="B338" s="20"/>
       <c r="C338" s="20"/>
       <c r="D338" s="20"/>
@@ -3477,7 +3618,7 @@
       <c r="I338" s="20"/>
       <c r="K338" s="20"/>
     </row>
-    <row r="339" spans="2:11" ht="13">
+    <row r="339" spans="2:11" ht="12.5">
       <c r="B339" s="20"/>
       <c r="C339" s="20"/>
       <c r="D339" s="20"/>
@@ -3488,7 +3629,7 @@
       <c r="I339" s="20"/>
       <c r="K339" s="20"/>
     </row>
-    <row r="340" spans="2:11" ht="13">
+    <row r="340" spans="2:11" ht="12.5">
       <c r="B340" s="20"/>
       <c r="C340" s="20"/>
       <c r="D340" s="20"/>
@@ -3499,7 +3640,7 @@
       <c r="I340" s="20"/>
       <c r="K340" s="20"/>
     </row>
-    <row r="341" spans="2:11" ht="13">
+    <row r="341" spans="2:11" ht="12.5">
       <c r="B341" s="20"/>
       <c r="C341" s="20"/>
       <c r="D341" s="20"/>
@@ -3510,7 +3651,7 @@
       <c r="I341" s="20"/>
       <c r="K341" s="20"/>
     </row>
-    <row r="342" spans="2:11" ht="13">
+    <row r="342" spans="2:11" ht="12.5">
       <c r="B342" s="20"/>
       <c r="C342" s="20"/>
       <c r="D342" s="20"/>
@@ -3521,7 +3662,7 @@
       <c r="I342" s="20"/>
       <c r="K342" s="20"/>
     </row>
-    <row r="343" spans="2:11" ht="13">
+    <row r="343" spans="2:11" ht="12.5">
       <c r="B343" s="20"/>
       <c r="C343" s="20"/>
       <c r="D343" s="20"/>
@@ -3532,7 +3673,7 @@
       <c r="I343" s="20"/>
       <c r="K343" s="20"/>
     </row>
-    <row r="344" spans="2:11" ht="13">
+    <row r="344" spans="2:11" ht="12.5">
       <c r="B344" s="20"/>
       <c r="C344" s="20"/>
       <c r="D344" s="20"/>
@@ -3543,7 +3684,7 @@
       <c r="I344" s="20"/>
       <c r="K344" s="20"/>
     </row>
-    <row r="345" spans="2:11" ht="13">
+    <row r="345" spans="2:11" ht="12.5">
       <c r="B345" s="20"/>
       <c r="C345" s="20"/>
       <c r="D345" s="20"/>
@@ -3554,7 +3695,7 @@
       <c r="I345" s="20"/>
       <c r="K345" s="20"/>
     </row>
-    <row r="346" spans="2:11" ht="13">
+    <row r="346" spans="2:11" ht="12.5">
       <c r="B346" s="20"/>
       <c r="C346" s="20"/>
       <c r="D346" s="20"/>
@@ -3565,7 +3706,7 @@
       <c r="I346" s="20"/>
       <c r="K346" s="20"/>
     </row>
-    <row r="347" spans="2:11" ht="13">
+    <row r="347" spans="2:11" ht="12.5">
       <c r="B347" s="20"/>
       <c r="C347" s="20"/>
       <c r="D347" s="20"/>
@@ -3576,7 +3717,7 @@
       <c r="I347" s="20"/>
       <c r="K347" s="20"/>
     </row>
-    <row r="348" spans="2:11" ht="13">
+    <row r="348" spans="2:11" ht="12.5">
       <c r="B348" s="20"/>
       <c r="C348" s="20"/>
       <c r="D348" s="20"/>
@@ -3587,7 +3728,7 @@
       <c r="I348" s="20"/>
       <c r="K348" s="20"/>
     </row>
-    <row r="349" spans="2:11" ht="13">
+    <row r="349" spans="2:11" ht="12.5">
       <c r="B349" s="20"/>
       <c r="C349" s="20"/>
       <c r="D349" s="20"/>
@@ -3598,7 +3739,7 @@
       <c r="I349" s="20"/>
       <c r="K349" s="20"/>
     </row>
-    <row r="350" spans="2:11" ht="13">
+    <row r="350" spans="2:11" ht="12.5">
       <c r="B350" s="20"/>
       <c r="C350" s="20"/>
       <c r="D350" s="20"/>
@@ -3609,7 +3750,7 @@
       <c r="I350" s="20"/>
       <c r="K350" s="20"/>
     </row>
-    <row r="351" spans="2:11" ht="13">
+    <row r="351" spans="2:11" ht="12.5">
       <c r="B351" s="20"/>
       <c r="C351" s="20"/>
       <c r="D351" s="20"/>
@@ -3620,7 +3761,7 @@
       <c r="I351" s="20"/>
       <c r="K351" s="20"/>
     </row>
-    <row r="352" spans="2:11" ht="13">
+    <row r="352" spans="2:11" ht="12.5">
       <c r="B352" s="20"/>
       <c r="C352" s="20"/>
       <c r="D352" s="20"/>
@@ -3631,7 +3772,7 @@
       <c r="I352" s="20"/>
       <c r="K352" s="20"/>
     </row>
-    <row r="353" spans="2:11" ht="13">
+    <row r="353" spans="2:11" ht="12.5">
       <c r="B353" s="20"/>
       <c r="C353" s="20"/>
       <c r="D353" s="20"/>
@@ -3642,7 +3783,7 @@
       <c r="I353" s="20"/>
       <c r="K353" s="20"/>
     </row>
-    <row r="354" spans="2:11" ht="13">
+    <row r="354" spans="2:11" ht="12.5">
       <c r="B354" s="20"/>
       <c r="C354" s="20"/>
       <c r="D354" s="20"/>
@@ -3653,7 +3794,7 @@
       <c r="I354" s="20"/>
       <c r="K354" s="20"/>
     </row>
-    <row r="355" spans="2:11" ht="13">
+    <row r="355" spans="2:11" ht="12.5">
       <c r="B355" s="20"/>
       <c r="C355" s="20"/>
       <c r="D355" s="20"/>
@@ -3664,7 +3805,7 @@
       <c r="I355" s="20"/>
       <c r="K355" s="20"/>
     </row>
-    <row r="356" spans="2:11" ht="13">
+    <row r="356" spans="2:11" ht="12.5">
       <c r="B356" s="20"/>
       <c r="C356" s="20"/>
       <c r="D356" s="20"/>
@@ -3675,7 +3816,7 @@
       <c r="I356" s="20"/>
       <c r="K356" s="20"/>
     </row>
-    <row r="357" spans="2:11" ht="13">
+    <row r="357" spans="2:11" ht="12.5">
       <c r="B357" s="20"/>
       <c r="C357" s="20"/>
       <c r="D357" s="20"/>
@@ -3686,7 +3827,7 @@
       <c r="I357" s="20"/>
       <c r="K357" s="20"/>
     </row>
-    <row r="358" spans="2:11" ht="13">
+    <row r="358" spans="2:11" ht="12.5">
       <c r="B358" s="20"/>
       <c r="C358" s="20"/>
       <c r="D358" s="20"/>
@@ -3697,7 +3838,7 @@
       <c r="I358" s="20"/>
       <c r="K358" s="20"/>
     </row>
-    <row r="359" spans="2:11" ht="13">
+    <row r="359" spans="2:11" ht="12.5">
       <c r="B359" s="20"/>
       <c r="C359" s="20"/>
       <c r="D359" s="20"/>
@@ -3708,7 +3849,7 @@
       <c r="I359" s="20"/>
       <c r="K359" s="20"/>
     </row>
-    <row r="360" spans="2:11" ht="13">
+    <row r="360" spans="2:11" ht="12.5">
       <c r="B360" s="20"/>
       <c r="C360" s="20"/>
       <c r="D360" s="20"/>
@@ -3719,7 +3860,7 @@
       <c r="I360" s="20"/>
       <c r="K360" s="20"/>
     </row>
-    <row r="361" spans="2:11" ht="13">
+    <row r="361" spans="2:11" ht="12.5">
       <c r="B361" s="20"/>
       <c r="C361" s="20"/>
       <c r="D361" s="20"/>
@@ -3730,7 +3871,7 @@
       <c r="I361" s="20"/>
       <c r="K361" s="20"/>
     </row>
-    <row r="362" spans="2:11" ht="13">
+    <row r="362" spans="2:11" ht="12.5">
       <c r="B362" s="20"/>
       <c r="C362" s="20"/>
       <c r="D362" s="20"/>
@@ -3741,7 +3882,7 @@
       <c r="I362" s="20"/>
       <c r="K362" s="20"/>
     </row>
-    <row r="363" spans="2:11" ht="13">
+    <row r="363" spans="2:11" ht="12.5">
       <c r="B363" s="20"/>
       <c r="C363" s="20"/>
       <c r="D363" s="20"/>
@@ -3752,7 +3893,7 @@
       <c r="I363" s="20"/>
       <c r="K363" s="20"/>
     </row>
-    <row r="364" spans="2:11" ht="13">
+    <row r="364" spans="2:11" ht="12.5">
       <c r="B364" s="20"/>
       <c r="C364" s="20"/>
       <c r="D364" s="20"/>
@@ -3763,7 +3904,7 @@
       <c r="I364" s="20"/>
       <c r="K364" s="20"/>
     </row>
-    <row r="365" spans="2:11" ht="13">
+    <row r="365" spans="2:11" ht="12.5">
       <c r="B365" s="20"/>
       <c r="C365" s="20"/>
       <c r="D365" s="20"/>
@@ -3774,7 +3915,7 @@
       <c r="I365" s="20"/>
       <c r="K365" s="20"/>
     </row>
-    <row r="366" spans="2:11" ht="13">
+    <row r="366" spans="2:11" ht="12.5">
       <c r="B366" s="20"/>
       <c r="C366" s="20"/>
       <c r="D366" s="20"/>
@@ -3785,7 +3926,7 @@
       <c r="I366" s="20"/>
       <c r="K366" s="20"/>
     </row>
-    <row r="367" spans="2:11" ht="13">
+    <row r="367" spans="2:11" ht="12.5">
       <c r="B367" s="20"/>
       <c r="C367" s="20"/>
       <c r="D367" s="20"/>
@@ -3796,7 +3937,7 @@
       <c r="I367" s="20"/>
       <c r="K367" s="20"/>
     </row>
-    <row r="368" spans="2:11" ht="13">
+    <row r="368" spans="2:11" ht="12.5">
       <c r="B368" s="20"/>
       <c r="C368" s="20"/>
       <c r="D368" s="20"/>
@@ -3807,7 +3948,7 @@
       <c r="I368" s="20"/>
       <c r="K368" s="20"/>
     </row>
-    <row r="369" spans="2:11" ht="13">
+    <row r="369" spans="2:11" ht="12.5">
       <c r="B369" s="20"/>
       <c r="C369" s="20"/>
       <c r="D369" s="20"/>
@@ -3818,7 +3959,7 @@
       <c r="I369" s="20"/>
       <c r="K369" s="20"/>
     </row>
-    <row r="370" spans="2:11" ht="13">
+    <row r="370" spans="2:11" ht="12.5">
       <c r="B370" s="20"/>
       <c r="C370" s="20"/>
       <c r="D370" s="20"/>
@@ -3829,7 +3970,7 @@
       <c r="I370" s="20"/>
       <c r="K370" s="20"/>
     </row>
-    <row r="371" spans="2:11" ht="13">
+    <row r="371" spans="2:11" ht="12.5">
       <c r="B371" s="20"/>
       <c r="C371" s="20"/>
       <c r="D371" s="20"/>
@@ -3840,7 +3981,7 @@
       <c r="I371" s="20"/>
       <c r="K371" s="20"/>
     </row>
-    <row r="372" spans="2:11" ht="13">
+    <row r="372" spans="2:11" ht="12.5">
       <c r="B372" s="20"/>
       <c r="C372" s="20"/>
       <c r="D372" s="20"/>
@@ -3851,7 +3992,7 @@
       <c r="I372" s="20"/>
       <c r="K372" s="20"/>
     </row>
-    <row r="373" spans="2:11" ht="13">
+    <row r="373" spans="2:11" ht="12.5">
       <c r="B373" s="20"/>
       <c r="C373" s="20"/>
       <c r="D373" s="20"/>
@@ -3862,7 +4003,7 @@
       <c r="I373" s="20"/>
       <c r="K373" s="20"/>
     </row>
-    <row r="374" spans="2:11" ht="13">
+    <row r="374" spans="2:11" ht="12.5">
       <c r="B374" s="20"/>
       <c r="C374" s="20"/>
       <c r="D374" s="20"/>
@@ -3873,7 +4014,7 @@
       <c r="I374" s="20"/>
       <c r="K374" s="20"/>
     </row>
-    <row r="375" spans="2:11" ht="13">
+    <row r="375" spans="2:11" ht="12.5">
       <c r="B375" s="20"/>
       <c r="C375" s="20"/>
       <c r="D375" s="20"/>
@@ -3884,7 +4025,7 @@
       <c r="I375" s="20"/>
       <c r="K375" s="20"/>
     </row>
-    <row r="376" spans="2:11" ht="13">
+    <row r="376" spans="2:11" ht="12.5">
       <c r="B376" s="20"/>
       <c r="C376" s="20"/>
       <c r="D376" s="20"/>
@@ -3895,7 +4036,7 @@
       <c r="I376" s="20"/>
       <c r="K376" s="20"/>
     </row>
-    <row r="377" spans="2:11" ht="13">
+    <row r="377" spans="2:11" ht="12.5">
       <c r="B377" s="20"/>
       <c r="C377" s="20"/>
       <c r="D377" s="20"/>
@@ -3906,7 +4047,7 @@
       <c r="I377" s="20"/>
       <c r="K377" s="20"/>
     </row>
-    <row r="378" spans="2:11" ht="13">
+    <row r="378" spans="2:11" ht="12.5">
       <c r="B378" s="20"/>
       <c r="C378" s="20"/>
       <c r="D378" s="20"/>
@@ -3917,7 +4058,7 @@
       <c r="I378" s="20"/>
       <c r="K378" s="20"/>
     </row>
-    <row r="379" spans="2:11" ht="13">
+    <row r="379" spans="2:11" ht="12.5">
       <c r="B379" s="20"/>
       <c r="C379" s="20"/>
       <c r="D379" s="20"/>
@@ -3928,7 +4069,7 @@
       <c r="I379" s="20"/>
       <c r="K379" s="20"/>
     </row>
-    <row r="380" spans="2:11" ht="13">
+    <row r="380" spans="2:11" ht="12.5">
       <c r="B380" s="20"/>
       <c r="C380" s="20"/>
       <c r="D380" s="20"/>
@@ -3939,7 +4080,7 @@
       <c r="I380" s="20"/>
       <c r="K380" s="20"/>
     </row>
-    <row r="381" spans="2:11" ht="13">
+    <row r="381" spans="2:11" ht="12.5">
       <c r="B381" s="20"/>
       <c r="C381" s="20"/>
       <c r="D381" s="20"/>
@@ -3950,7 +4091,7 @@
       <c r="I381" s="20"/>
       <c r="K381" s="20"/>
     </row>
-    <row r="382" spans="2:11" ht="13">
+    <row r="382" spans="2:11" ht="12.5">
       <c r="B382" s="20"/>
       <c r="C382" s="20"/>
       <c r="D382" s="20"/>
@@ -3961,7 +4102,7 @@
       <c r="I382" s="20"/>
       <c r="K382" s="20"/>
     </row>
-    <row r="383" spans="2:11" ht="13">
+    <row r="383" spans="2:11" ht="12.5">
       <c r="B383" s="20"/>
       <c r="C383" s="20"/>
       <c r="D383" s="20"/>
@@ -3972,7 +4113,7 @@
       <c r="I383" s="20"/>
       <c r="K383" s="20"/>
     </row>
-    <row r="384" spans="2:11" ht="13">
+    <row r="384" spans="2:11" ht="12.5">
       <c r="B384" s="20"/>
       <c r="C384" s="20"/>
       <c r="D384" s="20"/>
@@ -3983,7 +4124,7 @@
       <c r="I384" s="20"/>
       <c r="K384" s="20"/>
     </row>
-    <row r="385" spans="2:11" ht="13">
+    <row r="385" spans="2:11" ht="12.5">
       <c r="B385" s="20"/>
       <c r="C385" s="20"/>
       <c r="D385" s="20"/>
@@ -3994,7 +4135,7 @@
       <c r="I385" s="20"/>
       <c r="K385" s="20"/>
     </row>
-    <row r="386" spans="2:11" ht="13">
+    <row r="386" spans="2:11" ht="12.5">
       <c r="B386" s="20"/>
       <c r="C386" s="20"/>
       <c r="D386" s="20"/>
@@ -4005,7 +4146,7 @@
       <c r="I386" s="20"/>
       <c r="K386" s="20"/>
     </row>
-    <row r="387" spans="2:11" ht="13">
+    <row r="387" spans="2:11" ht="12.5">
       <c r="B387" s="20"/>
       <c r="C387" s="20"/>
       <c r="D387" s="20"/>
@@ -4016,7 +4157,7 @@
       <c r="I387" s="20"/>
       <c r="K387" s="20"/>
     </row>
-    <row r="388" spans="2:11" ht="13">
+    <row r="388" spans="2:11" ht="12.5">
       <c r="B388" s="20"/>
       <c r="C388" s="20"/>
       <c r="D388" s="20"/>
@@ -4027,7 +4168,7 @@
       <c r="I388" s="20"/>
       <c r="K388" s="20"/>
     </row>
-    <row r="389" spans="2:11" ht="13">
+    <row r="389" spans="2:11" ht="12.5">
       <c r="B389" s="20"/>
       <c r="C389" s="20"/>
       <c r="D389" s="20"/>
@@ -4038,7 +4179,7 @@
       <c r="I389" s="20"/>
       <c r="K389" s="20"/>
     </row>
-    <row r="390" spans="2:11" ht="13">
+    <row r="390" spans="2:11" ht="12.5">
       <c r="B390" s="20"/>
       <c r="C390" s="20"/>
       <c r="D390" s="20"/>
@@ -4049,7 +4190,7 @@
       <c r="I390" s="20"/>
       <c r="K390" s="20"/>
     </row>
-    <row r="391" spans="2:11" ht="13">
+    <row r="391" spans="2:11" ht="12.5">
       <c r="B391" s="20"/>
       <c r="C391" s="20"/>
       <c r="D391" s="20"/>
@@ -4060,7 +4201,7 @@
       <c r="I391" s="20"/>
       <c r="K391" s="20"/>
     </row>
-    <row r="392" spans="2:11" ht="13">
+    <row r="392" spans="2:11" ht="12.5">
       <c r="B392" s="20"/>
       <c r="C392" s="20"/>
       <c r="D392" s="20"/>
@@ -4071,7 +4212,7 @@
       <c r="I392" s="20"/>
       <c r="K392" s="20"/>
     </row>
-    <row r="393" spans="2:11" ht="13">
+    <row r="393" spans="2:11" ht="12.5">
       <c r="B393" s="20"/>
       <c r="C393" s="20"/>
       <c r="D393" s="20"/>
@@ -4082,7 +4223,7 @@
       <c r="I393" s="20"/>
       <c r="K393" s="20"/>
     </row>
-    <row r="394" spans="2:11" ht="13">
+    <row r="394" spans="2:11" ht="12.5">
       <c r="B394" s="20"/>
       <c r="C394" s="20"/>
       <c r="D394" s="20"/>
@@ -4093,7 +4234,7 @@
       <c r="I394" s="20"/>
       <c r="K394" s="20"/>
     </row>
-    <row r="395" spans="2:11" ht="13">
+    <row r="395" spans="2:11" ht="12.5">
       <c r="B395" s="20"/>
       <c r="C395" s="20"/>
       <c r="D395" s="20"/>
@@ -4104,7 +4245,7 @@
       <c r="I395" s="20"/>
       <c r="K395" s="20"/>
     </row>
-    <row r="396" spans="2:11" ht="13">
+    <row r="396" spans="2:11" ht="12.5">
       <c r="B396" s="20"/>
       <c r="C396" s="20"/>
       <c r="D396" s="20"/>
@@ -4115,7 +4256,7 @@
       <c r="I396" s="20"/>
       <c r="K396" s="20"/>
     </row>
-    <row r="397" spans="2:11" ht="13">
+    <row r="397" spans="2:11" ht="12.5">
       <c r="B397" s="20"/>
       <c r="C397" s="20"/>
       <c r="D397" s="20"/>
@@ -4126,7 +4267,7 @@
       <c r="I397" s="20"/>
       <c r="K397" s="20"/>
     </row>
-    <row r="398" spans="2:11" ht="13">
+    <row r="398" spans="2:11" ht="12.5">
       <c r="B398" s="20"/>
       <c r="C398" s="20"/>
       <c r="D398" s="20"/>
@@ -4137,7 +4278,7 @@
       <c r="I398" s="20"/>
       <c r="K398" s="20"/>
     </row>
-    <row r="399" spans="2:11" ht="13">
+    <row r="399" spans="2:11" ht="12.5">
       <c r="B399" s="20"/>
       <c r="C399" s="20"/>
       <c r="D399" s="20"/>
@@ -4148,7 +4289,7 @@
       <c r="I399" s="20"/>
       <c r="K399" s="20"/>
     </row>
-    <row r="400" spans="2:11" ht="13">
+    <row r="400" spans="2:11" ht="12.5">
       <c r="B400" s="20"/>
       <c r="C400" s="20"/>
       <c r="D400" s="20"/>
@@ -4159,7 +4300,7 @@
       <c r="I400" s="20"/>
       <c r="K400" s="20"/>
     </row>
-    <row r="401" spans="2:11" ht="13">
+    <row r="401" spans="2:11" ht="12.5">
       <c r="B401" s="20"/>
       <c r="C401" s="20"/>
       <c r="D401" s="20"/>
@@ -4170,7 +4311,7 @@
       <c r="I401" s="20"/>
       <c r="K401" s="20"/>
     </row>
-    <row r="402" spans="2:11" ht="13">
+    <row r="402" spans="2:11" ht="12.5">
       <c r="B402" s="20"/>
       <c r="C402" s="20"/>
       <c r="D402" s="20"/>
@@ -4181,7 +4322,7 @@
       <c r="I402" s="20"/>
       <c r="K402" s="20"/>
     </row>
-    <row r="403" spans="2:11" ht="13">
+    <row r="403" spans="2:11" ht="12.5">
       <c r="B403" s="20"/>
       <c r="C403" s="20"/>
       <c r="D403" s="20"/>
@@ -4192,7 +4333,7 @@
       <c r="I403" s="20"/>
       <c r="K403" s="20"/>
     </row>
-    <row r="404" spans="2:11" ht="13">
+    <row r="404" spans="2:11" ht="12.5">
       <c r="B404" s="20"/>
       <c r="C404" s="20"/>
       <c r="D404" s="20"/>
@@ -4203,7 +4344,7 @@
       <c r="I404" s="20"/>
       <c r="K404" s="20"/>
     </row>
-    <row r="405" spans="2:11" ht="13">
+    <row r="405" spans="2:11" ht="12.5">
       <c r="B405" s="20"/>
       <c r="C405" s="20"/>
       <c r="D405" s="20"/>
@@ -4214,7 +4355,7 @@
       <c r="I405" s="20"/>
       <c r="K405" s="20"/>
     </row>
-    <row r="406" spans="2:11" ht="13">
+    <row r="406" spans="2:11" ht="12.5">
       <c r="B406" s="20"/>
       <c r="C406" s="20"/>
       <c r="D406" s="20"/>
@@ -4225,7 +4366,7 @@
       <c r="I406" s="20"/>
       <c r="K406" s="20"/>
     </row>
-    <row r="407" spans="2:11" ht="13">
+    <row r="407" spans="2:11" ht="12.5">
       <c r="B407" s="20"/>
       <c r="C407" s="20"/>
       <c r="D407" s="20"/>
@@ -4236,7 +4377,7 @@
       <c r="I407" s="20"/>
       <c r="K407" s="20"/>
     </row>
-    <row r="408" spans="2:11" ht="13">
+    <row r="408" spans="2:11" ht="12.5">
       <c r="B408" s="20"/>
       <c r="C408" s="20"/>
       <c r="D408" s="20"/>
@@ -4247,7 +4388,7 @@
       <c r="I408" s="20"/>
       <c r="K408" s="20"/>
     </row>
-    <row r="409" spans="2:11" ht="13">
+    <row r="409" spans="2:11" ht="12.5">
       <c r="B409" s="20"/>
       <c r="C409" s="20"/>
       <c r="D409" s="20"/>
@@ -4258,7 +4399,7 @@
       <c r="I409" s="20"/>
       <c r="K409" s="20"/>
     </row>
-    <row r="410" spans="2:11" ht="13">
+    <row r="410" spans="2:11" ht="12.5">
       <c r="B410" s="20"/>
       <c r="C410" s="20"/>
       <c r="D410" s="20"/>
@@ -4269,7 +4410,7 @@
       <c r="I410" s="20"/>
       <c r="K410" s="20"/>
     </row>
-    <row r="411" spans="2:11" ht="13">
+    <row r="411" spans="2:11" ht="12.5">
       <c r="B411" s="20"/>
       <c r="C411" s="20"/>
       <c r="D411" s="20"/>
@@ -4280,7 +4421,7 @@
       <c r="I411" s="20"/>
       <c r="K411" s="20"/>
     </row>
-    <row r="412" spans="2:11" ht="13">
+    <row r="412" spans="2:11" ht="12.5">
       <c r="B412" s="20"/>
       <c r="C412" s="20"/>
       <c r="D412" s="20"/>
@@ -4291,7 +4432,7 @@
       <c r="I412" s="20"/>
       <c r="K412" s="20"/>
     </row>
-    <row r="413" spans="2:11" ht="13">
+    <row r="413" spans="2:11" ht="12.5">
       <c r="B413" s="20"/>
       <c r="C413" s="20"/>
       <c r="D413" s="20"/>
@@ -4302,7 +4443,7 @@
       <c r="I413" s="20"/>
       <c r="K413" s="20"/>
     </row>
-    <row r="414" spans="2:11" ht="13">
+    <row r="414" spans="2:11" ht="12.5">
       <c r="B414" s="20"/>
       <c r="C414" s="20"/>
       <c r="D414" s="20"/>
@@ -4313,7 +4454,7 @@
       <c r="I414" s="20"/>
       <c r="K414" s="20"/>
     </row>
-    <row r="415" spans="2:11" ht="13">
+    <row r="415" spans="2:11" ht="12.5">
       <c r="B415" s="20"/>
       <c r="C415" s="20"/>
       <c r="D415" s="20"/>
@@ -4324,7 +4465,7 @@
       <c r="I415" s="20"/>
       <c r="K415" s="20"/>
     </row>
-    <row r="416" spans="2:11" ht="13">
+    <row r="416" spans="2:11" ht="12.5">
       <c r="B416" s="20"/>
       <c r="C416" s="20"/>
       <c r="D416" s="20"/>
@@ -4335,7 +4476,7 @@
       <c r="I416" s="20"/>
       <c r="K416" s="20"/>
     </row>
-    <row r="417" spans="2:11" ht="13">
+    <row r="417" spans="2:11" ht="12.5">
       <c r="B417" s="20"/>
       <c r="C417" s="20"/>
       <c r="D417" s="20"/>
@@ -4346,7 +4487,7 @@
       <c r="I417" s="20"/>
       <c r="K417" s="20"/>
     </row>
-    <row r="418" spans="2:11" ht="13">
+    <row r="418" spans="2:11" ht="12.5">
       <c r="B418" s="20"/>
       <c r="C418" s="20"/>
       <c r="D418" s="20"/>
@@ -4357,7 +4498,7 @@
       <c r="I418" s="20"/>
       <c r="K418" s="20"/>
     </row>
-    <row r="419" spans="2:11" ht="13">
+    <row r="419" spans="2:11" ht="12.5">
       <c r="B419" s="20"/>
       <c r="C419" s="20"/>
       <c r="D419" s="20"/>
@@ -4368,7 +4509,7 @@
       <c r="I419" s="20"/>
       <c r="K419" s="20"/>
     </row>
-    <row r="420" spans="2:11" ht="13">
+    <row r="420" spans="2:11" ht="12.5">
       <c r="B420" s="20"/>
       <c r="C420" s="20"/>
       <c r="D420" s="20"/>
@@ -4379,7 +4520,7 @@
       <c r="I420" s="20"/>
       <c r="K420" s="20"/>
     </row>
-    <row r="421" spans="2:11" ht="13">
+    <row r="421" spans="2:11" ht="12.5">
       <c r="B421" s="20"/>
       <c r="C421" s="20"/>
       <c r="D421" s="20"/>
@@ -4390,7 +4531,7 @@
       <c r="I421" s="20"/>
       <c r="K421" s="20"/>
     </row>
-    <row r="422" spans="2:11" ht="13">
+    <row r="422" spans="2:11" ht="12.5">
       <c r="B422" s="20"/>
       <c r="C422" s="20"/>
       <c r="D422" s="20"/>
@@ -4401,7 +4542,7 @@
       <c r="I422" s="20"/>
       <c r="K422" s="20"/>
     </row>
-    <row r="423" spans="2:11" ht="13">
+    <row r="423" spans="2:11" ht="12.5">
       <c r="B423" s="20"/>
       <c r="C423" s="20"/>
       <c r="D423" s="20"/>
@@ -4412,7 +4553,7 @@
       <c r="I423" s="20"/>
       <c r="K423" s="20"/>
     </row>
-    <row r="424" spans="2:11" ht="13">
+    <row r="424" spans="2:11" ht="12.5">
       <c r="B424" s="20"/>
       <c r="C424" s="20"/>
       <c r="D424" s="20"/>
@@ -4423,7 +4564,7 @@
       <c r="I424" s="20"/>
       <c r="K424" s="20"/>
     </row>
-    <row r="425" spans="2:11" ht="13">
+    <row r="425" spans="2:11" ht="12.5">
       <c r="B425" s="20"/>
       <c r="C425" s="20"/>
       <c r="D425" s="20"/>
@@ -4434,7 +4575,7 @@
       <c r="I425" s="20"/>
       <c r="K425" s="20"/>
     </row>
-    <row r="426" spans="2:11" ht="13">
+    <row r="426" spans="2:11" ht="12.5">
       <c r="B426" s="20"/>
       <c r="C426" s="20"/>
       <c r="D426" s="20"/>
@@ -4445,7 +4586,7 @@
       <c r="I426" s="20"/>
       <c r="K426" s="20"/>
     </row>
-    <row r="427" spans="2:11" ht="13">
+    <row r="427" spans="2:11" ht="12.5">
       <c r="B427" s="20"/>
       <c r="C427" s="20"/>
       <c r="D427" s="20"/>
@@ -4456,7 +4597,7 @@
       <c r="I427" s="20"/>
       <c r="K427" s="20"/>
     </row>
-    <row r="428" spans="2:11" ht="13">
+    <row r="428" spans="2:11" ht="12.5">
       <c r="B428" s="20"/>
       <c r="C428" s="20"/>
       <c r="D428" s="20"/>
@@ -4467,7 +4608,7 @@
       <c r="I428" s="20"/>
       <c r="K428" s="20"/>
     </row>
-    <row r="429" spans="2:11" ht="13">
+    <row r="429" spans="2:11" ht="12.5">
       <c r="B429" s="20"/>
       <c r="C429" s="20"/>
       <c r="D429" s="20"/>
@@ -4478,7 +4619,7 @@
       <c r="I429" s="20"/>
       <c r="K429" s="20"/>
     </row>
-    <row r="430" spans="2:11" ht="13">
+    <row r="430" spans="2:11" ht="12.5">
       <c r="B430" s="20"/>
       <c r="C430" s="20"/>
       <c r="D430" s="20"/>
@@ -4489,7 +4630,7 @@
       <c r="I430" s="20"/>
       <c r="K430" s="20"/>
     </row>
-    <row r="431" spans="2:11" ht="13">
+    <row r="431" spans="2:11" ht="12.5">
       <c r="B431" s="20"/>
       <c r="C431" s="20"/>
       <c r="D431" s="20"/>
@@ -4500,7 +4641,7 @@
       <c r="I431" s="20"/>
       <c r="K431" s="20"/>
     </row>
-    <row r="432" spans="2:11" ht="13">
+    <row r="432" spans="2:11" ht="12.5">
       <c r="B432" s="20"/>
       <c r="C432" s="20"/>
       <c r="D432" s="20"/>
@@ -4511,7 +4652,7 @@
       <c r="I432" s="20"/>
       <c r="K432" s="20"/>
     </row>
-    <row r="433" spans="2:11" ht="13">
+    <row r="433" spans="2:11" ht="12.5">
       <c r="B433" s="20"/>
       <c r="C433" s="20"/>
       <c r="D433" s="20"/>
@@ -4522,7 +4663,7 @@
       <c r="I433" s="20"/>
       <c r="K433" s="20"/>
     </row>
-    <row r="434" spans="2:11" ht="13">
+    <row r="434" spans="2:11" ht="12.5">
       <c r="B434" s="20"/>
       <c r="C434" s="20"/>
       <c r="D434" s="20"/>
@@ -4533,7 +4674,7 @@
       <c r="I434" s="20"/>
       <c r="K434" s="20"/>
     </row>
-    <row r="435" spans="2:11" ht="13">
+    <row r="435" spans="2:11" ht="12.5">
       <c r="B435" s="20"/>
       <c r="C435" s="20"/>
       <c r="D435" s="20"/>
@@ -4544,7 +4685,7 @@
       <c r="I435" s="20"/>
       <c r="K435" s="20"/>
     </row>
-    <row r="436" spans="2:11" ht="13">
+    <row r="436" spans="2:11" ht="12.5">
       <c r="B436" s="20"/>
       <c r="C436" s="20"/>
       <c r="D436" s="20"/>
@@ -4555,7 +4696,7 @@
       <c r="I436" s="20"/>
       <c r="K436" s="20"/>
     </row>
-    <row r="437" spans="2:11" ht="13">
+    <row r="437" spans="2:11" ht="12.5">
       <c r="B437" s="20"/>
       <c r="C437" s="20"/>
       <c r="D437" s="20"/>
@@ -4566,7 +4707,7 @@
       <c r="I437" s="20"/>
       <c r="K437" s="20"/>
     </row>
-    <row r="438" spans="2:11" ht="13">
+    <row r="438" spans="2:11" ht="12.5">
       <c r="B438" s="20"/>
       <c r="C438" s="20"/>
       <c r="D438" s="20"/>
@@ -4577,7 +4718,7 @@
       <c r="I438" s="20"/>
       <c r="K438" s="20"/>
     </row>
-    <row r="439" spans="2:11" ht="13">
+    <row r="439" spans="2:11" ht="12.5">
       <c r="B439" s="20"/>
       <c r="C439" s="20"/>
       <c r="D439" s="20"/>
@@ -4588,7 +4729,7 @@
       <c r="I439" s="20"/>
       <c r="K439" s="20"/>
     </row>
-    <row r="440" spans="2:11" ht="13">
+    <row r="440" spans="2:11" ht="12.5">
       <c r="B440" s="20"/>
       <c r="C440" s="20"/>
       <c r="D440" s="20"/>
@@ -4599,7 +4740,7 @@
       <c r="I440" s="20"/>
       <c r="K440" s="20"/>
     </row>
-    <row r="441" spans="2:11" ht="13">
+    <row r="441" spans="2:11" ht="12.5">
       <c r="B441" s="20"/>
       <c r="C441" s="20"/>
       <c r="D441" s="20"/>
@@ -4610,7 +4751,7 @@
       <c r="I441" s="20"/>
       <c r="K441" s="20"/>
     </row>
-    <row r="442" spans="2:11" ht="13">
+    <row r="442" spans="2:11" ht="12.5">
       <c r="B442" s="20"/>
       <c r="C442" s="20"/>
       <c r="D442" s="20"/>
@@ -4621,7 +4762,7 @@
       <c r="I442" s="20"/>
       <c r="K442" s="20"/>
     </row>
-    <row r="443" spans="2:11" ht="13">
+    <row r="443" spans="2:11" ht="12.5">
       <c r="B443" s="20"/>
       <c r="C443" s="20"/>
       <c r="D443" s="20"/>
@@ -4632,7 +4773,7 @@
       <c r="I443" s="20"/>
       <c r="K443" s="20"/>
     </row>
-    <row r="444" spans="2:11" ht="13">
+    <row r="444" spans="2:11" ht="12.5">
       <c r="B444" s="20"/>
       <c r="C444" s="20"/>
       <c r="D444" s="20"/>
@@ -4643,7 +4784,7 @@
       <c r="I444" s="20"/>
       <c r="K444" s="20"/>
     </row>
-    <row r="445" spans="2:11" ht="13">
+    <row r="445" spans="2:11" ht="12.5">
       <c r="B445" s="20"/>
       <c r="C445" s="20"/>
       <c r="D445" s="20"/>
@@ -4654,7 +4795,7 @@
       <c r="I445" s="20"/>
       <c r="K445" s="20"/>
     </row>
-    <row r="446" spans="2:11" ht="13">
+    <row r="446" spans="2:11" ht="12.5">
       <c r="B446" s="20"/>
       <c r="C446" s="20"/>
       <c r="D446" s="20"/>
@@ -4665,7 +4806,7 @@
       <c r="I446" s="20"/>
       <c r="K446" s="20"/>
     </row>
-    <row r="447" spans="2:11" ht="13">
+    <row r="447" spans="2:11" ht="12.5">
       <c r="B447" s="20"/>
       <c r="C447" s="20"/>
       <c r="D447" s="20"/>
@@ -4676,7 +4817,7 @@
       <c r="I447" s="20"/>
       <c r="K447" s="20"/>
     </row>
-    <row r="448" spans="2:11" ht="13">
+    <row r="448" spans="2:11" ht="12.5">
       <c r="B448" s="20"/>
       <c r="C448" s="20"/>
       <c r="D448" s="20"/>
@@ -4687,7 +4828,7 @@
       <c r="I448" s="20"/>
       <c r="K448" s="20"/>
     </row>
-    <row r="449" spans="2:11" ht="13">
+    <row r="449" spans="2:11" ht="12.5">
       <c r="B449" s="20"/>
       <c r="C449" s="20"/>
       <c r="D449" s="20"/>
@@ -4698,7 +4839,7 @@
       <c r="I449" s="20"/>
       <c r="K449" s="20"/>
     </row>
-    <row r="450" spans="2:11" ht="13">
+    <row r="450" spans="2:11" ht="12.5">
       <c r="B450" s="20"/>
       <c r="C450" s="20"/>
       <c r="D450" s="20"/>
@@ -4709,7 +4850,7 @@
       <c r="I450" s="20"/>
       <c r="K450" s="20"/>
     </row>
-    <row r="451" spans="2:11" ht="13">
+    <row r="451" spans="2:11" ht="12.5">
       <c r="B451" s="20"/>
       <c r="C451" s="20"/>
       <c r="D451" s="20"/>
@@ -4720,7 +4861,7 @@
       <c r="I451" s="20"/>
       <c r="K451" s="20"/>
     </row>
-    <row r="452" spans="2:11" ht="13">
+    <row r="452" spans="2:11" ht="12.5">
       <c r="B452" s="20"/>
       <c r="C452" s="20"/>
       <c r="D452" s="20"/>
@@ -4731,7 +4872,7 @@
       <c r="I452" s="20"/>
       <c r="K452" s="20"/>
     </row>
-    <row r="453" spans="2:11" ht="13">
+    <row r="453" spans="2:11" ht="12.5">
       <c r="B453" s="20"/>
       <c r="C453" s="20"/>
       <c r="D453" s="20"/>
@@ -4742,7 +4883,7 @@
       <c r="I453" s="20"/>
       <c r="K453" s="20"/>
     </row>
-    <row r="454" spans="2:11" ht="13">
+    <row r="454" spans="2:11" ht="12.5">
       <c r="B454" s="20"/>
       <c r="C454" s="20"/>
       <c r="D454" s="20"/>
@@ -4753,7 +4894,7 @@
       <c r="I454" s="20"/>
       <c r="K454" s="20"/>
     </row>
-    <row r="455" spans="2:11" ht="13">
+    <row r="455" spans="2:11" ht="12.5">
       <c r="B455" s="20"/>
       <c r="C455" s="20"/>
       <c r="D455" s="20"/>
@@ -4764,7 +4905,7 @@
       <c r="I455" s="20"/>
       <c r="K455" s="20"/>
     </row>
-    <row r="456" spans="2:11" ht="13">
+    <row r="456" spans="2:11" ht="12.5">
       <c r="B456" s="20"/>
       <c r="C456" s="20"/>
       <c r="D456" s="20"/>
@@ -4775,7 +4916,7 @@
       <c r="I456" s="20"/>
       <c r="K456" s="20"/>
     </row>
-    <row r="457" spans="2:11" ht="13">
+    <row r="457" spans="2:11" ht="12.5">
       <c r="B457" s="20"/>
       <c r="C457" s="20"/>
       <c r="D457" s="20"/>
@@ -4786,7 +4927,7 @@
       <c r="I457" s="20"/>
       <c r="K457" s="20"/>
     </row>
-    <row r="458" spans="2:11" ht="13">
+    <row r="458" spans="2:11" ht="12.5">
       <c r="B458" s="20"/>
       <c r="C458" s="20"/>
       <c r="D458" s="20"/>
@@ -4797,7 +4938,7 @@
       <c r="I458" s="20"/>
       <c r="K458" s="20"/>
     </row>
-    <row r="459" spans="2:11" ht="13">
+    <row r="459" spans="2:11" ht="12.5">
       <c r="B459" s="20"/>
       <c r="C459" s="20"/>
       <c r="D459" s="20"/>
@@ -4808,7 +4949,7 @@
       <c r="I459" s="20"/>
       <c r="K459" s="20"/>
     </row>
-    <row r="460" spans="2:11" ht="13">
+    <row r="460" spans="2:11" ht="12.5">
       <c r="B460" s="20"/>
       <c r="C460" s="20"/>
       <c r="D460" s="20"/>
@@ -4819,7 +4960,7 @@
       <c r="I460" s="20"/>
       <c r="K460" s="20"/>
     </row>
-    <row r="461" spans="2:11" ht="13">
+    <row r="461" spans="2:11" ht="12.5">
       <c r="B461" s="20"/>
       <c r="C461" s="20"/>
       <c r="D461" s="20"/>
@@ -4830,7 +4971,7 @@
       <c r="I461" s="20"/>
       <c r="K461" s="20"/>
     </row>
-    <row r="462" spans="2:11" ht="13">
+    <row r="462" spans="2:11" ht="12.5">
       <c r="B462" s="20"/>
       <c r="C462" s="20"/>
       <c r="D462" s="20"/>
@@ -4841,7 +4982,7 @@
       <c r="I462" s="20"/>
       <c r="K462" s="20"/>
     </row>
-    <row r="463" spans="2:11" ht="13">
+    <row r="463" spans="2:11" ht="12.5">
       <c r="B463" s="20"/>
       <c r="C463" s="20"/>
       <c r="D463" s="20"/>
@@ -4852,7 +4993,7 @@
       <c r="I463" s="20"/>
       <c r="K463" s="20"/>
     </row>
-    <row r="464" spans="2:11" ht="13">
+    <row r="464" spans="2:11" ht="12.5">
       <c r="B464" s="20"/>
       <c r="C464" s="20"/>
       <c r="D464" s="20"/>
@@ -4863,7 +5004,7 @@
       <c r="I464" s="20"/>
       <c r="K464" s="20"/>
     </row>
-    <row r="465" spans="2:11" ht="13">
+    <row r="465" spans="2:11" ht="12.5">
       <c r="B465" s="20"/>
       <c r="C465" s="20"/>
       <c r="D465" s="20"/>
@@ -4874,7 +5015,7 @@
       <c r="I465" s="20"/>
       <c r="K465" s="20"/>
     </row>
-    <row r="466" spans="2:11" ht="13">
+    <row r="466" spans="2:11" ht="12.5">
       <c r="B466" s="20"/>
       <c r="C466" s="20"/>
       <c r="D466" s="20"/>
@@ -4885,7 +5026,7 @@
       <c r="I466" s="20"/>
       <c r="K466" s="20"/>
     </row>
-    <row r="467" spans="2:11" ht="13">
+    <row r="467" spans="2:11" ht="12.5">
       <c r="B467" s="20"/>
       <c r="C467" s="20"/>
       <c r="D467" s="20"/>
@@ -4896,7 +5037,7 @@
       <c r="I467" s="20"/>
       <c r="K467" s="20"/>
     </row>
-    <row r="468" spans="2:11" ht="13">
+    <row r="468" spans="2:11" ht="12.5">
       <c r="B468" s="20"/>
       <c r="C468" s="20"/>
       <c r="D468" s="20"/>
@@ -4907,7 +5048,7 @@
       <c r="I468" s="20"/>
       <c r="K468" s="20"/>
     </row>
-    <row r="469" spans="2:11" ht="13">
+    <row r="469" spans="2:11" ht="12.5">
       <c r="B469" s="20"/>
       <c r="C469" s="20"/>
       <c r="D469" s="20"/>
@@ -4918,7 +5059,7 @@
       <c r="I469" s="20"/>
       <c r="K469" s="20"/>
     </row>
-    <row r="470" spans="2:11" ht="13">
+    <row r="470" spans="2:11" ht="12.5">
       <c r="B470" s="20"/>
       <c r="C470" s="20"/>
       <c r="D470" s="20"/>
@@ -4929,7 +5070,7 @@
       <c r="I470" s="20"/>
       <c r="K470" s="20"/>
     </row>
-    <row r="471" spans="2:11" ht="13">
+    <row r="471" spans="2:11" ht="12.5">
       <c r="B471" s="20"/>
       <c r="C471" s="20"/>
       <c r="D471" s="20"/>
@@ -4940,7 +5081,7 @@
       <c r="I471" s="20"/>
       <c r="K471" s="20"/>
     </row>
-    <row r="472" spans="2:11" ht="13">
+    <row r="472" spans="2:11" ht="12.5">
       <c r="B472" s="20"/>
       <c r="C472" s="20"/>
       <c r="D472" s="20"/>
@@ -4951,7 +5092,7 @@
       <c r="I472" s="20"/>
       <c r="K472" s="20"/>
     </row>
-    <row r="473" spans="2:11" ht="13">
+    <row r="473" spans="2:11" ht="12.5">
       <c r="B473" s="20"/>
       <c r="C473" s="20"/>
       <c r="D473" s="20"/>
@@ -4962,7 +5103,7 @@
       <c r="I473" s="20"/>
       <c r="K473" s="20"/>
     </row>
-    <row r="474" spans="2:11" ht="13">
+    <row r="474" spans="2:11" ht="12.5">
       <c r="B474" s="20"/>
       <c r="C474" s="20"/>
       <c r="D474" s="20"/>
@@ -4973,7 +5114,7 @@
       <c r="I474" s="20"/>
       <c r="K474" s="20"/>
     </row>
-    <row r="475" spans="2:11" ht="13">
+    <row r="475" spans="2:11" ht="12.5">
       <c r="B475" s="20"/>
       <c r="C475" s="20"/>
       <c r="D475" s="20"/>
@@ -4984,7 +5125,7 @@
       <c r="I475" s="20"/>
       <c r="K475" s="20"/>
     </row>
-    <row r="476" spans="2:11" ht="13">
+    <row r="476" spans="2:11" ht="12.5">
       <c r="B476" s="20"/>
       <c r="C476" s="20"/>
       <c r="D476" s="20"/>
@@ -4995,7 +5136,7 @@
       <c r="I476" s="20"/>
       <c r="K476" s="20"/>
     </row>
-    <row r="477" spans="2:11" ht="13">
+    <row r="477" spans="2:11" ht="12.5">
       <c r="B477" s="20"/>
       <c r="C477" s="20"/>
       <c r="D477" s="20"/>
@@ -5006,7 +5147,7 @@
       <c r="I477" s="20"/>
       <c r="K477" s="20"/>
     </row>
-    <row r="478" spans="2:11" ht="13">
+    <row r="478" spans="2:11" ht="12.5">
       <c r="B478" s="20"/>
       <c r="C478" s="20"/>
       <c r="D478" s="20"/>
@@ -5017,7 +5158,7 @@
       <c r="I478" s="20"/>
       <c r="K478" s="20"/>
     </row>
-    <row r="479" spans="2:11" ht="13">
+    <row r="479" spans="2:11" ht="12.5">
       <c r="B479" s="20"/>
       <c r="C479" s="20"/>
       <c r="D479" s="20"/>
@@ -5028,7 +5169,7 @@
       <c r="I479" s="20"/>
       <c r="K479" s="20"/>
     </row>
-    <row r="480" spans="2:11" ht="13">
+    <row r="480" spans="2:11" ht="12.5">
       <c r="B480" s="20"/>
       <c r="C480" s="20"/>
       <c r="D480" s="20"/>
@@ -5039,7 +5180,7 @@
       <c r="I480" s="20"/>
       <c r="K480" s="20"/>
     </row>
-    <row r="481" spans="2:11" ht="13">
+    <row r="481" spans="2:11" ht="12.5">
       <c r="B481" s="20"/>
       <c r="C481" s="20"/>
       <c r="D481" s="20"/>
@@ -5050,7 +5191,7 @@
       <c r="I481" s="20"/>
       <c r="K481" s="20"/>
     </row>
-    <row r="482" spans="2:11" ht="13">
+    <row r="482" spans="2:11" ht="12.5">
       <c r="B482" s="20"/>
       <c r="C482" s="20"/>
       <c r="D482" s="20"/>
@@ -5061,7 +5202,7 @@
       <c r="I482" s="20"/>
       <c r="K482" s="20"/>
     </row>
-    <row r="483" spans="2:11" ht="13">
+    <row r="483" spans="2:11" ht="12.5">
       <c r="B483" s="20"/>
       <c r="C483" s="20"/>
       <c r="D483" s="20"/>
@@ -5072,7 +5213,7 @@
       <c r="I483" s="20"/>
       <c r="K483" s="20"/>
     </row>
-    <row r="484" spans="2:11" ht="13">
+    <row r="484" spans="2:11" ht="12.5">
       <c r="B484" s="20"/>
       <c r="C484" s="20"/>
       <c r="D484" s="20"/>
@@ -5083,7 +5224,7 @@
       <c r="I484" s="20"/>
       <c r="K484" s="20"/>
     </row>
-    <row r="485" spans="2:11" ht="13">
+    <row r="485" spans="2:11" ht="12.5">
       <c r="B485" s="20"/>
       <c r="C485" s="20"/>
       <c r="D485" s="20"/>
@@ -5094,7 +5235,7 @@
       <c r="I485" s="20"/>
       <c r="K485" s="20"/>
     </row>
-    <row r="486" spans="2:11" ht="13">
+    <row r="486" spans="2:11" ht="12.5">
       <c r="B486" s="20"/>
       <c r="C486" s="20"/>
       <c r="D486" s="20"/>
@@ -5105,7 +5246,7 @@
       <c r="I486" s="20"/>
       <c r="K486" s="20"/>
     </row>
-    <row r="487" spans="2:11" ht="13">
+    <row r="487" spans="2:11" ht="12.5">
       <c r="B487" s="20"/>
       <c r="C487" s="20"/>
       <c r="D487" s="20"/>
@@ -5116,7 +5257,7 @@
       <c r="I487" s="20"/>
       <c r="K487" s="20"/>
     </row>
-    <row r="488" spans="2:11" ht="13">
+    <row r="488" spans="2:11" ht="12.5">
       <c r="B488" s="20"/>
       <c r="C488" s="20"/>
       <c r="D488" s="20"/>
@@ -5127,7 +5268,7 @@
       <c r="I488" s="20"/>
       <c r="K488" s="20"/>
     </row>
-    <row r="489" spans="2:11" ht="13">
+    <row r="489" spans="2:11" ht="12.5">
       <c r="B489" s="20"/>
       <c r="C489" s="20"/>
       <c r="D489" s="20"/>
@@ -5138,7 +5279,7 @@
       <c r="I489" s="20"/>
       <c r="K489" s="20"/>
     </row>
-    <row r="490" spans="2:11" ht="13">
+    <row r="490" spans="2:11" ht="12.5">
       <c r="B490" s="20"/>
       <c r="C490" s="20"/>
       <c r="D490" s="20"/>
@@ -5149,7 +5290,7 @@
       <c r="I490" s="20"/>
       <c r="K490" s="20"/>
     </row>
-    <row r="491" spans="2:11" ht="13">
+    <row r="491" spans="2:11" ht="12.5">
       <c r="B491" s="20"/>
       <c r="C491" s="20"/>
       <c r="D491" s="20"/>
@@ -5160,7 +5301,7 @@
       <c r="I491" s="20"/>
       <c r="K491" s="20"/>
     </row>
-    <row r="492" spans="2:11" ht="13">
+    <row r="492" spans="2:11" ht="12.5">
       <c r="B492" s="20"/>
       <c r="C492" s="20"/>
       <c r="D492" s="20"/>
@@ -5171,7 +5312,7 @@
       <c r="I492" s="20"/>
       <c r="K492" s="20"/>
     </row>
-    <row r="493" spans="2:11" ht="13">
+    <row r="493" spans="2:11" ht="12.5">
       <c r="B493" s="20"/>
       <c r="C493" s="20"/>
       <c r="D493" s="20"/>
@@ -5182,7 +5323,7 @@
       <c r="I493" s="20"/>
       <c r="K493" s="20"/>
     </row>
-    <row r="494" spans="2:11" ht="13">
+    <row r="494" spans="2:11" ht="12.5">
       <c r="B494" s="20"/>
       <c r="C494" s="20"/>
       <c r="D494" s="20"/>
@@ -5193,7 +5334,7 @@
       <c r="I494" s="20"/>
       <c r="K494" s="20"/>
     </row>
-    <row r="495" spans="2:11" ht="13">
+    <row r="495" spans="2:11" ht="12.5">
       <c r="B495" s="20"/>
       <c r="C495" s="20"/>
       <c r="D495" s="20"/>
@@ -5204,7 +5345,7 @@
       <c r="I495" s="20"/>
       <c r="K495" s="20"/>
     </row>
-    <row r="496" spans="2:11" ht="13">
+    <row r="496" spans="2:11" ht="12.5">
       <c r="B496" s="20"/>
       <c r="C496" s="20"/>
       <c r="D496" s="20"/>
@@ -5215,7 +5356,7 @@
       <c r="I496" s="20"/>
       <c r="K496" s="20"/>
     </row>
-    <row r="497" spans="2:11" ht="13">
+    <row r="497" spans="2:11" ht="12.5">
       <c r="B497" s="20"/>
       <c r="C497" s="20"/>
       <c r="D497" s="20"/>
@@ -5226,7 +5367,7 @@
       <c r="I497" s="20"/>
       <c r="K497" s="20"/>
     </row>
-    <row r="498" spans="2:11" ht="13">
+    <row r="498" spans="2:11" ht="12.5">
       <c r="B498" s="20"/>
       <c r="C498" s="20"/>
       <c r="D498" s="20"/>
@@ -5237,7 +5378,7 @@
       <c r="I498" s="20"/>
       <c r="K498" s="20"/>
     </row>
-    <row r="499" spans="2:11" ht="13">
+    <row r="499" spans="2:11" ht="12.5">
       <c r="B499" s="20"/>
       <c r="C499" s="20"/>
       <c r="D499" s="20"/>
@@ -5248,7 +5389,7 @@
       <c r="I499" s="20"/>
       <c r="K499" s="20"/>
     </row>
-    <row r="500" spans="2:11" ht="13">
+    <row r="500" spans="2:11" ht="12.5">
       <c r="B500" s="20"/>
       <c r="C500" s="20"/>
       <c r="D500" s="20"/>
@@ -5259,7 +5400,7 @@
       <c r="I500" s="20"/>
       <c r="K500" s="20"/>
     </row>
-    <row r="501" spans="2:11" ht="13">
+    <row r="501" spans="2:11" ht="12.5">
       <c r="B501" s="20"/>
       <c r="C501" s="20"/>
       <c r="D501" s="20"/>
@@ -5270,7 +5411,7 @@
       <c r="I501" s="20"/>
       <c r="K501" s="20"/>
     </row>
-    <row r="502" spans="2:11" ht="13">
+    <row r="502" spans="2:11" ht="12.5">
       <c r="B502" s="20"/>
       <c r="C502" s="20"/>
       <c r="D502" s="20"/>
@@ -5281,7 +5422,7 @@
       <c r="I502" s="20"/>
       <c r="K502" s="20"/>
     </row>
-    <row r="503" spans="2:11" ht="13">
+    <row r="503" spans="2:11" ht="12.5">
       <c r="B503" s="20"/>
       <c r="C503" s="20"/>
       <c r="D503" s="20"/>
@@ -5292,7 +5433,7 @@
       <c r="I503" s="20"/>
       <c r="K503" s="20"/>
     </row>
-    <row r="504" spans="2:11" ht="13">
+    <row r="504" spans="2:11" ht="12.5">
       <c r="B504" s="20"/>
       <c r="C504" s="20"/>
       <c r="D504" s="20"/>
@@ -5303,7 +5444,7 @@
       <c r="I504" s="20"/>
       <c r="K504" s="20"/>
     </row>
-    <row r="505" spans="2:11" ht="13">
+    <row r="505" spans="2:11" ht="12.5">
       <c r="B505" s="20"/>
       <c r="C505" s="20"/>
       <c r="D505" s="20"/>
@@ -5314,7 +5455,7 @@
       <c r="I505" s="20"/>
       <c r="K505" s="20"/>
     </row>
-    <row r="506" spans="2:11" ht="13">
+    <row r="506" spans="2:11" ht="12.5">
       <c r="B506" s="20"/>
       <c r="C506" s="20"/>
       <c r="D506" s="20"/>
@@ -5325,7 +5466,7 @@
       <c r="I506" s="20"/>
       <c r="K506" s="20"/>
     </row>
-    <row r="507" spans="2:11" ht="13">
+    <row r="507" spans="2:11" ht="12.5">
       <c r="B507" s="20"/>
       <c r="C507" s="20"/>
       <c r="D507" s="20"/>
@@ -5336,7 +5477,7 @@
       <c r="I507" s="20"/>
       <c r="K507" s="20"/>
     </row>
-    <row r="508" spans="2:11" ht="13">
+    <row r="508" spans="2:11" ht="12.5">
       <c r="B508" s="20"/>
       <c r="C508" s="20"/>
       <c r="D508" s="20"/>
@@ -5347,7 +5488,7 @@
       <c r="I508" s="20"/>
       <c r="K508" s="20"/>
     </row>
-    <row r="509" spans="2:11" ht="13">
+    <row r="509" spans="2:11" ht="12.5">
       <c r="B509" s="20"/>
       <c r="C509" s="20"/>
       <c r="D509" s="20"/>
@@ -5358,7 +5499,7 @@
       <c r="I509" s="20"/>
       <c r="K509" s="20"/>
     </row>
-    <row r="510" spans="2:11" ht="13">
+    <row r="510" spans="2:11" ht="12.5">
       <c r="B510" s="20"/>
       <c r="C510" s="20"/>
       <c r="D510" s="20"/>
@@ -5369,7 +5510,7 @@
       <c r="I510" s="20"/>
       <c r="K510" s="20"/>
     </row>
-    <row r="511" spans="2:11" ht="13">
+    <row r="511" spans="2:11" ht="12.5">
       <c r="B511" s="20"/>
       <c r="C511" s="20"/>
       <c r="D511" s="20"/>
@@ -5380,7 +5521,7 @@
       <c r="I511" s="20"/>
       <c r="K511" s="20"/>
     </row>
-    <row r="512" spans="2:11" ht="13">
+    <row r="512" spans="2:11" ht="12.5">
       <c r="B512" s="20"/>
       <c r="C512" s="20"/>
       <c r="D512" s="20"/>
@@ -5391,7 +5532,7 @@
       <c r="I512" s="20"/>
       <c r="K512" s="20"/>
     </row>
-    <row r="513" spans="2:11" ht="13">
+    <row r="513" spans="2:11" ht="12.5">
       <c r="B513" s="20"/>
       <c r="C513" s="20"/>
       <c r="D513" s="20"/>
@@ -5402,7 +5543,7 @@
       <c r="I513" s="20"/>
       <c r="K513" s="20"/>
     </row>
-    <row r="514" spans="2:11" ht="13">
+    <row r="514" spans="2:11" ht="12.5">
       <c r="B514" s="20"/>
       <c r="C514" s="20"/>
       <c r="D514" s="20"/>
@@ -5413,7 +5554,7 @@
       <c r="I514" s="20"/>
       <c r="K514" s="20"/>
     </row>
-    <row r="515" spans="2:11" ht="13">
+    <row r="515" spans="2:11" ht="12.5">
       <c r="B515" s="20"/>
       <c r="C515" s="20"/>
       <c r="D515" s="20"/>
@@ -5424,7 +5565,7 @@
       <c r="I515" s="20"/>
       <c r="K515" s="20"/>
     </row>
-    <row r="516" spans="2:11" ht="13">
+    <row r="516" spans="2:11" ht="12.5">
       <c r="B516" s="20"/>
       <c r="C516" s="20"/>
       <c r="D516" s="20"/>
@@ -5435,7 +5576,7 @@
       <c r="I516" s="20"/>
       <c r="K516" s="20"/>
     </row>
-    <row r="517" spans="2:11" ht="13">
+    <row r="517" spans="2:11" ht="12.5">
       <c r="B517" s="20"/>
       <c r="C517" s="20"/>
       <c r="D517" s="20"/>
@@ -5446,7 +5587,7 @@
       <c r="I517" s="20"/>
       <c r="K517" s="20"/>
     </row>
-    <row r="518" spans="2:11" ht="13">
+    <row r="518" spans="2:11" ht="12.5">
       <c r="B518" s="20"/>
       <c r="C518" s="20"/>
       <c r="D518" s="20"/>
@@ -5457,7 +5598,7 @@
       <c r="I518" s="20"/>
       <c r="K518" s="20"/>
     </row>
-    <row r="519" spans="2:11" ht="13">
+    <row r="519" spans="2:11" ht="12.5">
       <c r="B519" s="20"/>
       <c r="C519" s="20"/>
       <c r="D519" s="20"/>
@@ -5468,7 +5609,7 @@
       <c r="I519" s="20"/>
       <c r="K519" s="20"/>
     </row>
-    <row r="520" spans="2:11" ht="13">
+    <row r="520" spans="2:11" ht="12.5">
       <c r="B520" s="20"/>
       <c r="C520" s="20"/>
       <c r="D520" s="20"/>
@@ -5479,7 +5620,7 @@
       <c r="I520" s="20"/>
       <c r="K520" s="20"/>
     </row>
-    <row r="521" spans="2:11" ht="13">
+    <row r="521" spans="2:11" ht="12.5">
       <c r="B521" s="20"/>
       <c r="C521" s="20"/>
       <c r="D521" s="20"/>
@@ -5490,7 +5631,7 @@
       <c r="I521" s="20"/>
       <c r="K521" s="20"/>
     </row>
-    <row r="522" spans="2:11" ht="13">
+    <row r="522" spans="2:11" ht="12.5">
       <c r="B522" s="20"/>
       <c r="C522" s="20"/>
       <c r="D522" s="20"/>
@@ -5501,7 +5642,7 @@
       <c r="I522" s="20"/>
       <c r="K522" s="20"/>
     </row>
-    <row r="523" spans="2:11" ht="13">
+    <row r="523" spans="2:11" ht="12.5">
       <c r="B523" s="20"/>
       <c r="C523" s="20"/>
       <c r="D523" s="20"/>
@@ -5512,7 +5653,7 @@
       <c r="I523" s="20"/>
       <c r="K523" s="20"/>
     </row>
-    <row r="524" spans="2:11" ht="13">
+    <row r="524" spans="2:11" ht="12.5">
       <c r="B524" s="20"/>
       <c r="C524" s="20"/>
       <c r="D524" s="20"/>
@@ -5523,7 +5664,7 @@
       <c r="I524" s="20"/>
       <c r="K524" s="20"/>
     </row>
-    <row r="525" spans="2:11" ht="13">
+    <row r="525" spans="2:11" ht="12.5">
       <c r="B525" s="20"/>
       <c r="C525" s="20"/>
       <c r="D525" s="20"/>
@@ -5534,7 +5675,7 @@
       <c r="I525" s="20"/>
       <c r="K525" s="20"/>
     </row>
-    <row r="526" spans="2:11" ht="13">
+    <row r="526" spans="2:11" ht="12.5">
       <c r="B526" s="20"/>
       <c r="C526" s="20"/>
       <c r="D526" s="20"/>
@@ -5545,7 +5686,7 @@
       <c r="I526" s="20"/>
       <c r="K526" s="20"/>
     </row>
-    <row r="527" spans="2:11" ht="13">
+    <row r="527" spans="2:11" ht="12.5">
       <c r="B527" s="20"/>
       <c r="C527" s="20"/>
       <c r="D527" s="20"/>
@@ -5556,7 +5697,7 @@
       <c r="I527" s="20"/>
       <c r="K527" s="20"/>
     </row>
-    <row r="528" spans="2:11" ht="13">
+    <row r="528" spans="2:11" ht="12.5">
       <c r="B528" s="20"/>
       <c r="C528" s="20"/>
       <c r="D528" s="20"/>
@@ -5567,7 +5708,7 @@
       <c r="I528" s="20"/>
       <c r="K528" s="20"/>
     </row>
-    <row r="529" spans="2:11" ht="13">
+    <row r="529" spans="2:11" ht="12.5">
       <c r="B529" s="20"/>
       <c r="C529" s="20"/>
       <c r="D529" s="20"/>
@@ -5578,7 +5719,7 @@
       <c r="I529" s="20"/>
       <c r="K529" s="20"/>
     </row>
-    <row r="530" spans="2:11" ht="13">
+    <row r="530" spans="2:11" ht="12.5">
       <c r="B530" s="20"/>
       <c r="C530" s="20"/>
       <c r="D530" s="20"/>
@@ -5589,7 +5730,7 @@
       <c r="I530" s="20"/>
       <c r="K530" s="20"/>
     </row>
-    <row r="531" spans="2:11" ht="13">
+    <row r="531" spans="2:11" ht="12.5">
       <c r="B531" s="20"/>
       <c r="C531" s="20"/>
       <c r="D531" s="20"/>
@@ -5600,7 +5741,7 @@
       <c r="I531" s="20"/>
       <c r="K531" s="20"/>
     </row>
-    <row r="532" spans="2:11" ht="13">
+    <row r="532" spans="2:11" ht="12.5">
       <c r="B532" s="20"/>
       <c r="C532" s="20"/>
       <c r="D532" s="20"/>
@@ -5611,7 +5752,7 @@
       <c r="I532" s="20"/>
       <c r="K532" s="20"/>
     </row>
-    <row r="533" spans="2:11" ht="13">
+    <row r="533" spans="2:11" ht="12.5">
       <c r="B533" s="20"/>
       <c r="C533" s="20"/>
       <c r="D533" s="20"/>
@@ -5622,7 +5763,7 @@
       <c r="I533" s="20"/>
       <c r="K533" s="20"/>
     </row>
-    <row r="534" spans="2:11" ht="13">
+    <row r="534" spans="2:11" ht="12.5">
       <c r="B534" s="20"/>
       <c r="C534" s="20"/>
       <c r="D534" s="20"/>
@@ -5633,7 +5774,7 @@
       <c r="I534" s="20"/>
       <c r="K534" s="20"/>
     </row>
-    <row r="535" spans="2:11" ht="13">
+    <row r="535" spans="2:11" ht="12.5">
       <c r="B535" s="20"/>
       <c r="C535" s="20"/>
       <c r="D535" s="20"/>
@@ -5644,7 +5785,7 @@
       <c r="I535" s="20"/>
       <c r="K535" s="20"/>
     </row>
-    <row r="536" spans="2:11" ht="13">
+    <row r="536" spans="2:11" ht="12.5">
       <c r="B536" s="20"/>
       <c r="C536" s="20"/>
       <c r="D536" s="20"/>
@@ -5655,7 +5796,7 @@
       <c r="I536" s="20"/>
       <c r="K536" s="20"/>
     </row>
-    <row r="537" spans="2:11" ht="13">
+    <row r="537" spans="2:11" ht="12.5">
       <c r="B537" s="20"/>
       <c r="C537" s="20"/>
       <c r="D537" s="20"/>
@@ -5666,7 +5807,7 @@
       <c r="I537" s="20"/>
       <c r="K537" s="20"/>
     </row>
-    <row r="538" spans="2:11" ht="13">
+    <row r="538" spans="2:11" ht="12.5">
       <c r="B538" s="20"/>
       <c r="C538" s="20"/>
       <c r="D538" s="20"/>
@@ -5677,7 +5818,7 @@
       <c r="I538" s="20"/>
       <c r="K538" s="20"/>
     </row>
-    <row r="539" spans="2:11" ht="13">
+    <row r="539" spans="2:11" ht="12.5">
       <c r="B539" s="20"/>
       <c r="C539" s="20"/>
       <c r="D539" s="20"/>
@@ -5688,7 +5829,7 @@
       <c r="I539" s="20"/>
       <c r="K539" s="20"/>
     </row>
-    <row r="540" spans="2:11" ht="13">
+    <row r="540" spans="2:11" ht="12.5">
       <c r="B540" s="20"/>
       <c r="C540" s="20"/>
       <c r="D540" s="20"/>
@@ -5699,7 +5840,7 @@
       <c r="I540" s="20"/>
       <c r="K540" s="20"/>
     </row>
-    <row r="541" spans="2:11" ht="13">
+    <row r="541" spans="2:11" ht="12.5">
       <c r="B541" s="20"/>
       <c r="C541" s="20"/>
       <c r="D541" s="20"/>
@@ -5710,7 +5851,7 @@
       <c r="I541" s="20"/>
       <c r="K541" s="20"/>
     </row>
-    <row r="542" spans="2:11" ht="13">
+    <row r="542" spans="2:11" ht="12.5">
       <c r="B542" s="20"/>
       <c r="C542" s="20"/>
       <c r="D542" s="20"/>
@@ -5721,7 +5862,7 @@
       <c r="I542" s="20"/>
       <c r="K542" s="20"/>
     </row>
-    <row r="543" spans="2:11" ht="13">
+    <row r="543" spans="2:11" ht="12.5">
       <c r="B543" s="20"/>
       <c r="C543" s="20"/>
       <c r="D543" s="20"/>
@@ -5732,7 +5873,7 @@
       <c r="I543" s="20"/>
       <c r="K543" s="20"/>
     </row>
-    <row r="544" spans="2:11" ht="13">
+    <row r="544" spans="2:11" ht="12.5">
       <c r="B544" s="20"/>
       <c r="C544" s="20"/>
       <c r="D544" s="20"/>
@@ -5743,7 +5884,7 @@
       <c r="I544" s="20"/>
       <c r="K544" s="20"/>
     </row>
-    <row r="545" spans="2:11" ht="13">
+    <row r="545" spans="2:11" ht="12.5">
       <c r="B545" s="20"/>
       <c r="C545" s="20"/>
       <c r="D545" s="20"/>
@@ -5754,7 +5895,7 @@
       <c r="I545" s="20"/>
       <c r="K545" s="20"/>
     </row>
-    <row r="546" spans="2:11" ht="13">
+    <row r="546" spans="2:11" ht="12.5">
       <c r="B546" s="20"/>
       <c r="C546" s="20"/>
       <c r="D546" s="20"/>
@@ -5765,7 +5906,7 @@
       <c r="I546" s="20"/>
       <c r="K546" s="20"/>
     </row>
-    <row r="547" spans="2:11" ht="13">
+    <row r="547" spans="2:11" ht="12.5">
       <c r="B547" s="20"/>
       <c r="C547" s="20"/>
       <c r="D547" s="20"/>
@@ -5776,7 +5917,7 @@
       <c r="I547" s="20"/>
       <c r="K547" s="20"/>
     </row>
-    <row r="548" spans="2:11" ht="13">
+    <row r="548" spans="2:11" ht="12.5">
       <c r="B548" s="20"/>
       <c r="C548" s="20"/>
       <c r="D548" s="20"/>
@@ -5787,7 +5928,7 @@
       <c r="I548" s="20"/>
       <c r="K548" s="20"/>
     </row>
-    <row r="549" spans="2:11" ht="13">
+    <row r="549" spans="2:11" ht="12.5">
       <c r="B549" s="20"/>
       <c r="C549" s="20"/>
       <c r="D549" s="20"/>
@@ -5798,7 +5939,7 @@
       <c r="I549" s="20"/>
       <c r="K549" s="20"/>
     </row>
-    <row r="550" spans="2:11" ht="13">
+    <row r="550" spans="2:11" ht="12.5">
       <c r="B550" s="20"/>
       <c r="C550" s="20"/>
       <c r="D550" s="20"/>
@@ -5809,7 +5950,7 @@
       <c r="I550" s="20"/>
       <c r="K550" s="20"/>
     </row>
-    <row r="551" spans="2:11" ht="13">
+    <row r="551" spans="2:11" ht="12.5">
       <c r="B551" s="20"/>
       <c r="C551" s="20"/>
       <c r="D551" s="20"/>
@@ -5820,7 +5961,7 @@
       <c r="I551" s="20"/>
       <c r="K551" s="20"/>
     </row>
-    <row r="552" spans="2:11" ht="13">
+    <row r="552" spans="2:11" ht="12.5">
       <c r="B552" s="20"/>
       <c r="C552" s="20"/>
       <c r="D552" s="20"/>
@@ -5831,7 +5972,7 @@
       <c r="I552" s="20"/>
       <c r="K552" s="20"/>
     </row>
-    <row r="553" spans="2:11" ht="13">
+    <row r="553" spans="2:11" ht="12.5">
       <c r="B553" s="20"/>
       <c r="C553" s="20"/>
       <c r="D553" s="20"/>
@@ -5842,7 +5983,7 @@
       <c r="I553" s="20"/>
       <c r="K553" s="20"/>
     </row>
-    <row r="554" spans="2:11" ht="13">
+    <row r="554" spans="2:11" ht="12.5">
       <c r="B554" s="20"/>
       <c r="C554" s="20"/>
       <c r="D554" s="20"/>
@@ -5853,7 +5994,7 @@
       <c r="I554" s="20"/>
       <c r="K554" s="20"/>
     </row>
-    <row r="555" spans="2:11" ht="13">
+    <row r="555" spans="2:11" ht="12.5">
       <c r="B555" s="20"/>
       <c r="C555" s="20"/>
       <c r="D555" s="20"/>
@@ -5864,7 +6005,7 @@
       <c r="I555" s="20"/>
       <c r="K555" s="20"/>
     </row>
-    <row r="556" spans="2:11" ht="13">
+    <row r="556" spans="2:11" ht="12.5">
       <c r="B556" s="20"/>
       <c r="C556" s="20"/>
       <c r="D556" s="20"/>
@@ -5875,7 +6016,7 @@
       <c r="I556" s="20"/>
       <c r="K556" s="20"/>
     </row>
-    <row r="557" spans="2:11" ht="13">
+    <row r="557" spans="2:11" ht="12.5">
       <c r="B557" s="20"/>
       <c r="C557" s="20"/>
       <c r="D557" s="20"/>
@@ -5886,7 +6027,7 @@
       <c r="I557" s="20"/>
       <c r="K557" s="20"/>
     </row>
-    <row r="558" spans="2:11" ht="13">
+    <row r="558" spans="2:11" ht="12.5">
       <c r="B558" s="20"/>
       <c r="C558" s="20"/>
       <c r="D558" s="20"/>
@@ -5897,7 +6038,7 @@
       <c r="I558" s="20"/>
       <c r="K558" s="20"/>
     </row>
-    <row r="559" spans="2:11" ht="13">
+    <row r="559" spans="2:11" ht="12.5">
       <c r="B559" s="20"/>
       <c r="C559" s="20"/>
       <c r="D559" s="20"/>
@@ -5908,7 +6049,7 @@
       <c r="I559" s="20"/>
       <c r="K559" s="20"/>
     </row>
-    <row r="560" spans="2:11" ht="13">
+    <row r="560" spans="2:11" ht="12.5">
       <c r="B560" s="20"/>
       <c r="C560" s="20"/>
       <c r="D560" s="20"/>
@@ -5919,7 +6060,7 @@
       <c r="I560" s="20"/>
       <c r="K560" s="20"/>
     </row>
-    <row r="561" spans="2:11" ht="13">
+    <row r="561" spans="2:11" ht="12.5">
       <c r="B561" s="20"/>
       <c r="C561" s="20"/>
       <c r="D561" s="20"/>
@@ -5930,7 +6071,7 @@
       <c r="I561" s="20"/>
       <c r="K561" s="20"/>
     </row>
-    <row r="562" spans="2:11" ht="13">
+    <row r="562" spans="2:11" ht="12.5">
       <c r="B562" s="20"/>
       <c r="C562" s="20"/>
       <c r="D562" s="20"/>
@@ -5941,7 +6082,7 @@
       <c r="I562" s="20"/>
       <c r="K562" s="20"/>
     </row>
-    <row r="563" spans="2:11" ht="13">
+    <row r="563" spans="2:11" ht="12.5">
       <c r="B563" s="20"/>
       <c r="C563" s="20"/>
       <c r="D563" s="20"/>
@@ -5952,7 +6093,7 @@
       <c r="I563" s="20"/>
       <c r="K563" s="20"/>
     </row>
-    <row r="564" spans="2:11" ht="13">
+    <row r="564" spans="2:11" ht="12.5">
       <c r="B564" s="20"/>
       <c r="C564" s="20"/>
       <c r="D564" s="20"/>
@@ -5963,7 +6104,7 @@
       <c r="I564" s="20"/>
       <c r="K564" s="20"/>
     </row>
-    <row r="565" spans="2:11" ht="13">
+    <row r="565" spans="2:11" ht="12.5">
       <c r="B565" s="20"/>
       <c r="C565" s="20"/>
       <c r="D565" s="20"/>
@@ -5974,7 +6115,7 @@
       <c r="I565" s="20"/>
       <c r="K565" s="20"/>
     </row>
-    <row r="566" spans="2:11" ht="13">
+    <row r="566" spans="2:11" ht="12.5">
       <c r="B566" s="20"/>
       <c r="C566" s="20"/>
       <c r="D566" s="20"/>
@@ -5985,7 +6126,7 @@
       <c r="I566" s="20"/>
       <c r="K566" s="20"/>
     </row>
-    <row r="567" spans="2:11" ht="13">
+    <row r="567" spans="2:11" ht="12.5">
       <c r="B567" s="20"/>
       <c r="C567" s="20"/>
       <c r="D567" s="20"/>
@@ -5996,7 +6137,7 @@
       <c r="I567" s="20"/>
       <c r="K567" s="20"/>
     </row>
-    <row r="568" spans="2:11" ht="13">
+    <row r="568" spans="2:11" ht="12.5">
       <c r="B568" s="20"/>
       <c r="C568" s="20"/>
       <c r="D568" s="20"/>
@@ -6007,7 +6148,7 @@
       <c r="I568" s="20"/>
       <c r="K568" s="20"/>
     </row>
-    <row r="569" spans="2:11" ht="13">
+    <row r="569" spans="2:11" ht="12.5">
       <c r="B569" s="20"/>
       <c r="C569" s="20"/>
       <c r="D569" s="20"/>
@@ -6018,7 +6159,7 @@
       <c r="I569" s="20"/>
       <c r="K569" s="20"/>
     </row>
-    <row r="570" spans="2:11" ht="13">
+    <row r="570" spans="2:11" ht="12.5">
       <c r="B570" s="20"/>
       <c r="C570" s="20"/>
       <c r="D570" s="20"/>
@@ -6029,7 +6170,7 @@
       <c r="I570" s="20"/>
       <c r="K570" s="20"/>
     </row>
-    <row r="571" spans="2:11" ht="13">
+    <row r="571" spans="2:11" ht="12.5">
       <c r="B571" s="20"/>
       <c r="C571" s="20"/>
       <c r="D571" s="20"/>
@@ -6040,7 +6181,7 @@
       <c r="I571" s="20"/>
       <c r="K571" s="20"/>
     </row>
-    <row r="572" spans="2:11" ht="13">
+    <row r="572" spans="2:11" ht="12.5">
       <c r="B572" s="20"/>
       <c r="C572" s="20"/>
       <c r="D572" s="20"/>
@@ -6051,7 +6192,7 @@
       <c r="I572" s="20"/>
       <c r="K572" s="20"/>
     </row>
-    <row r="573" spans="2:11" ht="13">
+    <row r="573" spans="2:11" ht="12.5">
       <c r="B573" s="20"/>
       <c r="C573" s="20"/>
       <c r="D573" s="20"/>
@@ -6062,7 +6203,7 @@
       <c r="I573" s="20"/>
       <c r="K573" s="20"/>
     </row>
-    <row r="574" spans="2:11" ht="13">
+    <row r="574" spans="2:11" ht="12.5">
       <c r="B574" s="20"/>
       <c r="C574" s="20"/>
       <c r="D574" s="20"/>
@@ -6073,7 +6214,7 @@
       <c r="I574" s="20"/>
       <c r="K574" s="20"/>
     </row>
-    <row r="575" spans="2:11" ht="13">
+    <row r="575" spans="2:11" ht="12.5">
       <c r="B575" s="20"/>
       <c r="C575" s="20"/>
       <c r="D575" s="20"/>
@@ -6084,7 +6225,7 @@
       <c r="I575" s="20"/>
       <c r="K575" s="20"/>
     </row>
-    <row r="576" spans="2:11" ht="13">
+    <row r="576" spans="2:11" ht="12.5">
       <c r="B576" s="20"/>
       <c r="C576" s="20"/>
       <c r="D576" s="20"/>
@@ -6095,7 +6236,7 @@
       <c r="I576" s="20"/>
       <c r="K576" s="20"/>
     </row>
-    <row r="577" spans="2:11" ht="13">
+    <row r="577" spans="2:11" ht="12.5">
       <c r="B577" s="20"/>
       <c r="C577" s="20"/>
       <c r="D577" s="20"/>
@@ -6106,7 +6247,7 @@
       <c r="I577" s="20"/>
       <c r="K577" s="20"/>
     </row>
-    <row r="578" spans="2:11" ht="13">
+    <row r="578" spans="2:11" ht="12.5">
       <c r="B578" s="20"/>
       <c r="C578" s="20"/>
       <c r="D578" s="20"/>
@@ -6117,7 +6258,7 @@
       <c r="I578" s="20"/>
       <c r="K578" s="20"/>
     </row>
-    <row r="579" spans="2:11" ht="13">
+    <row r="579" spans="2:11" ht="12.5">
       <c r="B579" s="20"/>
       <c r="C579" s="20"/>
       <c r="D579" s="20"/>
@@ -6128,7 +6269,7 @@
       <c r="I579" s="20"/>
       <c r="K579" s="20"/>
     </row>
-    <row r="580" spans="2:11" ht="13">
+    <row r="580" spans="2:11" ht="12.5">
       <c r="B580" s="20"/>
       <c r="C580" s="20"/>
       <c r="D580" s="20"/>
@@ -6139,7 +6280,7 @@
       <c r="I580" s="20"/>
       <c r="K580" s="20"/>
     </row>
-    <row r="581" spans="2:11" ht="13">
+    <row r="581" spans="2:11" ht="12.5">
       <c r="B581" s="20"/>
       <c r="C581" s="20"/>
       <c r="D581" s="20"/>
@@ -6150,7 +6291,7 @@
       <c r="I581" s="20"/>
       <c r="K581" s="20"/>
     </row>
-    <row r="582" spans="2:11" ht="13">
+    <row r="582" spans="2:11" ht="12.5">
       <c r="B582" s="20"/>
       <c r="C582" s="20"/>
       <c r="D582" s="20"/>
@@ -6161,7 +6302,7 @@
       <c r="I582" s="20"/>
       <c r="K582" s="20"/>
     </row>
-    <row r="583" spans="2:11" ht="13">
+    <row r="583" spans="2:11" ht="12.5">
       <c r="B583" s="20"/>
       <c r="C583" s="20"/>
       <c r="D583" s="20"/>
@@ -6172,7 +6313,7 @@
       <c r="I583" s="20"/>
       <c r="K583" s="20"/>
     </row>
-    <row r="584" spans="2:11" ht="13">
+    <row r="584" spans="2:11" ht="12.5">
       <c r="B584" s="20"/>
       <c r="C584" s="20"/>
       <c r="D584" s="20"/>
@@ -6183,7 +6324,7 @@
       <c r="I584" s="20"/>
       <c r="K584" s="20"/>
     </row>
-    <row r="585" spans="2:11" ht="13">
+    <row r="585" spans="2:11" ht="12.5">
       <c r="B585" s="20"/>
       <c r="C585" s="20"/>
       <c r="D585" s="20"/>
@@ -6194,7 +6335,7 @@
       <c r="I585" s="20"/>
       <c r="K585" s="20"/>
     </row>
-    <row r="586" spans="2:11" ht="13">
+    <row r="586" spans="2:11" ht="12.5">
       <c r="B586" s="20"/>
       <c r="C586" s="20"/>
       <c r="D586" s="20"/>
@@ -6205,7 +6346,7 @@
       <c r="I586" s="20"/>
       <c r="K586" s="20"/>
     </row>
-    <row r="587" spans="2:11" ht="13">
+    <row r="587" spans="2:11" ht="12.5">
       <c r="B587" s="20"/>
       <c r="C587" s="20"/>
       <c r="D587" s="20"/>
@@ -6216,7 +6357,7 @@
       <c r="I587" s="20"/>
       <c r="K587" s="20"/>
     </row>
-    <row r="588" spans="2:11" ht="13">
+    <row r="588" spans="2:11" ht="12.5">
       <c r="B588" s="20"/>
       <c r="C588" s="20"/>
       <c r="D588" s="20"/>
@@ -6227,7 +6368,7 @@
       <c r="I588" s="20"/>
       <c r="K588" s="20"/>
     </row>
-    <row r="589" spans="2:11" ht="13">
+    <row r="589" spans="2:11" ht="12.5">
       <c r="B589" s="20"/>
       <c r="C589" s="20"/>
       <c r="D589" s="20"/>
@@ -6238,7 +6379,7 @@
       <c r="I589" s="20"/>
       <c r="K589" s="20"/>
     </row>
-    <row r="590" spans="2:11" ht="13">
+    <row r="590" spans="2:11" ht="12.5">
       <c r="B590" s="20"/>
       <c r="C590" s="20"/>
       <c r="D590" s="20"/>
@@ -6249,7 +6390,7 @@
       <c r="I590" s="20"/>
       <c r="K590" s="20"/>
     </row>
-    <row r="591" spans="2:11" ht="13">
+    <row r="591" spans="2:11" ht="12.5">
       <c r="B591" s="20"/>
       <c r="C591" s="20"/>
       <c r="D591" s="20"/>
@@ -6260,7 +6401,7 @@
       <c r="I591" s="20"/>
       <c r="K591" s="20"/>
     </row>
-    <row r="592" spans="2:11" ht="13">
+    <row r="592" spans="2:11" ht="12.5">
       <c r="B592" s="20"/>
       <c r="C592" s="20"/>
       <c r="D592" s="20"/>
@@ -6271,7 +6412,7 @@
       <c r="I592" s="20"/>
       <c r="K592" s="20"/>
     </row>
-    <row r="593" spans="2:11" ht="13">
+    <row r="593" spans="2:11" ht="12.5">
       <c r="B593" s="20"/>
       <c r="C593" s="20"/>
       <c r="D593" s="20"/>
@@ -6282,7 +6423,7 @@
       <c r="I593" s="20"/>
       <c r="K593" s="20"/>
     </row>
-    <row r="594" spans="2:11" ht="13">
+    <row r="594" spans="2:11" ht="12.5">
       <c r="B594" s="20"/>
       <c r="C594" s="20"/>
       <c r="D594" s="20"/>
@@ -6293,7 +6434,7 @@
       <c r="I594" s="20"/>
       <c r="K594" s="20"/>
     </row>
-    <row r="595" spans="2:11" ht="13">
+    <row r="595" spans="2:11" ht="12.5">
       <c r="B595" s="20"/>
       <c r="C595" s="20"/>
       <c r="D595" s="20"/>
@@ -6304,7 +6445,7 @@
       <c r="I595" s="20"/>
       <c r="K595" s="20"/>
     </row>
-    <row r="596" spans="2:11" ht="13">
+    <row r="596" spans="2:11" ht="12.5">
       <c r="B596" s="20"/>
       <c r="C596" s="20"/>
       <c r="D596" s="20"/>
@@ -6315,7 +6456,7 @@
       <c r="I596" s="20"/>
       <c r="K596" s="20"/>
     </row>
-    <row r="597" spans="2:11" ht="13">
+    <row r="597" spans="2:11" ht="12.5">
       <c r="B597" s="20"/>
       <c r="C597" s="20"/>
       <c r="D597" s="20"/>
@@ -6326,7 +6467,7 @@
       <c r="I597" s="20"/>
       <c r="K597" s="20"/>
     </row>
-    <row r="598" spans="2:11" ht="13">
+    <row r="598" spans="2:11" ht="12.5">
       <c r="B598" s="20"/>
       <c r="C598" s="20"/>
       <c r="D598" s="20"/>
@@ -6337,7 +6478,7 @@
       <c r="I598" s="20"/>
       <c r="K598" s="20"/>
     </row>
-    <row r="599" spans="2:11" ht="13">
+    <row r="599" spans="2:11" ht="12.5">
       <c r="B599" s="20"/>
       <c r="C599" s="20"/>
       <c r="D599" s="20"/>
@@ -6348,7 +6489,7 @@
       <c r="I599" s="20"/>
       <c r="K599" s="20"/>
     </row>
-    <row r="600" spans="2:11" ht="13">
+    <row r="600" spans="2:11" ht="12.5">
       <c r="B600" s="20"/>
       <c r="C600" s="20"/>
       <c r="D600" s="20"/>
@@ -6359,7 +6500,7 @@
       <c r="I600" s="20"/>
       <c r="K600" s="20"/>
     </row>
-    <row r="601" spans="2:11" ht="13">
+    <row r="601" spans="2:11" ht="12.5">
       <c r="B601" s="20"/>
       <c r="C601" s="20"/>
       <c r="D601" s="20"/>
@@ -6370,7 +6511,7 @@
       <c r="I601" s="20"/>
       <c r="K601" s="20"/>
     </row>
-    <row r="602" spans="2:11" ht="13">
+    <row r="602" spans="2:11" ht="12.5">
       <c r="B602" s="20"/>
       <c r="C602" s="20"/>
       <c r="D602" s="20"/>
@@ -6381,7 +6522,7 @@
       <c r="I602" s="20"/>
       <c r="K602" s="20"/>
     </row>
-    <row r="603" spans="2:11" ht="13">
+    <row r="603" spans="2:11" ht="12.5">
       <c r="B603" s="20"/>
       <c r="C603" s="20"/>
       <c r="D603" s="20"/>
@@ -6392,7 +6533,7 @@
       <c r="I603" s="20"/>
       <c r="K603" s="20"/>
     </row>
-    <row r="604" spans="2:11" ht="13">
+    <row r="604" spans="2:11" ht="12.5">
       <c r="B604" s="20"/>
       <c r="C604" s="20"/>
       <c r="D604" s="20"/>
@@ -6403,7 +6544,7 @@
       <c r="I604" s="20"/>
       <c r="K604" s="20"/>
     </row>
-    <row r="605" spans="2:11" ht="13">
+    <row r="605" spans="2:11" ht="12.5">
       <c r="B605" s="20"/>
       <c r="C605" s="20"/>
       <c r="D605" s="20"/>
@@ -6414,7 +6555,7 @@
       <c r="I605" s="20"/>
       <c r="K605" s="20"/>
     </row>
-    <row r="606" spans="2:11" ht="13">
+    <row r="606" spans="2:11" ht="12.5">
       <c r="B606" s="20"/>
       <c r="C606" s="20"/>
       <c r="D606" s="20"/>
@@ -6425,7 +6566,7 @@
       <c r="I606" s="20"/>
       <c r="K606" s="20"/>
     </row>
-    <row r="607" spans="2:11" ht="13">
+    <row r="607" spans="2:11" ht="12.5">
       <c r="B607" s="20"/>
       <c r="C607" s="20"/>
       <c r="D607" s="20"/>
@@ -6436,7 +6577,7 @@
       <c r="I607" s="20"/>
       <c r="K607" s="20"/>
     </row>
-    <row r="608" spans="2:11" ht="13">
+    <row r="608" spans="2:11" ht="12.5">
       <c r="B608" s="20"/>
       <c r="C608" s="20"/>
       <c r="D608" s="20"/>
@@ -6447,7 +6588,7 @@
       <c r="I608" s="20"/>
       <c r="K608" s="20"/>
     </row>
-    <row r="609" spans="2:11" ht="13">
+    <row r="609" spans="2:11" ht="12.5">
       <c r="B609" s="20"/>
       <c r="C609" s="20"/>
       <c r="D609" s="20"/>
@@ -6458,7 +6599,7 @@
       <c r="I609" s="20"/>
       <c r="K609" s="20"/>
     </row>
-    <row r="610" spans="2:11" ht="13">
+    <row r="610" spans="2:11" ht="12.5">
       <c r="B610" s="20"/>
       <c r="C610" s="20"/>
       <c r="D610" s="20"/>
@@ -6469,7 +6610,7 @@
       <c r="I610" s="20"/>
       <c r="K610" s="20"/>
     </row>
-    <row r="611" spans="2:11" ht="13">
+    <row r="611" spans="2:11" ht="12.5">
       <c r="B611" s="20"/>
       <c r="C611" s="20"/>
       <c r="D611" s="20"/>
@@ -6480,7 +6621,7 @@
       <c r="I611" s="20"/>
       <c r="K611" s="20"/>
     </row>
-    <row r="612" spans="2:11" ht="13">
+    <row r="612" spans="2:11" ht="12.5">
       <c r="B612" s="20"/>
       <c r="C612" s="20"/>
       <c r="D612" s="20"/>
@@ -6491,7 +6632,7 @@
       <c r="I612" s="20"/>
       <c r="K612" s="20"/>
     </row>
-    <row r="613" spans="2:11" ht="13">
+    <row r="613" spans="2:11" ht="12.5">
       <c r="B613" s="20"/>
       <c r="C613" s="20"/>
       <c r="D613" s="20"/>
@@ -6502,7 +6643,7 @@
       <c r="I613" s="20"/>
       <c r="K613" s="20"/>
     </row>
-    <row r="614" spans="2:11" ht="13">
+    <row r="614" spans="2:11" ht="12.5">
       <c r="B614" s="20"/>
       <c r="C614" s="20"/>
       <c r="D614" s="20"/>
@@ -6513,7 +6654,7 @@
       <c r="I614" s="20"/>
       <c r="K614" s="20"/>
     </row>
-    <row r="615" spans="2:11" ht="13">
+    <row r="615" spans="2:11" ht="12.5">
       <c r="B615" s="20"/>
       <c r="C615" s="20"/>
       <c r="D615" s="20"/>
@@ -6524,7 +6665,7 @@
       <c r="I615" s="20"/>
       <c r="K615" s="20"/>
     </row>
-    <row r="616" spans="2:11" ht="13">
+    <row r="616" spans="2:11" ht="12.5">
       <c r="B616" s="20"/>
       <c r="C616" s="20"/>
       <c r="D616" s="20"/>
@@ -6535,7 +6676,7 @@
       <c r="I616" s="20"/>
       <c r="K616" s="20"/>
     </row>
-    <row r="617" spans="2:11" ht="13">
+    <row r="617" spans="2:11" ht="12.5">
       <c r="B617" s="20"/>
       <c r="C617" s="20"/>
       <c r="D617" s="20"/>
@@ -6546,7 +6687,7 @@
       <c r="I617" s="20"/>
       <c r="K617" s="20"/>
     </row>
-    <row r="618" spans="2:11" ht="13">
+    <row r="618" spans="2:11" ht="12.5">
       <c r="B618" s="20"/>
       <c r="C618" s="20"/>
       <c r="D618" s="20"/>
@@ -6557,7 +6698,7 @@
       <c r="I618" s="20"/>
       <c r="K618" s="20"/>
     </row>
-    <row r="619" spans="2:11" ht="13">
+    <row r="619" spans="2:11" ht="12.5">
       <c r="B619" s="20"/>
       <c r="C619" s="20"/>
       <c r="D619" s="20"/>
@@ -6568,7 +6709,7 @@
       <c r="I619" s="20"/>
       <c r="K619" s="20"/>
     </row>
-    <row r="620" spans="2:11" ht="13">
+    <row r="620" spans="2:11" ht="12.5">
       <c r="B620" s="20"/>
       <c r="C620" s="20"/>
       <c r="D620" s="20"/>
@@ -6579,7 +6720,7 @@
       <c r="I620" s="20"/>
       <c r="K620" s="20"/>
     </row>
-    <row r="621" spans="2:11" ht="13">
+    <row r="621" spans="2:11" ht="12.5">
       <c r="B621" s="20"/>
       <c r="C621" s="20"/>
       <c r="D621" s="20"/>
@@ -6590,7 +6731,7 @@
       <c r="I621" s="20"/>
       <c r="K621" s="20"/>
     </row>
-    <row r="622" spans="2:11" ht="13">
+    <row r="622" spans="2:11" ht="12.5">
       <c r="B622" s="20"/>
       <c r="C622" s="20"/>
       <c r="D622" s="20"/>
@@ -6601,7 +6742,7 @@
       <c r="I622" s="20"/>
       <c r="K622" s="20"/>
     </row>
-    <row r="623" spans="2:11" ht="13">
+    <row r="623" spans="2:11" ht="12.5">
       <c r="B623" s="20"/>
       <c r="C623" s="20"/>
       <c r="D623" s="20"/>
@@ -6612,7 +6753,7 @@
       <c r="I623" s="20"/>
       <c r="K623" s="20"/>
     </row>
-    <row r="624" spans="2:11" ht="13">
+    <row r="624" spans="2:11" ht="12.5">
       <c r="B624" s="20"/>
       <c r="C624" s="20"/>
       <c r="D624" s="20"/>
@@ -6623,7 +6764,7 @@
       <c r="I624" s="20"/>
       <c r="K624" s="20"/>
     </row>
-    <row r="625" spans="2:11" ht="13">
+    <row r="625" spans="2:11" ht="12.5">
       <c r="B625" s="20"/>
       <c r="C625" s="20"/>
       <c r="D625" s="20"/>
@@ -6634,7 +6775,7 @@
       <c r="I625" s="20"/>
       <c r="K625" s="20"/>
     </row>
-    <row r="626" spans="2:11" ht="13">
+    <row r="626" spans="2:11" ht="12.5">
       <c r="B626" s="20"/>
       <c r="C626" s="20"/>
       <c r="D626" s="20"/>
@@ -6645,7 +6786,7 @@
       <c r="I626" s="20"/>
       <c r="K626" s="20"/>
     </row>
-    <row r="627" spans="2:11" ht="13">
+    <row r="627" spans="2:11" ht="12.5">
       <c r="B627" s="20"/>
       <c r="C627" s="20"/>
       <c r="D627" s="20"/>
@@ -6656,7 +6797,7 @@
       <c r="I627" s="20"/>
       <c r="K627" s="20"/>
     </row>
-    <row r="628" spans="2:11" ht="13">
+    <row r="628" spans="2:11" ht="12.5">
       <c r="B628" s="20"/>
       <c r="C628" s="20"/>
       <c r="D628" s="20"/>
@@ -6667,7 +6808,7 @@
       <c r="I628" s="20"/>
       <c r="K628" s="20"/>
     </row>
-    <row r="629" spans="2:11" ht="13">
+    <row r="629" spans="2:11" ht="12.5">
       <c r="B629" s="20"/>
       <c r="C629" s="20"/>
       <c r="D629" s="20"/>
@@ -6678,7 +6819,7 @@
       <c r="I629" s="20"/>
       <c r="K629" s="20"/>
     </row>
-    <row r="630" spans="2:11" ht="13">
+    <row r="630" spans="2:11" ht="12.5">
       <c r="B630" s="20"/>
       <c r="C630" s="20"/>
       <c r="D630" s="20"/>
@@ -6689,7 +6830,7 @@
       <c r="I630" s="20"/>
       <c r="K630" s="20"/>
     </row>
-    <row r="631" spans="2:11" ht="13">
+    <row r="631" spans="2:11" ht="12.5">
       <c r="B631" s="20"/>
       <c r="C631" s="20"/>
       <c r="D631" s="20"/>
@@ -6700,7 +6841,7 @@
       <c r="I631" s="20"/>
       <c r="K631" s="20"/>
     </row>
-    <row r="632" spans="2:11" ht="13">
+    <row r="632" spans="2:11" ht="12.5">
       <c r="B632" s="20"/>
       <c r="C632" s="20"/>
       <c r="D632" s="20"/>
@@ -6711,7 +6852,7 @@
       <c r="I632" s="20"/>
       <c r="K632" s="20"/>
     </row>
-    <row r="633" spans="2:11" ht="13">
+    <row r="633" spans="2:11" ht="12.5">
       <c r="B633" s="20"/>
       <c r="C633" s="20"/>
       <c r="D633" s="20"/>
@@ -6722,7 +6863,7 @@
       <c r="I633" s="20"/>
       <c r="K633" s="20"/>
     </row>
-    <row r="634" spans="2:11" ht="13">
+    <row r="634" spans="2:11" ht="12.5">
       <c r="B634" s="20"/>
       <c r="C634" s="20"/>
       <c r="D634" s="20"/>
@@ -6733,7 +6874,7 @@
       <c r="I634" s="20"/>
       <c r="K634" s="20"/>
     </row>
-    <row r="635" spans="2:11" ht="13">
+    <row r="635" spans="2:11" ht="12.5">
       <c r="B635" s="20"/>
       <c r="C635" s="20"/>
       <c r="D635" s="20"/>
@@ -6744,7 +6885,7 @@
       <c r="I635" s="20"/>
       <c r="K635" s="20"/>
     </row>
-    <row r="636" spans="2:11" ht="13">
+    <row r="636" spans="2:11" ht="12.5">
       <c r="B636" s="20"/>
       <c r="C636" s="20"/>
       <c r="D636" s="20"/>
@@ -6755,7 +6896,7 @@
       <c r="I636" s="20"/>
       <c r="K636" s="20"/>
     </row>
-    <row r="637" spans="2:11" ht="13">
+    <row r="637" spans="2:11" ht="12.5">
       <c r="B637" s="20"/>
       <c r="C637" s="20"/>
       <c r="D637" s="20"/>
@@ -6766,7 +6907,7 @@
       <c r="I637" s="20"/>
       <c r="K637" s="20"/>
     </row>
-    <row r="638" spans="2:11" ht="13">
+    <row r="638" spans="2:11" ht="12.5">
       <c r="B638" s="20"/>
       <c r="C638" s="20"/>
       <c r="D638" s="20"/>
@@ -6777,7 +6918,7 @@
       <c r="I638" s="20"/>
       <c r="K638" s="20"/>
     </row>
-    <row r="639" spans="2:11" ht="13">
+    <row r="639" spans="2:11" ht="12.5">
       <c r="B639" s="20"/>
       <c r="C639" s="20"/>
       <c r="D639" s="20"/>
@@ -6788,7 +6929,7 @@
       <c r="I639" s="20"/>
       <c r="K639" s="20"/>
     </row>
-    <row r="640" spans="2:11" ht="13">
+    <row r="640" spans="2:11" ht="12.5">
       <c r="B640" s="20"/>
       <c r="C640" s="20"/>
       <c r="D640" s="20"/>
@@ -6799,7 +6940,7 @@
       <c r="I640" s="20"/>
       <c r="K640" s="20"/>
     </row>
-    <row r="641" spans="2:11" ht="13">
+    <row r="641" spans="2:11" ht="12.5">
       <c r="B641" s="20"/>
       <c r="C641" s="20"/>
       <c r="D641" s="20"/>
@@ -6810,7 +6951,7 @@
       <c r="I641" s="20"/>
       <c r="K641" s="20"/>
     </row>
-    <row r="642" spans="2:11" ht="13">
+    <row r="642" spans="2:11" ht="12.5">
       <c r="B642" s="20"/>
       <c r="C642" s="20"/>
       <c r="D642" s="20"/>
@@ -6821,7 +6962,7 @@
       <c r="I642" s="20"/>
       <c r="K642" s="20"/>
     </row>
-    <row r="643" spans="2:11" ht="13">
+    <row r="643" spans="2:11" ht="12.5">
       <c r="B643" s="20"/>
       <c r="C643" s="20"/>
       <c r="D643" s="20"/>
@@ -6832,7 +6973,7 @@
       <c r="I643" s="20"/>
       <c r="K643" s="20"/>
     </row>
-    <row r="644" spans="2:11" ht="13">
+    <row r="644" spans="2:11" ht="12.5">
       <c r="B644" s="20"/>
       <c r="C644" s="20"/>
       <c r="D644" s="20"/>
@@ -6843,7 +6984,7 @@
       <c r="I644" s="20"/>
       <c r="K644" s="20"/>
     </row>
-    <row r="645" spans="2:11" ht="13">
+    <row r="645" spans="2:11" ht="12.5">
       <c r="B645" s="20"/>
       <c r="C645" s="20"/>
       <c r="D645" s="20"/>
@@ -6854,7 +6995,7 @@
       <c r="I645" s="20"/>
       <c r="K645" s="20"/>
     </row>
-    <row r="646" spans="2:11" ht="13">
+    <row r="646" spans="2:11" ht="12.5">
       <c r="B646" s="20"/>
       <c r="C646" s="20"/>
       <c r="D646" s="20"/>
@@ -6865,7 +7006,7 @@
       <c r="I646" s="20"/>
       <c r="K646" s="20"/>
     </row>
-    <row r="647" spans="2:11" ht="13">
+    <row r="647" spans="2:11" ht="12.5">
       <c r="B647" s="20"/>
       <c r="C647" s="20"/>
       <c r="D647" s="20"/>
@@ -6876,7 +7017,7 @@
       <c r="I647" s="20"/>
       <c r="K647" s="20"/>
     </row>
-    <row r="648" spans="2:11" ht="13">
+    <row r="648" spans="2:11" ht="12.5">
       <c r="B648" s="20"/>
       <c r="C648" s="20"/>
       <c r="D648" s="20"/>
@@ -6887,7 +7028,7 @@
       <c r="I648" s="20"/>
       <c r="K648" s="20"/>
     </row>
-    <row r="649" spans="2:11" ht="13">
+    <row r="649" spans="2:11" ht="12.5">
       <c r="B649" s="20"/>
       <c r="C649" s="20"/>
       <c r="D649" s="20"/>
@@ -6898,7 +7039,7 @@
       <c r="I649" s="20"/>
       <c r="K649" s="20"/>
     </row>
-    <row r="650" spans="2:11" ht="13">
+    <row r="650" spans="2:11" ht="12.5">
       <c r="B650" s="20"/>
       <c r="C650" s="20"/>
       <c r="D650" s="20"/>
@@ -6909,7 +7050,7 @@
       <c r="I650" s="20"/>
       <c r="K650" s="20"/>
     </row>
-    <row r="651" spans="2:11" ht="13">
+    <row r="651" spans="2:11" ht="12.5">
       <c r="B651" s="20"/>
       <c r="C651" s="20"/>
       <c r="D651" s="20"/>
@@ -6920,7 +7061,7 @@
       <c r="I651" s="20"/>
       <c r="K651" s="20"/>
     </row>
-    <row r="652" spans="2:11" ht="13">
+    <row r="652" spans="2:11" ht="12.5">
       <c r="B652" s="20"/>
       <c r="C652" s="20"/>
       <c r="D652" s="20"/>
@@ -6931,7 +7072,7 @@
       <c r="I652" s="20"/>
       <c r="K652" s="20"/>
     </row>
-    <row r="653" spans="2:11" ht="13">
+    <row r="653" spans="2:11" ht="12.5">
       <c r="B653" s="20"/>
       <c r="C653" s="20"/>
       <c r="D653" s="20"/>
@@ -6942,7 +7083,7 @@
       <c r="I653" s="20"/>
       <c r="K653" s="20"/>
     </row>
-    <row r="654" spans="2:11" ht="13">
+    <row r="654" spans="2:11" ht="12.5">
       <c r="B654" s="20"/>
       <c r="C654" s="20"/>
       <c r="D654" s="20"/>
@@ -6953,7 +7094,7 @@
       <c r="I654" s="20"/>
       <c r="K654" s="20"/>
     </row>
-    <row r="655" spans="2:11" ht="13">
+    <row r="655" spans="2:11" ht="12.5">
       <c r="B655" s="20"/>
       <c r="C655" s="20"/>
       <c r="D655" s="20"/>
@@ -6964,7 +7105,7 @@
       <c r="I655" s="20"/>
       <c r="K655" s="20"/>
     </row>
-    <row r="656" spans="2:11" ht="13">
+    <row r="656" spans="2:11" ht="12.5">
       <c r="B656" s="20"/>
       <c r="C656" s="20"/>
       <c r="D656" s="20"/>
@@ -6975,7 +7116,7 @@
       <c r="I656" s="20"/>
       <c r="K656" s="20"/>
     </row>
-    <row r="657" spans="2:11" ht="13">
+    <row r="657" spans="2:11" ht="12.5">
       <c r="B657" s="20"/>
       <c r="C657" s="20"/>
       <c r="D657" s="20"/>
@@ -6986,7 +7127,7 @@
       <c r="I657" s="20"/>
       <c r="K657" s="20"/>
     </row>
-    <row r="658" spans="2:11" ht="13">
+    <row r="658" spans="2:11" ht="12.5">
       <c r="B658" s="20"/>
       <c r="C658" s="20"/>
       <c r="D658" s="20"/>
@@ -6997,7 +7138,7 @@
       <c r="I658" s="20"/>
       <c r="K658" s="20"/>
     </row>
-    <row r="659" spans="2:11" ht="13">
+    <row r="659" spans="2:11" ht="12.5">
       <c r="B659" s="20"/>
       <c r="C659" s="20"/>
       <c r="D659" s="20"/>
@@ -7008,7 +7149,7 @@
       <c r="I659" s="20"/>
       <c r="K659" s="20"/>
     </row>
-    <row r="660" spans="2:11" ht="13">
+    <row r="660" spans="2:11" ht="12.5">
       <c r="B660" s="20"/>
       <c r="C660" s="20"/>
       <c r="D660" s="20"/>
@@ -7019,7 +7160,7 @@
       <c r="I660" s="20"/>
       <c r="K660" s="20"/>
     </row>
-    <row r="661" spans="2:11" ht="13">
+    <row r="661" spans="2:11" ht="12.5">
       <c r="B661" s="20"/>
       <c r="C661" s="20"/>
       <c r="D661" s="20"/>
@@ -7030,7 +7171,7 @@
       <c r="I661" s="20"/>
       <c r="K661" s="20"/>
     </row>
-    <row r="662" spans="2:11" ht="13">
+    <row r="662" spans="2:11" ht="12.5">
       <c r="B662" s="20"/>
       <c r="C662" s="20"/>
       <c r="D662" s="20"/>
@@ -7041,7 +7182,7 @@
       <c r="I662" s="20"/>
       <c r="K662" s="20"/>
     </row>
-    <row r="663" spans="2:11" ht="13">
+    <row r="663" spans="2:11" ht="12.5">
       <c r="B663" s="20"/>
       <c r="C663" s="20"/>
       <c r="D663" s="20"/>
@@ -7052,7 +7193,7 @@
       <c r="I663" s="20"/>
       <c r="K663" s="20"/>
     </row>
-    <row r="664" spans="2:11" ht="13">
+    <row r="664" spans="2:11" ht="12.5">
       <c r="B664" s="20"/>
       <c r="C664" s="20"/>
       <c r="D664" s="20"/>
@@ -7063,7 +7204,7 @@
       <c r="I664" s="20"/>
       <c r="K664" s="20"/>
     </row>
-    <row r="665" spans="2:11" ht="13">
+    <row r="665" spans="2:11" ht="12.5">
       <c r="B665" s="20"/>
       <c r="C665" s="20"/>
       <c r="D665" s="20"/>
@@ -7074,7 +7215,7 @@
       <c r="I665" s="20"/>
       <c r="K665" s="20"/>
     </row>
-    <row r="666" spans="2:11" ht="13">
+    <row r="666" spans="2:11" ht="12.5">
       <c r="B666" s="20"/>
       <c r="C666" s="20"/>
       <c r="D666" s="20"/>
@@ -7085,7 +7226,7 @@
       <c r="I666" s="20"/>
       <c r="K666" s="20"/>
     </row>
-    <row r="667" spans="2:11" ht="13">
+    <row r="667" spans="2:11" ht="12.5">
       <c r="B667" s="20"/>
       <c r="C667" s="20"/>
       <c r="D667" s="20"/>
@@ -7096,7 +7237,7 @@
       <c r="I667" s="20"/>
       <c r="K667" s="20"/>
     </row>
-    <row r="668" spans="2:11" ht="13">
+    <row r="668" spans="2:11" ht="12.5">
       <c r="B668" s="20"/>
       <c r="C668" s="20"/>
       <c r="D668" s="20"/>
@@ -7107,7 +7248,7 @@
       <c r="I668" s="20"/>
       <c r="K668" s="20"/>
     </row>
-    <row r="669" spans="2:11" ht="13">
+    <row r="669" spans="2:11" ht="12.5">
       <c r="B669" s="20"/>
       <c r="C669" s="20"/>
       <c r="D669" s="20"/>
@@ -7118,7 +7259,7 @@
       <c r="I669" s="20"/>
       <c r="K669" s="20"/>
     </row>
-    <row r="670" spans="2:11" ht="13">
+    <row r="670" spans="2:11" ht="12.5">
       <c r="B670" s="20"/>
       <c r="C670" s="20"/>
       <c r="D670" s="20"/>
@@ -7129,7 +7270,7 @@
       <c r="I670" s="20"/>
       <c r="K670" s="20"/>
     </row>
-    <row r="671" spans="2:11" ht="13">
+    <row r="671" spans="2:11" ht="12.5">
       <c r="B671" s="20"/>
       <c r="C671" s="20"/>
       <c r="D671" s="20"/>
@@ -7140,7 +7281,7 @@
       <c r="I671" s="20"/>
       <c r="K671" s="20"/>
     </row>
-    <row r="672" spans="2:11" ht="13">
+    <row r="672" spans="2:11" ht="12.5">
       <c r="B672" s="20"/>
       <c r="C672" s="20"/>
       <c r="D672" s="20"/>
@@ -7151,7 +7292,7 @@
       <c r="I672" s="20"/>
       <c r="K672" s="20"/>
     </row>
-    <row r="673" spans="2:11" ht="13">
+    <row r="673" spans="2:11" ht="12.5">
       <c r="B673" s="20"/>
       <c r="C673" s="20"/>
       <c r="D673" s="20"/>
@@ -7162,7 +7303,7 @@
       <c r="I673" s="20"/>
       <c r="K673" s="20"/>
     </row>
-    <row r="674" spans="2:11" ht="13">
+    <row r="674" spans="2:11" ht="12.5">
       <c r="B674" s="20"/>
       <c r="C674" s="20"/>
       <c r="D674" s="20"/>
@@ -7173,7 +7314,7 @@
       <c r="I674" s="20"/>
       <c r="K674" s="20"/>
     </row>
-    <row r="675" spans="2:11" ht="13">
+    <row r="675" spans="2:11" ht="12.5">
       <c r="B675" s="20"/>
       <c r="C675" s="20"/>
       <c r="D675" s="20"/>
@@ -7184,7 +7325,7 @@
       <c r="I675" s="20"/>
       <c r="K675" s="20"/>
     </row>
-    <row r="676" spans="2:11" ht="13">
+    <row r="676" spans="2:11" ht="12.5">
       <c r="B676" s="20"/>
       <c r="C676" s="20"/>
       <c r="D676" s="20"/>
@@ -7195,7 +7336,7 @@
       <c r="I676" s="20"/>
       <c r="K676" s="20"/>
     </row>
-    <row r="677" spans="2:11" ht="13">
+    <row r="677" spans="2:11" ht="12.5">
       <c r="B677" s="20"/>
       <c r="C677" s="20"/>
       <c r="D677" s="20"/>
@@ -7206,7 +7347,7 @@
       <c r="I677" s="20"/>
       <c r="K677" s="20"/>
     </row>
-    <row r="678" spans="2:11" ht="13">
+    <row r="678" spans="2:11" ht="12.5">
       <c r="B678" s="20"/>
       <c r="C678" s="20"/>
       <c r="D678" s="20"/>
@@ -7217,7 +7358,7 @@
       <c r="I678" s="20"/>
       <c r="K678" s="20"/>
     </row>
-    <row r="679" spans="2:11" ht="13">
+    <row r="679" spans="2:11" ht="12.5">
       <c r="B679" s="20"/>
       <c r="C679" s="20"/>
       <c r="D679" s="20"/>
@@ -7228,7 +7369,7 @@
       <c r="I679" s="20"/>
       <c r="K679" s="20"/>
     </row>
-    <row r="680" spans="2:11" ht="13">
+    <row r="680" spans="2:11" ht="12.5">
       <c r="B680" s="20"/>
       <c r="C680" s="20"/>
       <c r="D680" s="20"/>
@@ -7239,7 +7380,7 @@
       <c r="I680" s="20"/>
       <c r="K680" s="20"/>
     </row>
-    <row r="681" spans="2:11" ht="13">
+    <row r="681" spans="2:11" ht="12.5">
       <c r="B681" s="20"/>
       <c r="C681" s="20"/>
       <c r="D681" s="20"/>
@@ -7250,7 +7391,7 @@
       <c r="I681" s="20"/>
       <c r="K681" s="20"/>
     </row>
-    <row r="682" spans="2:11" ht="13">
+    <row r="682" spans="2:11" ht="12.5">
       <c r="B682" s="20"/>
       <c r="C682" s="20"/>
       <c r="D682" s="20"/>
@@ -7261,7 +7402,7 @@
       <c r="I682" s="20"/>
       <c r="K682" s="20"/>
     </row>
-    <row r="683" spans="2:11" ht="13">
+    <row r="683" spans="2:11" ht="12.5">
       <c r="B683" s="20"/>
       <c r="C683" s="20"/>
       <c r="D683" s="20"/>
@@ -7272,7 +7413,7 @@
       <c r="I683" s="20"/>
       <c r="K683" s="20"/>
     </row>
-    <row r="684" spans="2:11" ht="13">
+    <row r="684" spans="2:11" ht="12.5">
       <c r="B684" s="20"/>
       <c r="C684" s="20"/>
       <c r="D684" s="20"/>
@@ -7283,7 +7424,7 @@
       <c r="I684" s="20"/>
       <c r="K684" s="20"/>
     </row>
-    <row r="685" spans="2:11" ht="13">
+    <row r="685" spans="2:11" ht="12.5">
       <c r="B685" s="20"/>
       <c r="C685" s="20"/>
       <c r="D685" s="20"/>
@@ -7294,7 +7435,7 @@
       <c r="I685" s="20"/>
       <c r="K685" s="20"/>
     </row>
-    <row r="686" spans="2:11" ht="13">
+    <row r="686" spans="2:11" ht="12.5">
       <c r="B686" s="20"/>
       <c r="C686" s="20"/>
       <c r="D686" s="20"/>
@@ -7305,7 +7446,7 @@
       <c r="I686" s="20"/>
       <c r="K686" s="20"/>
     </row>
-    <row r="687" spans="2:11" ht="13">
+    <row r="687" spans="2:11" ht="12.5">
       <c r="B687" s="20"/>
       <c r="C687" s="20"/>
       <c r="D687" s="20"/>
@@ -7316,7 +7457,7 @@
       <c r="I687" s="20"/>
       <c r="K687" s="20"/>
     </row>
-    <row r="688" spans="2:11" ht="13">
+    <row r="688" spans="2:11" ht="12.5">
       <c r="B688" s="20"/>
       <c r="C688" s="20"/>
       <c r="D688" s="20"/>
@@ -7327,7 +7468,7 @@
       <c r="I688" s="20"/>
       <c r="K688" s="20"/>
     </row>
-    <row r="689" spans="2:11" ht="13">
+    <row r="689" spans="2:11" ht="12.5">
       <c r="B689" s="20"/>
       <c r="C689" s="20"/>
       <c r="D689" s="20"/>
@@ -7338,7 +7479,7 @@
       <c r="I689" s="20"/>
       <c r="K689" s="20"/>
     </row>
-    <row r="690" spans="2:11" ht="13">
+    <row r="690" spans="2:11" ht="12.5">
       <c r="B690" s="20"/>
       <c r="C690" s="20"/>
       <c r="D690" s="20"/>
@@ -7349,7 +7490,7 @@
       <c r="I690" s="20"/>
       <c r="K690" s="20"/>
     </row>
-    <row r="691" spans="2:11" ht="13">
+    <row r="691" spans="2:11" ht="12.5">
       <c r="B691" s="20"/>
       <c r="C691" s="20"/>
       <c r="D691" s="20"/>
@@ -7360,7 +7501,7 @@
       <c r="I691" s="20"/>
       <c r="K691" s="20"/>
     </row>
-    <row r="692" spans="2:11" ht="13">
+    <row r="692" spans="2:11" ht="12.5">
       <c r="B692" s="20"/>
       <c r="C692" s="20"/>
       <c r="D692" s="20"/>
@@ -7371,7 +7512,7 @@
       <c r="I692" s="20"/>
       <c r="K692" s="20"/>
     </row>
-    <row r="693" spans="2:11" ht="13">
+    <row r="693" spans="2:11" ht="12.5">
       <c r="B693" s="20"/>
       <c r="C693" s="20"/>
       <c r="D693" s="20"/>
@@ -7382,7 +7523,7 @@
       <c r="I693" s="20"/>
       <c r="K693" s="20"/>
     </row>
-    <row r="694" spans="2:11" ht="13">
+    <row r="694" spans="2:11" ht="12.5">
       <c r="B694" s="20"/>
       <c r="C694" s="20"/>
       <c r="D694" s="20"/>
@@ -7393,7 +7534,7 @@
       <c r="I694" s="20"/>
       <c r="K694" s="20"/>
     </row>
-    <row r="695" spans="2:11" ht="13">
+    <row r="695" spans="2:11" ht="12.5">
       <c r="B695" s="20"/>
       <c r="C695" s="20"/>
       <c r="D695" s="20"/>
@@ -7404,7 +7545,7 @@
       <c r="I695" s="20"/>
       <c r="K695" s="20"/>
     </row>
-    <row r="696" spans="2:11" ht="13">
+    <row r="696" spans="2:11" ht="12.5">
       <c r="B696" s="20"/>
       <c r="C696" s="20"/>
       <c r="D696" s="20"/>
@@ -7415,7 +7556,7 @@
       <c r="I696" s="20"/>
       <c r="K696" s="20"/>
     </row>
-    <row r="697" spans="2:11" ht="13">
+    <row r="697" spans="2:11" ht="12.5">
       <c r="B697" s="20"/>
       <c r="C697" s="20"/>
       <c r="D697" s="20"/>
@@ -7426,7 +7567,7 @@
       <c r="I697" s="20"/>
       <c r="K697" s="20"/>
     </row>
-    <row r="698" spans="2:11" ht="13">
+    <row r="698" spans="2:11" ht="12.5">
       <c r="B698" s="20"/>
       <c r="C698" s="20"/>
       <c r="D698" s="20"/>
@@ -7437,7 +7578,7 @@
       <c r="I698" s="20"/>
       <c r="K698" s="20"/>
     </row>
-    <row r="699" spans="2:11" ht="13">
+    <row r="699" spans="2:11" ht="12.5">
       <c r="B699" s="20"/>
       <c r="C699" s="20"/>
       <c r="D699" s="20"/>
@@ -7448,7 +7589,7 @@
       <c r="I699" s="20"/>
       <c r="K699" s="20"/>
     </row>
-    <row r="700" spans="2:11" ht="13">
+    <row r="700" spans="2:11" ht="12.5">
       <c r="B700" s="20"/>
       <c r="C700" s="20"/>
       <c r="D700" s="20"/>
@@ -7459,7 +7600,7 @@
       <c r="I700" s="20"/>
       <c r="K700" s="20"/>
     </row>
-    <row r="701" spans="2:11" ht="13">
+    <row r="701" spans="2:11" ht="12.5">
       <c r="B701" s="20"/>
       <c r="C701" s="20"/>
       <c r="D701" s="20"/>
@@ -7470,7 +7611,7 @@
       <c r="I701" s="20"/>
       <c r="K701" s="20"/>
     </row>
-    <row r="702" spans="2:11" ht="13">
+    <row r="702" spans="2:11" ht="12.5">
       <c r="B702" s="20"/>
       <c r="C702" s="20"/>
       <c r="D702" s="20"/>
@@ -7481,7 +7622,7 @@
       <c r="I702" s="20"/>
       <c r="K702" s="20"/>
     </row>
-    <row r="703" spans="2:11" ht="13">
+    <row r="703" spans="2:11" ht="12.5">
       <c r="B703" s="20"/>
       <c r="C703" s="20"/>
       <c r="D703" s="20"/>
@@ -7492,7 +7633,7 @@
       <c r="I703" s="20"/>
       <c r="K703" s="20"/>
     </row>
-    <row r="704" spans="2:11" ht="13">
+    <row r="704" spans="2:11" ht="12.5">
       <c r="B704" s="20"/>
       <c r="C704" s="20"/>
       <c r="D704" s="20"/>
@@ -7503,7 +7644,7 @@
       <c r="I704" s="20"/>
       <c r="K704" s="20"/>
     </row>
-    <row r="705" spans="2:11" ht="13">
+    <row r="705" spans="2:11" ht="12.5">
       <c r="B705" s="20"/>
       <c r="C705" s="20"/>
       <c r="D705" s="20"/>
@@ -7514,7 +7655,7 @@
       <c r="I705" s="20"/>
       <c r="K705" s="20"/>
     </row>
-    <row r="706" spans="2:11" ht="13">
+    <row r="706" spans="2:11" ht="12.5">
       <c r="B706" s="20"/>
       <c r="C706" s="20"/>
       <c r="D706" s="20"/>
@@ -7525,7 +7666,7 @@
       <c r="I706" s="20"/>
       <c r="K706" s="20"/>
     </row>
-    <row r="707" spans="2:11" ht="13">
+    <row r="707" spans="2:11" ht="12.5">
       <c r="B707" s="20"/>
       <c r="C707" s="20"/>
       <c r="D707" s="20"/>
@@ -7536,7 +7677,7 @@
       <c r="I707" s="20"/>
       <c r="K707" s="20"/>
     </row>
-    <row r="708" spans="2:11" ht="13">
+    <row r="708" spans="2:11" ht="12.5">
       <c r="B708" s="20"/>
       <c r="C708" s="20"/>
       <c r="D708" s="20"/>
@@ -7547,7 +7688,7 @@
       <c r="I708" s="20"/>
       <c r="K708" s="20"/>
     </row>
-    <row r="709" spans="2:11" ht="13">
+    <row r="709" spans="2:11" ht="12.5">
       <c r="B709" s="20"/>
       <c r="C709" s="20"/>
       <c r="D709" s="20"/>
@@ -7558,7 +7699,7 @@
       <c r="I709" s="20"/>
       <c r="K709" s="20"/>
     </row>
-    <row r="710" spans="2:11" ht="13">
+    <row r="710" spans="2:11" ht="12.5">
       <c r="B710" s="20"/>
       <c r="C710" s="20"/>
       <c r="D710" s="20"/>
@@ -7569,7 +7710,7 @@
       <c r="I710" s="20"/>
       <c r="K710" s="20"/>
     </row>
-    <row r="711" spans="2:11" ht="13">
+    <row r="711" spans="2:11" ht="12.5">
       <c r="B711" s="20"/>
       <c r="C711" s="20"/>
       <c r="D711" s="20"/>
@@ -7580,7 +7721,7 @@
       <c r="I711" s="20"/>
       <c r="K711" s="20"/>
     </row>
-    <row r="712" spans="2:11" ht="13">
+    <row r="712" spans="2:11" ht="12.5">
       <c r="B712" s="20"/>
       <c r="C712" s="20"/>
       <c r="D712" s="20"/>
@@ -7591,7 +7732,7 @@
       <c r="I712" s="20"/>
       <c r="K712" s="20"/>
     </row>
-    <row r="713" spans="2:11" ht="13">
+    <row r="713" spans="2:11" ht="12.5">
       <c r="B713" s="20"/>
       <c r="C713" s="20"/>
       <c r="D713" s="20"/>
@@ -7602,7 +7743,7 @@
       <c r="I713" s="20"/>
       <c r="K713" s="20"/>
     </row>
-    <row r="714" spans="2:11" ht="13">
+    <row r="714" spans="2:11" ht="12.5">
       <c r="B714" s="20"/>
       <c r="C714" s="20"/>
       <c r="D714" s="20"/>
@@ -7613,7 +7754,7 @@
       <c r="I714" s="20"/>
       <c r="K714" s="20"/>
     </row>
-    <row r="715" spans="2:11" ht="13">
+    <row r="715" spans="2:11" ht="12.5">
       <c r="B715" s="20"/>
       <c r="C715" s="20"/>
       <c r="D715" s="20"/>
@@ -7624,7 +7765,7 @@
       <c r="I715" s="20"/>
       <c r="K715" s="20"/>
     </row>
-    <row r="716" spans="2:11" ht="13">
+    <row r="716" spans="2:11" ht="12.5">
       <c r="B716" s="20"/>
       <c r="C716" s="20"/>
       <c r="D716" s="20"/>
@@ -7635,7 +7776,7 @@
       <c r="I716" s="20"/>
       <c r="K716" s="20"/>
     </row>
-    <row r="717" spans="2:11" ht="13">
+    <row r="717" spans="2:11" ht="12.5">
       <c r="B717" s="20"/>
       <c r="C717" s="20"/>
       <c r="D717" s="20"/>
@@ -7646,7 +7787,7 @@
       <c r="I717" s="20"/>
       <c r="K717" s="20"/>
     </row>
-    <row r="718" spans="2:11" ht="13">
+    <row r="718" spans="2:11" ht="12.5">
       <c r="B718" s="20"/>
       <c r="C718" s="20"/>
       <c r="D718" s="20"/>
@@ -7657,7 +7798,7 @@
       <c r="I718" s="20"/>
       <c r="K718" s="20"/>
     </row>
-    <row r="719" spans="2:11" ht="13">
+    <row r="719" spans="2:11" ht="12.5">
       <c r="B719" s="20"/>
       <c r="C719" s="20"/>
       <c r="D719" s="20"/>
@@ -7668,7 +7809,7 @@
       <c r="I719" s="20"/>
       <c r="K719" s="20"/>
     </row>
-    <row r="720" spans="2:11" ht="13">
+    <row r="720" spans="2:11" ht="12.5">
       <c r="B720" s="20"/>
       <c r="C720" s="20"/>
       <c r="D720" s="20"/>
@@ -7679,7 +7820,7 @@
       <c r="I720" s="20"/>
       <c r="K720" s="20"/>
     </row>
-    <row r="721" spans="2:11" ht="13">
+    <row r="721" spans="2:11" ht="12.5">
       <c r="B721" s="20"/>
       <c r="C721" s="20"/>
       <c r="D721" s="20"/>
@@ -7690,7 +7831,7 @@
       <c r="I721" s="20"/>
       <c r="K721" s="20"/>
     </row>
-    <row r="722" spans="2:11" ht="13">
+    <row r="722" spans="2:11" ht="12.5">
       <c r="B722" s="20"/>
       <c r="C722" s="20"/>
       <c r="D722" s="20"/>
@@ -7701,7 +7842,7 @@
       <c r="I722" s="20"/>
       <c r="K722" s="20"/>
     </row>
-    <row r="723" spans="2:11" ht="13">
+    <row r="723" spans="2:11" ht="12.5">
       <c r="B723" s="20"/>
       <c r="C723" s="20"/>
       <c r="D723" s="20"/>
@@ -7712,7 +7853,7 @@
       <c r="I723" s="20"/>
       <c r="K723" s="20"/>
     </row>
-    <row r="724" spans="2:11" ht="13">
+    <row r="724" spans="2:11" ht="12.5">
       <c r="B724" s="20"/>
       <c r="C724" s="20"/>
       <c r="D724" s="20"/>
@@ -7723,7 +7864,7 @@
       <c r="I724" s="20"/>
       <c r="K724" s="20"/>
     </row>
-    <row r="725" spans="2:11" ht="13">
+    <row r="725" spans="2:11" ht="12.5">
       <c r="B725" s="20"/>
       <c r="C725" s="20"/>
       <c r="D725" s="20"/>
@@ -7734,7 +7875,7 @@
       <c r="I725" s="20"/>
       <c r="K725" s="20"/>
     </row>
-    <row r="726" spans="2:11" ht="13">
+    <row r="726" spans="2:11" ht="12.5">
       <c r="B726" s="20"/>
       <c r="C726" s="20"/>
       <c r="D726" s="20"/>
@@ -7745,7 +7886,7 @@
       <c r="I726" s="20"/>
       <c r="K726" s="20"/>
     </row>
-    <row r="727" spans="2:11" ht="13">
+    <row r="727" spans="2:11" ht="12.5">
       <c r="B727" s="20"/>
       <c r="C727" s="20"/>
       <c r="D727" s="20"/>
@@ -7756,7 +7897,7 @@
       <c r="I727" s="20"/>
       <c r="K727" s="20"/>
     </row>
-    <row r="728" spans="2:11" ht="13">
+    <row r="728" spans="2:11" ht="12.5">
       <c r="B728" s="20"/>
       <c r="C728" s="20"/>
       <c r="D728" s="20"/>
@@ -7767,7 +7908,7 @@
       <c r="I728" s="20"/>
       <c r="K728" s="20"/>
     </row>
-    <row r="729" spans="2:11" ht="13">
+    <row r="729" spans="2:11" ht="12.5">
       <c r="B729" s="20"/>
       <c r="C729" s="20"/>
       <c r="D729" s="20"/>
@@ -7778,7 +7919,7 @@
       <c r="I729" s="20"/>
       <c r="K729" s="20"/>
     </row>
-    <row r="730" spans="2:11" ht="13">
+    <row r="730" spans="2:11" ht="12.5">
       <c r="B730" s="20"/>
       <c r="C730" s="20"/>
       <c r="D730" s="20"/>
@@ -7789,7 +7930,7 @@
       <c r="I730" s="20"/>
       <c r="K730" s="20"/>
     </row>
-    <row r="731" spans="2:11" ht="13">
+    <row r="731" spans="2:11" ht="12.5">
       <c r="B731" s="20"/>
       <c r="C731" s="20"/>
       <c r="D731" s="20"/>
@@ -7800,7 +7941,7 @@
       <c r="I731" s="20"/>
       <c r="K731" s="20"/>
     </row>
-    <row r="732" spans="2:11" ht="13">
+    <row r="732" spans="2:11" ht="12.5">
       <c r="B732" s="20"/>
       <c r="C732" s="20"/>
       <c r="D732" s="20"/>
@@ -7811,7 +7952,7 @@
       <c r="I732" s="20"/>
       <c r="K732" s="20"/>
     </row>
-    <row r="733" spans="2:11" ht="13">
+    <row r="733" spans="2:11" ht="12.5">
       <c r="B733" s="20"/>
       <c r="C733" s="20"/>
       <c r="D733" s="20"/>
@@ -7822,7 +7963,7 @@
       <c r="I733" s="20"/>
       <c r="K733" s="20"/>
     </row>
-    <row r="734" spans="2:11" ht="13">
+    <row r="734" spans="2:11" ht="12.5">
       <c r="B734" s="20"/>
       <c r="C734" s="20"/>
       <c r="D734" s="20"/>
@@ -7833,7 +7974,7 @@
       <c r="I734" s="20"/>
       <c r="K734" s="20"/>
     </row>
-    <row r="735" spans="2:11" ht="13">
+    <row r="735" spans="2:11" ht="12.5">
       <c r="B735" s="20"/>
       <c r="C735" s="20"/>
       <c r="D735" s="20"/>
@@ -7844,7 +7985,7 @@
       <c r="I735" s="20"/>
       <c r="K735" s="20"/>
     </row>
-    <row r="736" spans="2:11" ht="13">
+    <row r="736" spans="2:11" ht="12.5">
       <c r="B736" s="20"/>
       <c r="C736" s="20"/>
       <c r="D736" s="20"/>
@@ -7855,7 +7996,7 @@
       <c r="I736" s="20"/>
       <c r="K736" s="20"/>
     </row>
-    <row r="737" spans="2:11" ht="13">
+    <row r="737" spans="2:11" ht="12.5">
       <c r="B737" s="20"/>
       <c r="C737" s="20"/>
       <c r="D737" s="20"/>
@@ -7866,7 +8007,7 @@
       <c r="I737" s="20"/>
       <c r="K737" s="20"/>
     </row>
-    <row r="738" spans="2:11" ht="13">
+    <row r="738" spans="2:11" ht="12.5">
       <c r="B738" s="20"/>
       <c r="C738" s="20"/>
       <c r="D738" s="20"/>
@@ -7877,7 +8018,7 @@
       <c r="I738" s="20"/>
       <c r="K738" s="20"/>
     </row>
-    <row r="739" spans="2:11" ht="13">
+    <row r="739" spans="2:11" ht="12.5">
       <c r="B739" s="20"/>
       <c r="C739" s="20"/>
       <c r="D739" s="20"/>
@@ -7888,7 +8029,7 @@
       <c r="I739" s="20"/>
       <c r="K739" s="20"/>
     </row>
-    <row r="740" spans="2:11" ht="13">
+    <row r="740" spans="2:11" ht="12.5">
       <c r="B740" s="20"/>
       <c r="C740" s="20"/>
       <c r="D740" s="20"/>
@@ -7899,7 +8040,7 @@
       <c r="I740" s="20"/>
       <c r="K740" s="20"/>
     </row>
-    <row r="741" spans="2:11" ht="13">
+    <row r="741" spans="2:11" ht="12.5">
       <c r="B741" s="20"/>
       <c r="C741" s="20"/>
       <c r="D741" s="20"/>
@@ -7910,7 +8051,7 @@
       <c r="I741" s="20"/>
       <c r="K741" s="20"/>
     </row>
-    <row r="742" spans="2:11" ht="13">
+    <row r="742" spans="2:11" ht="12.5">
       <c r="B742" s="20"/>
       <c r="C742" s="20"/>
       <c r="D742" s="20"/>
@@ -7921,7 +8062,7 @@
       <c r="I742" s="20"/>
       <c r="K742" s="20"/>
     </row>
-    <row r="743" spans="2:11" ht="13">
+    <row r="743" spans="2:11" ht="12.5">
       <c r="B743" s="20"/>
       <c r="C743" s="20"/>
       <c r="D743" s="20"/>
@@ -7932,7 +8073,7 @@
       <c r="I743" s="20"/>
       <c r="K743" s="20"/>
     </row>
-    <row r="744" spans="2:11" ht="13">
+    <row r="744" spans="2:11" ht="12.5">
       <c r="B744" s="20"/>
       <c r="C744" s="20"/>
       <c r="D744" s="20"/>
@@ -7943,7 +8084,7 @@
       <c r="I744" s="20"/>
       <c r="K744" s="20"/>
     </row>
-    <row r="745" spans="2:11" ht="13">
+    <row r="745" spans="2:11" ht="12.5">
       <c r="B745" s="20"/>
       <c r="C745" s="20"/>
       <c r="D745" s="20"/>
@@ -7954,7 +8095,7 @@
       <c r="I745" s="20"/>
       <c r="K745" s="20"/>
     </row>
-    <row r="746" spans="2:11" ht="13">
+    <row r="746" spans="2:11" ht="12.5">
       <c r="B746" s="20"/>
       <c r="C746" s="20"/>
       <c r="D746" s="20"/>
@@ -7965,7 +8106,7 @@
       <c r="I746" s="20"/>
       <c r="K746" s="20"/>
     </row>
-    <row r="747" spans="2:11" ht="13">
+    <row r="747" spans="2:11" ht="12.5">
       <c r="B747" s="20"/>
       <c r="C747" s="20"/>
       <c r="D747" s="20"/>
@@ -7976,7 +8117,7 @@
       <c r="I747" s="20"/>
       <c r="K747" s="20"/>
     </row>
-    <row r="748" spans="2:11" ht="13">
+    <row r="748" spans="2:11" ht="12.5">
       <c r="B748" s="20"/>
       <c r="C748" s="20"/>
       <c r="D748" s="20"/>
@@ -7987,7 +8128,7 @@
       <c r="I748" s="20"/>
       <c r="K748" s="20"/>
     </row>
-    <row r="749" spans="2:11" ht="13">
+    <row r="749" spans="2:11" ht="12.5">
       <c r="B749" s="20"/>
       <c r="C749" s="20"/>
       <c r="D749" s="20"/>
@@ -7998,7 +8139,7 @@
       <c r="I749" s="20"/>
       <c r="K749" s="20"/>
     </row>
-    <row r="750" spans="2:11" ht="13">
+    <row r="750" spans="2:11" ht="12.5">
       <c r="B750" s="20"/>
       <c r="C750" s="20"/>
       <c r="D750" s="20"/>
@@ -8009,7 +8150,7 @@
       <c r="I750" s="20"/>
       <c r="K750" s="20"/>
     </row>
-    <row r="751" spans="2:11" ht="13">
+    <row r="751" spans="2:11" ht="12.5">
       <c r="B751" s="20"/>
       <c r="C751" s="20"/>
       <c r="D751" s="20"/>
@@ -8020,7 +8161,7 @@
       <c r="I751" s="20"/>
       <c r="K751" s="20"/>
     </row>
-    <row r="752" spans="2:11" ht="13">
+    <row r="752" spans="2:11" ht="12.5">
       <c r="B752" s="20"/>
       <c r="C752" s="20"/>
       <c r="D752" s="20"/>
@@ -8031,7 +8172,7 @@
       <c r="I752" s="20"/>
       <c r="K752" s="20"/>
     </row>
-    <row r="753" spans="2:11" ht="13">
+    <row r="753" spans="2:11" ht="12.5">
       <c r="B753" s="20"/>
       <c r="C753" s="20"/>
       <c r="D753" s="20"/>
@@ -8042,7 +8183,7 @@
       <c r="I753" s="20"/>
       <c r="K753" s="20"/>
     </row>
-    <row r="754" spans="2:11" ht="13">
+    <row r="754" spans="2:11" ht="12.5">
       <c r="B754" s="20"/>
       <c r="C754" s="20"/>
       <c r="D754" s="20"/>
@@ -8053,7 +8194,7 @@
       <c r="I754" s="20"/>
       <c r="K754" s="20"/>
     </row>
-    <row r="755" spans="2:11" ht="13">
+    <row r="755" spans="2:11" ht="12.5">
       <c r="B755" s="20"/>
       <c r="C755" s="20"/>
       <c r="D755" s="20"/>
@@ -8064,7 +8205,7 @@
       <c r="I755" s="20"/>
       <c r="K755" s="20"/>
     </row>
-    <row r="756" spans="2:11" ht="13">
+    <row r="756" spans="2:11" ht="12.5">
       <c r="B756" s="20"/>
       <c r="C756" s="20"/>
       <c r="D756" s="20"/>
@@ -8075,7 +8216,7 @@
       <c r="I756" s="20"/>
       <c r="K756" s="20"/>
     </row>
-    <row r="757" spans="2:11" ht="13">
+    <row r="757" spans="2:11" ht="12.5">
       <c r="B757" s="20"/>
       <c r="C757" s="20"/>
       <c r="D757" s="20"/>
@@ -8086,7 +8227,7 @@
       <c r="I757" s="20"/>
       <c r="K757" s="20"/>
     </row>
-    <row r="758" spans="2:11" ht="13">
+    <row r="758" spans="2:11" ht="12.5">
       <c r="B758" s="20"/>
       <c r="C758" s="20"/>
       <c r="D758" s="20"/>
@@ -8097,7 +8238,7 @@
       <c r="I758" s="20"/>
       <c r="K758" s="20"/>
     </row>
-    <row r="759" spans="2:11" ht="13">
+    <row r="759" spans="2:11" ht="12.5">
       <c r="B759" s="20"/>
       <c r="C759" s="20"/>
       <c r="D759" s="20"/>
@@ -8108,7 +8249,7 @@
       <c r="I759" s="20"/>
       <c r="K759" s="20"/>
     </row>
-    <row r="760" spans="2:11" ht="13">
+    <row r="760" spans="2:11" ht="12.5">
       <c r="B760" s="20"/>
       <c r="C760" s="20"/>
       <c r="D760" s="20"/>
@@ -8119,7 +8260,7 @@
       <c r="I760" s="20"/>
       <c r="K760" s="20"/>
     </row>
-    <row r="761" spans="2:11" ht="13">
+    <row r="761" spans="2:11" ht="12.5">
       <c r="B761" s="20"/>
       <c r="C761" s="20"/>
       <c r="D761" s="20"/>
@@ -8130,7 +8271,7 @@
       <c r="I761" s="20"/>
       <c r="K761" s="20"/>
     </row>
-    <row r="762" spans="2:11" ht="13">
+    <row r="762" spans="2:11" ht="12.5">
       <c r="B762" s="20"/>
       <c r="C762" s="20"/>
       <c r="D762" s="20"/>
@@ -8141,7 +8282,7 @@
       <c r="I762" s="20"/>
       <c r="K762" s="20"/>
     </row>
-    <row r="763" spans="2:11" ht="13">
+    <row r="763" spans="2:11" ht="12.5">
       <c r="B763" s="20"/>
       <c r="C763" s="20"/>
       <c r="D763" s="20"/>
@@ -8152,7 +8293,7 @@
       <c r="I763" s="20"/>
       <c r="K763" s="20"/>
     </row>
-    <row r="764" spans="2:11" ht="13">
+    <row r="764" spans="2:11" ht="12.5">
       <c r="B764" s="20"/>
       <c r="C764" s="20"/>
       <c r="D764" s="20"/>
@@ -8163,7 +8304,7 @@
       <c r="I764" s="20"/>
       <c r="K764" s="20"/>
     </row>
-    <row r="765" spans="2:11" ht="13">
+    <row r="765" spans="2:11" ht="12.5">
       <c r="B765" s="20"/>
       <c r="C765" s="20"/>
       <c r="D765" s="20"/>
@@ -8174,7 +8315,7 @@
       <c r="I765" s="20"/>
       <c r="K765" s="20"/>
     </row>
-    <row r="766" spans="2:11" ht="13">
+    <row r="766" spans="2:11" ht="12.5">
       <c r="B766" s="20"/>
       <c r="C766" s="20"/>
       <c r="D766" s="20"/>
@@ -8185,7 +8326,7 @@
       <c r="I766" s="20"/>
       <c r="K766" s="20"/>
     </row>
-    <row r="767" spans="2:11" ht="13">
+    <row r="767" spans="2:11" ht="12.5">
       <c r="B767" s="20"/>
       <c r="C767" s="20"/>
       <c r="D767" s="20"/>
@@ -8196,7 +8337,7 @@
       <c r="I767" s="20"/>
       <c r="K767" s="20"/>
     </row>
-    <row r="768" spans="2:11" ht="13">
+    <row r="768" spans="2:11" ht="12.5">
       <c r="B768" s="20"/>
       <c r="C768" s="20"/>
       <c r="D768" s="20"/>
@@ -8207,7 +8348,7 @@
       <c r="I768" s="20"/>
       <c r="K768" s="20"/>
     </row>
-    <row r="769" spans="2:11" ht="13">
+    <row r="769" spans="2:11" ht="12.5">
       <c r="B769" s="20"/>
       <c r="C769" s="20"/>
       <c r="D769" s="20"/>
@@ -8218,7 +8359,7 @@
       <c r="I769" s="20"/>
       <c r="K769" s="20"/>
     </row>
-    <row r="770" spans="2:11" ht="13">
+    <row r="770" spans="2:11" ht="12.5">
       <c r="B770" s="20"/>
       <c r="C770" s="20"/>
       <c r="D770" s="20"/>
@@ -8229,7 +8370,7 @@
       <c r="I770" s="20"/>
       <c r="K770" s="20"/>
     </row>
-    <row r="771" spans="2:11" ht="13">
+    <row r="771" spans="2:11" ht="12.5">
       <c r="B771" s="20"/>
       <c r="C771" s="20"/>
       <c r="D771" s="20"/>
@@ -8240,7 +8381,7 @@
       <c r="I771" s="20"/>
       <c r="K771" s="20"/>
     </row>
-    <row r="772" spans="2:11" ht="13">
+    <row r="772" spans="2:11" ht="12.5">
       <c r="B772" s="20"/>
       <c r="C772" s="20"/>
       <c r="D772" s="20"/>
@@ -8251,7 +8392,7 @@
       <c r="I772" s="20"/>
       <c r="K772" s="20"/>
     </row>
-    <row r="773" spans="2:11" ht="13">
+    <row r="773" spans="2:11" ht="12.5">
       <c r="B773" s="20"/>
       <c r="C773" s="20"/>
       <c r="D773" s="20"/>
@@ -8262,7 +8403,7 @@
       <c r="I773" s="20"/>
       <c r="K773" s="20"/>
     </row>
-    <row r="774" spans="2:11" ht="13">
+    <row r="774" spans="2:11" ht="12.5">
       <c r="B774" s="20"/>
       <c r="C774" s="20"/>
       <c r="D774" s="20"/>
@@ -8273,7 +8414,7 @@
       <c r="I774" s="20"/>
       <c r="K774" s="20"/>
     </row>
-    <row r="775" spans="2:11" ht="13">
+    <row r="775" spans="2:11" ht="12.5">
       <c r="B775" s="20"/>
       <c r="C775" s="20"/>
       <c r="D775" s="20"/>
@@ -8284,7 +8425,7 @@
       <c r="I775" s="20"/>
       <c r="K775" s="20"/>
     </row>
-    <row r="776" spans="2:11" ht="13">
+    <row r="776" spans="2:11" ht="12.5">
       <c r="B776" s="20"/>
       <c r="C776" s="20"/>
       <c r="D776" s="20"/>
@@ -8295,7 +8436,7 @@
       <c r="I776" s="20"/>
       <c r="K776" s="20"/>
     </row>
-    <row r="777" spans="2:11" ht="13">
+    <row r="777" spans="2:11" ht="12.5">
       <c r="B777" s="20"/>
       <c r="C777" s="20"/>
       <c r="D777" s="20"/>
@@ -8306,7 +8447,7 @@
       <c r="I777" s="20"/>
       <c r="K777" s="20"/>
     </row>
-    <row r="778" spans="2:11" ht="13">
+    <row r="778" spans="2:11" ht="12.5">
       <c r="B778" s="20"/>
       <c r="C778" s="20"/>
       <c r="D778" s="20"/>
@@ -8317,7 +8458,7 @@
       <c r="I778" s="20"/>
       <c r="K778" s="20"/>
     </row>
-    <row r="779" spans="2:11" ht="13">
+    <row r="779" spans="2:11" ht="12.5">
       <c r="B779" s="20"/>
       <c r="C779" s="20"/>
       <c r="D779" s="20"/>
@@ -8328,7 +8469,7 @@
       <c r="I779" s="20"/>
       <c r="K779" s="20"/>
     </row>
-    <row r="780" spans="2:11" ht="13">
+    <row r="780" spans="2:11" ht="12.5">
       <c r="B780" s="20"/>
       <c r="C780" s="20"/>
       <c r="D780" s="20"/>
@@ -8339,7 +8480,7 @@
       <c r="I780" s="20"/>
       <c r="K780" s="20"/>
     </row>
-    <row r="781" spans="2:11" ht="13">
+    <row r="781" spans="2:11" ht="12.5">
       <c r="B781" s="20"/>
       <c r="C781" s="20"/>
       <c r="D781" s="20"/>
@@ -8350,7 +8491,7 @@
       <c r="I781" s="20"/>
       <c r="K781" s="20"/>
     </row>
-    <row r="782" spans="2:11" ht="13">
+    <row r="782" spans="2:11" ht="12.5">
       <c r="B782" s="20"/>
       <c r="C782" s="20"/>
       <c r="D782" s="20"/>
@@ -8361,7 +8502,7 @@
       <c r="I782" s="20"/>
       <c r="K782" s="20"/>
     </row>
-    <row r="783" spans="2:11" ht="13">
+    <row r="783" spans="2:11" ht="12.5">
       <c r="B783" s="20"/>
       <c r="C783" s="20"/>
       <c r="D783" s="20"/>
@@ -8372,7 +8513,7 @@
       <c r="I783" s="20"/>
       <c r="K783" s="20"/>
     </row>
-    <row r="784" spans="2:11" ht="13">
+    <row r="784" spans="2:11" ht="12.5">
       <c r="B784" s="20"/>
       <c r="C784" s="20"/>
       <c r="D784" s="20"/>
@@ -8383,7 +8524,7 @@
       <c r="I784" s="20"/>
       <c r="K784" s="20"/>
     </row>
-    <row r="785" spans="2:11" ht="13">
+    <row r="785" spans="2:11" ht="12.5">
       <c r="B785" s="20"/>
       <c r="C785" s="20"/>
       <c r="D785" s="20"/>
@@ -8394,7 +8535,7 @@
       <c r="I785" s="20"/>
       <c r="K785" s="20"/>
     </row>
-    <row r="786" spans="2:11" ht="13">
+    <row r="786" spans="2:11" ht="12.5">
       <c r="B786" s="20"/>
       <c r="C786" s="20"/>
       <c r="D786" s="20"/>
@@ -8405,7 +8546,7 @@
       <c r="I786" s="20"/>
       <c r="K786" s="20"/>
     </row>
-    <row r="787" spans="2:11" ht="13">
+    <row r="787" spans="2:11" ht="12.5">
       <c r="B787" s="20"/>
       <c r="C787" s="20"/>
       <c r="D787" s="20"/>
@@ -8416,7 +8557,7 @@
       <c r="I787" s="20"/>
       <c r="K787" s="20"/>
     </row>
-    <row r="788" spans="2:11" ht="13">
+    <row r="788" spans="2:11" ht="12.5">
       <c r="B788" s="20"/>
       <c r="C788" s="20"/>
       <c r="D788" s="20"/>
@@ -8427,7 +8568,7 @@
       <c r="I788" s="20"/>
       <c r="K788" s="20"/>
     </row>
-    <row r="789" spans="2:11" ht="13">
+    <row r="789" spans="2:11" ht="12.5">
       <c r="B789" s="20"/>
       <c r="C789" s="20"/>
       <c r="D789" s="20"/>
@@ -8438,7 +8579,7 @@
       <c r="I789" s="20"/>
       <c r="K789" s="20"/>
     </row>
-    <row r="790" spans="2:11" ht="13">
+    <row r="790" spans="2:11" ht="12.5">
       <c r="B790" s="20"/>
       <c r="C790" s="20"/>
       <c r="D790" s="20"/>
@@ -8449,7 +8590,7 @@
       <c r="I790" s="20"/>
       <c r="K790" s="20"/>
     </row>
-    <row r="791" spans="2:11" ht="13">
+    <row r="791" spans="2:11" ht="12.5">
       <c r="B791" s="20"/>
       <c r="C791" s="20"/>
       <c r="D791" s="20"/>
@@ -8460,7 +8601,7 @@
       <c r="I791" s="20"/>
       <c r="K791" s="20"/>
     </row>
-    <row r="792" spans="2:11" ht="13">
+    <row r="792" spans="2:11" ht="12.5">
       <c r="B792" s="20"/>
       <c r="C792" s="20"/>
       <c r="D792" s="20"/>
@@ -8471,7 +8612,7 @@
       <c r="I792" s="20"/>
       <c r="K792" s="20"/>
     </row>
-    <row r="793" spans="2:11" ht="13">
+    <row r="793" spans="2:11" ht="12.5">
       <c r="B793" s="20"/>
       <c r="C793" s="20"/>
       <c r="D793" s="20"/>
@@ -8482,7 +8623,7 @@
       <c r="I793" s="20"/>
       <c r="K793" s="20"/>
     </row>
-    <row r="794" spans="2:11" ht="13">
+    <row r="794" spans="2:11" ht="12.5">
       <c r="B794" s="20"/>
       <c r="C794" s="20"/>
       <c r="D794" s="20"/>
@@ -8493,7 +8634,7 @@
       <c r="I794" s="20"/>
       <c r="K794" s="20"/>
     </row>
-    <row r="795" spans="2:11" ht="13">
+    <row r="795" spans="2:11" ht="12.5">
       <c r="B795" s="20"/>
       <c r="C795" s="20"/>
       <c r="D795" s="20"/>
@@ -8504,7 +8645,7 @@
       <c r="I795" s="20"/>
       <c r="K795" s="20"/>
     </row>
-    <row r="796" spans="2:11" ht="13">
+    <row r="796" spans="2:11" ht="12.5">
       <c r="B796" s="20"/>
       <c r="C796" s="20"/>
       <c r="D796" s="20"/>
@@ -8515,7 +8656,7 @@
       <c r="I796" s="20"/>
       <c r="K796" s="20"/>
     </row>
-    <row r="797" spans="2:11" ht="13">
+    <row r="797" spans="2:11" ht="12.5">
       <c r="B797" s="20"/>
       <c r="C797" s="20"/>
       <c r="D797" s="20"/>
@@ -8526,7 +8667,7 @@
       <c r="I797" s="20"/>
       <c r="K797" s="20"/>
     </row>
-    <row r="798" spans="2:11" ht="13">
+    <row r="798" spans="2:11" ht="12.5">
       <c r="B798" s="20"/>
       <c r="C798" s="20"/>
       <c r="D798" s="20"/>
@@ -8537,7 +8678,7 @@
       <c r="I798" s="20"/>
       <c r="K798" s="20"/>
     </row>
-    <row r="799" spans="2:11" ht="13">
+    <row r="799" spans="2:11" ht="12.5">
       <c r="B799" s="20"/>
       <c r="C799" s="20"/>
       <c r="D799" s="20"/>
@@ -8548,7 +8689,7 @@
       <c r="I799" s="20"/>
       <c r="K799" s="20"/>
     </row>
-    <row r="800" spans="2:11" ht="13">
+    <row r="800" spans="2:11" ht="12.5">
       <c r="B800" s="20"/>
       <c r="C800" s="20"/>
       <c r="D800" s="20"/>
@@ -8559,7 +8700,7 @@
       <c r="I800" s="20"/>
       <c r="K800" s="20"/>
     </row>
-    <row r="801" spans="2:11" ht="13">
+    <row r="801" spans="2:11" ht="12.5">
       <c r="B801" s="20"/>
       <c r="C801" s="20"/>
       <c r="D801" s="20"/>
@@ -8570,7 +8711,7 @@
       <c r="I801" s="20"/>
       <c r="K801" s="20"/>
     </row>
-    <row r="802" spans="2:11" ht="13">
+    <row r="802" spans="2:11" ht="12.5">
       <c r="B802" s="20"/>
       <c r="C802" s="20"/>
       <c r="D802" s="20"/>
@@ -8581,7 +8722,7 @@
       <c r="I802" s="20"/>
       <c r="K802" s="20"/>
     </row>
-    <row r="803" spans="2:11" ht="13">
+    <row r="803" spans="2:11" ht="12.5">
       <c r="B803" s="20"/>
       <c r="C803" s="20"/>
       <c r="D803" s="20"/>
@@ -8592,7 +8733,7 @@
       <c r="I803" s="20"/>
       <c r="K803" s="20"/>
     </row>
-    <row r="804" spans="2:11" ht="13">
+    <row r="804" spans="2:11" ht="12.5">
       <c r="B804" s="20"/>
       <c r="C804" s="20"/>
       <c r="D804" s="20"/>
@@ -8603,7 +8744,7 @@
       <c r="I804" s="20"/>
       <c r="K804" s="20"/>
     </row>
-    <row r="805" spans="2:11" ht="13">
+    <row r="805" spans="2:11" ht="12.5">
       <c r="B805" s="20"/>
       <c r="C805" s="20"/>
       <c r="D805" s="20"/>
@@ -8614,7 +8755,7 @@
       <c r="I805" s="20"/>
       <c r="K805" s="20"/>
     </row>
-    <row r="806" spans="2:11" ht="13">
+    <row r="806" spans="2:11" ht="12.5">
       <c r="B806" s="20"/>
       <c r="C806" s="20"/>
       <c r="D806" s="20"/>
@@ -8625,7 +8766,7 @@
       <c r="I806" s="20"/>
       <c r="K806" s="20"/>
     </row>
-    <row r="807" spans="2:11" ht="13">
+    <row r="807" spans="2:11" ht="12.5">
       <c r="B807" s="20"/>
       <c r="C807" s="20"/>
       <c r="D807" s="20"/>
@@ -8636,7 +8777,7 @@
       <c r="I807" s="20"/>
       <c r="K807" s="20"/>
     </row>
-    <row r="808" spans="2:11" ht="13">
+    <row r="808" spans="2:11" ht="12.5">
       <c r="B808" s="20"/>
       <c r="C808" s="20"/>
       <c r="D808" s="20"/>
@@ -8647,7 +8788,7 @@
       <c r="I808" s="20"/>
       <c r="K808" s="20"/>
     </row>
-    <row r="809" spans="2:11" ht="13">
+    <row r="809" spans="2:11" ht="12.5">
       <c r="B809" s="20"/>
       <c r="C809" s="20"/>
       <c r="D809" s="20"/>
@@ -8658,7 +8799,7 @@
       <c r="I809" s="20"/>
       <c r="K809" s="20"/>
     </row>
-    <row r="810" spans="2:11" ht="13">
+    <row r="810" spans="2:11" ht="12.5">
       <c r="B810" s="20"/>
       <c r="C810" s="20"/>
       <c r="D810" s="20"/>
@@ -8669,7 +8810,7 @@
       <c r="I810" s="20"/>
       <c r="K810" s="20"/>
     </row>
-    <row r="811" spans="2:11" ht="13">
+    <row r="811" spans="2:11" ht="12.5">
       <c r="B811" s="20"/>
       <c r="C811" s="20"/>
       <c r="D811" s="20"/>
@@ -8680,7 +8821,7 @@
       <c r="I811" s="20"/>
       <c r="K811" s="20"/>
     </row>
-    <row r="812" spans="2:11" ht="13">
+    <row r="812" spans="2:11" ht="12.5">
       <c r="B812" s="20"/>
       <c r="C812" s="20"/>
       <c r="D812" s="20"/>
@@ -8691,7 +8832,7 @@
       <c r="I812" s="20"/>
       <c r="K812" s="20"/>
     </row>
-    <row r="813" spans="2:11" ht="13">
+    <row r="813" spans="2:11" ht="12.5">
       <c r="B813" s="20"/>
       <c r="C813" s="20"/>
       <c r="D813" s="20"/>
@@ -8702,7 +8843,7 @@
       <c r="I813" s="20"/>
       <c r="K813" s="20"/>
     </row>
-    <row r="814" spans="2:11" ht="13">
+    <row r="814" spans="2:11" ht="12.5">
       <c r="B814" s="20"/>
       <c r="C814" s="20"/>
       <c r="D814" s="20"/>
@@ -8713,7 +8854,7 @@
       <c r="I814" s="20"/>
       <c r="K814" s="20"/>
     </row>
-    <row r="815" spans="2:11" ht="13">
+    <row r="815" spans="2:11" ht="12.5">
       <c r="B815" s="20"/>
       <c r="C815" s="20"/>
       <c r="D815" s="20"/>
@@ -8724,7 +8865,7 @@
       <c r="I815" s="20"/>
       <c r="K815" s="20"/>
     </row>
-    <row r="816" spans="2:11" ht="13">
+    <row r="816" spans="2:11" ht="12.5">
       <c r="B816" s="20"/>
       <c r="C816" s="20"/>
       <c r="D816" s="20"/>
@@ -8735,7 +8876,7 @@
       <c r="I816" s="20"/>
       <c r="K816" s="20"/>
     </row>
-    <row r="817" spans="2:11" ht="13">
+    <row r="817" spans="2:11" ht="12.5">
       <c r="B817" s="20"/>
       <c r="C817" s="20"/>
       <c r="D817" s="20"/>
@@ -8746,7 +8887,7 @@
       <c r="I817" s="20"/>
       <c r="K817" s="20"/>
     </row>
-    <row r="818" spans="2:11" ht="13">
+    <row r="818" spans="2:11" ht="12.5">
       <c r="B818" s="20"/>
       <c r="C818" s="20"/>
       <c r="D818" s="20"/>
@@ -8757,7 +8898,7 @@
       <c r="I818" s="20"/>
       <c r="K818" s="20"/>
     </row>
-    <row r="819" spans="2:11" ht="13">
+    <row r="819" spans="2:11" ht="12.5">
       <c r="B819" s="20"/>
       <c r="C819" s="20"/>
       <c r="D819" s="20"/>
@@ -8768,7 +8909,7 @@
       <c r="I819" s="20"/>
       <c r="K819" s="20"/>
     </row>
-    <row r="820" spans="2:11" ht="13">
+    <row r="820" spans="2:11" ht="12.5">
       <c r="B820" s="20"/>
       <c r="C820" s="20"/>
       <c r="D820" s="20"/>
@@ -8779,7 +8920,7 @@
       <c r="I820" s="20"/>
       <c r="K820" s="20"/>
     </row>
-    <row r="821" spans="2:11" ht="13">
+    <row r="821" spans="2:11" ht="12.5">
       <c r="B821" s="20"/>
       <c r="C821" s="20"/>
       <c r="D821" s="20"/>
@@ -8790,7 +8931,7 @@
       <c r="I821" s="20"/>
       <c r="K821" s="20"/>
     </row>
-    <row r="822" spans="2:11" ht="13">
+    <row r="822" spans="2:11" ht="12.5">
       <c r="B822" s="20"/>
       <c r="C822" s="20"/>
       <c r="D822" s="20"/>
@@ -8801,7 +8942,7 @@
       <c r="I822" s="20"/>
       <c r="K822" s="20"/>
     </row>
-    <row r="823" spans="2:11" ht="13">
+    <row r="823" spans="2:11" ht="12.5">
       <c r="B823" s="20"/>
       <c r="C823" s="20"/>
       <c r="D823" s="20"/>
@@ -8812,7 +8953,7 @@
       <c r="I823" s="20"/>
       <c r="K823" s="20"/>
     </row>
-    <row r="824" spans="2:11" ht="13">
+    <row r="824" spans="2:11" ht="12.5">
       <c r="B824" s="20"/>
       <c r="C824" s="20"/>
       <c r="D824" s="20"/>
@@ -8823,7 +8964,7 @@
       <c r="I824" s="20"/>
       <c r="K824" s="20"/>
     </row>
-    <row r="825" spans="2:11" ht="13">
+    <row r="825" spans="2:11" ht="12.5">
       <c r="B825" s="20"/>
       <c r="C825" s="20"/>
       <c r="D825" s="20"/>
@@ -8834,7 +8975,7 @@
       <c r="I825" s="20"/>
       <c r="K825" s="20"/>
     </row>
-    <row r="826" spans="2:11" ht="13">
+    <row r="826" spans="2:11" ht="12.5">
       <c r="B826" s="20"/>
       <c r="C826" s="20"/>
       <c r="D826" s="20"/>
@@ -8845,7 +8986,7 @@
       <c r="I826" s="20"/>
       <c r="K826" s="20"/>
     </row>
-    <row r="827" spans="2:11" ht="13">
+    <row r="827" spans="2:11" ht="12.5">
       <c r="B827" s="20"/>
       <c r="C827" s="20"/>
       <c r="D827" s="20"/>
@@ -8856,7 +8997,7 @@
       <c r="I827" s="20"/>
       <c r="K827" s="20"/>
     </row>
-    <row r="828" spans="2:11" ht="13">
+    <row r="828" spans="2:11" ht="12.5">
       <c r="B828" s="20"/>
       <c r="C828" s="20"/>
       <c r="D828" s="20"/>
@@ -8867,7 +9008,7 @@
       <c r="I828" s="20"/>
       <c r="K828" s="20"/>
     </row>
-    <row r="829" spans="2:11" ht="13">
+    <row r="829" spans="2:11" ht="12.5">
       <c r="B829" s="20"/>
       <c r="C829" s="20"/>
       <c r="D829" s="20"/>
@@ -8878,7 +9019,7 @@
       <c r="I829" s="20"/>
       <c r="K829" s="20"/>
     </row>
-    <row r="830" spans="2:11" ht="13">
+    <row r="830" spans="2:11" ht="12.5">
       <c r="B830" s="20"/>
       <c r="C830" s="20"/>
       <c r="D830" s="20"/>
@@ -8889,7 +9030,7 @@
       <c r="I830" s="20"/>
       <c r="K830" s="20"/>
     </row>
-    <row r="831" spans="2:11" ht="13">
+    <row r="831" spans="2:11" ht="12.5">
       <c r="B831" s="20"/>
       <c r="C831" s="20"/>
       <c r="D831" s="20"/>
@@ -8900,7 +9041,7 @@
       <c r="I831" s="20"/>
       <c r="K831" s="20"/>
     </row>
-    <row r="832" spans="2:11" ht="13">
+    <row r="832" spans="2:11" ht="12.5">
       <c r="B832" s="20"/>
       <c r="C832" s="20"/>
       <c r="D832" s="20"/>
@@ -8911,7 +9052,7 @@
       <c r="I832" s="20"/>
       <c r="K832" s="20"/>
     </row>
-    <row r="833" spans="2:11" ht="13">
+    <row r="833" spans="2:11" ht="12.5">
       <c r="B833" s="20"/>
       <c r="C833" s="20"/>
       <c r="D833" s="20"/>
@@ -8922,7 +9063,7 @@
       <c r="I833" s="20"/>
       <c r="K833" s="20"/>
     </row>
-    <row r="834" spans="2:11" ht="13">
+    <row r="834" spans="2:11" ht="12.5">
       <c r="B834" s="20"/>
       <c r="C834" s="20"/>
       <c r="D834" s="20"/>
@@ -8933,7 +9074,7 @@
       <c r="I834" s="20"/>
       <c r="K834" s="20"/>
     </row>
-    <row r="835" spans="2:11" ht="13">
+    <row r="835" spans="2:11" ht="12.5">
       <c r="B835" s="20"/>
       <c r="C835" s="20"/>
       <c r="D835" s="20"/>
@@ -8944,7 +9085,7 @@
       <c r="I835" s="20"/>
       <c r="K835" s="20"/>
     </row>
-    <row r="836" spans="2:11" ht="13">
+    <row r="836" spans="2:11" ht="12.5">
       <c r="B836" s="20"/>
       <c r="C836" s="20"/>
       <c r="D836" s="20"/>
@@ -8955,7 +9096,7 @@
       <c r="I836" s="20"/>
       <c r="K836" s="20"/>
     </row>
-    <row r="837" spans="2:11" ht="13">
+    <row r="837" spans="2:11" ht="12.5">
       <c r="B837" s="20"/>
       <c r="C837" s="20"/>
       <c r="D837" s="20"/>
@@ -8966,7 +9107,7 @@
       <c r="I837" s="20"/>
       <c r="K837" s="20"/>
     </row>
-    <row r="838" spans="2:11" ht="13">
+    <row r="838" spans="2:11" ht="12.5">
       <c r="B838" s="20"/>
       <c r="C838" s="20"/>
       <c r="D838" s="20"/>
@@ -8977,7 +9118,7 @@
       <c r="I838" s="20"/>
       <c r="K838" s="20"/>
     </row>
-    <row r="839" spans="2:11" ht="13">
+    <row r="839" spans="2:11" ht="12.5">
       <c r="B839" s="20"/>
       <c r="C839" s="20"/>
       <c r="D839" s="20"/>
@@ -8988,7 +9129,7 @@
       <c r="I839" s="20"/>
       <c r="K839" s="20"/>
     </row>
-    <row r="840" spans="2:11" ht="13">
+    <row r="840" spans="2:11" ht="12.5">
       <c r="B840" s="20"/>
       <c r="C840" s="20"/>
       <c r="D840" s="20"/>
@@ -8999,7 +9140,7 @@
       <c r="I840" s="20"/>
       <c r="K840" s="20"/>
     </row>
-    <row r="841" spans="2:11" ht="13">
+    <row r="841" spans="2:11" ht="12.5">
       <c r="B841" s="20"/>
       <c r="C841" s="20"/>
       <c r="D841" s="20"/>
@@ -9010,7 +9151,7 @@
       <c r="I841" s="20"/>
       <c r="K841" s="20"/>
     </row>
-    <row r="842" spans="2:11" ht="13">
+    <row r="842" spans="2:11" ht="12.5">
       <c r="B842" s="20"/>
       <c r="C842" s="20"/>
       <c r="D842" s="20"/>
@@ -9021,7 +9162,7 @@
       <c r="I842" s="20"/>
       <c r="K842" s="20"/>
     </row>
-    <row r="843" spans="2:11" ht="13">
+    <row r="843" spans="2:11" ht="12.5">
       <c r="B843" s="20"/>
       <c r="C843" s="20"/>
       <c r="D843" s="20"/>
@@ -9032,7 +9173,7 @@
       <c r="I843" s="20"/>
       <c r="K843" s="20"/>
     </row>
-    <row r="844" spans="2:11" ht="13">
+    <row r="844" spans="2:11" ht="12.5">
       <c r="B844" s="20"/>
       <c r="C844" s="20"/>
       <c r="D844" s="20"/>
@@ -9043,7 +9184,7 @@
       <c r="I844" s="20"/>
       <c r="K844" s="20"/>
     </row>
-    <row r="845" spans="2:11" ht="13">
+    <row r="845" spans="2:11" ht="12.5">
       <c r="B845" s="20"/>
       <c r="C845" s="20"/>
       <c r="D845" s="20"/>
@@ -9054,7 +9195,7 @@
       <c r="I845" s="20"/>
       <c r="K845" s="20"/>
     </row>
-    <row r="846" spans="2:11" ht="13">
+    <row r="846" spans="2:11" ht="12.5">
       <c r="B846" s="20"/>
       <c r="C846" s="20"/>
       <c r="D846" s="20"/>
@@ -9065,7 +9206,7 @@
       <c r="I846" s="20"/>
       <c r="K846" s="20"/>
     </row>
-    <row r="847" spans="2:11" ht="13">
+    <row r="847" spans="2:11" ht="12.5">
       <c r="B847" s="20"/>
       <c r="C847" s="20"/>
       <c r="D847" s="20"/>
@@ -9076,7 +9217,7 @@
       <c r="I847" s="20"/>
       <c r="K847" s="20"/>
     </row>
-    <row r="848" spans="2:11" ht="13">
+    <row r="848" spans="2:11" ht="12.5">
       <c r="B848" s="20"/>
       <c r="C848" s="20"/>
       <c r="D848" s="20"/>
@@ -9087,7 +9228,7 @@
       <c r="I848" s="20"/>
       <c r="K848" s="20"/>
     </row>
-    <row r="849" spans="2:11" ht="13">
+    <row r="849" spans="2:11" ht="12.5">
       <c r="B849" s="20"/>
       <c r="C849" s="20"/>
       <c r="D849" s="20"/>
@@ -9098,7 +9239,7 @@
       <c r="I849" s="20"/>
       <c r="K849" s="20"/>
     </row>
-    <row r="850" spans="2:11" ht="13">
+    <row r="850" spans="2:11" ht="12.5">
       <c r="B850" s="20"/>
       <c r="C850" s="20"/>
       <c r="D850" s="20"/>
@@ -9109,7 +9250,7 @@
       <c r="I850" s="20"/>
       <c r="K850" s="20"/>
     </row>
-    <row r="851" spans="2:11" ht="13">
+    <row r="851" spans="2:11" ht="12.5">
       <c r="B851" s="20"/>
       <c r="C851" s="20"/>
       <c r="D851" s="20"/>
@@ -9120,7 +9261,7 @@
       <c r="I851" s="20"/>
       <c r="K851" s="20"/>
     </row>
-    <row r="852" spans="2:11" ht="13">
+    <row r="852" spans="2:11" ht="12.5">
       <c r="B852" s="20"/>
       <c r="C852" s="20"/>
       <c r="D852" s="20"/>
@@ -9131,7 +9272,7 @@
       <c r="I852" s="20"/>
       <c r="K852" s="20"/>
     </row>
-    <row r="853" spans="2:11" ht="13">
+    <row r="853" spans="2:11" ht="12.5">
       <c r="B853" s="20"/>
       <c r="C853" s="20"/>
       <c r="D853" s="20"/>
@@ -9142,7 +9283,7 @@
       <c r="I853" s="20"/>
       <c r="K853" s="20"/>
     </row>
-    <row r="854" spans="2:11" ht="13">
+    <row r="854" spans="2:11" ht="12.5">
       <c r="B854" s="20"/>
       <c r="C854" s="20"/>
       <c r="D854" s="20"/>
@@ -9153,7 +9294,7 @@
       <c r="I854" s="20"/>
       <c r="K854" s="20"/>
     </row>
-    <row r="855" spans="2:11" ht="13">
+    <row r="855" spans="2:11" ht="12.5">
       <c r="B855" s="20"/>
       <c r="C855" s="20"/>
       <c r="D855" s="20"/>
@@ -9164,7 +9305,7 @@
       <c r="I855" s="20"/>
       <c r="K855" s="20"/>
     </row>
-    <row r="856" spans="2:11" ht="13">
+    <row r="856" spans="2:11" ht="12.5">
       <c r="B856" s="20"/>
       <c r="C856" s="20"/>
       <c r="D856" s="20"/>
@@ -9175,7 +9316,7 @@
       <c r="I856" s="20"/>
       <c r="K856" s="20"/>
     </row>
-    <row r="857" spans="2:11" ht="13">
+    <row r="857" spans="2:11" ht="12.5">
       <c r="B857" s="20"/>
       <c r="C857" s="20"/>
       <c r="D857" s="20"/>
@@ -9186,7 +9327,7 @@
       <c r="I857" s="20"/>
       <c r="K857" s="20"/>
     </row>
-    <row r="858" spans="2:11" ht="13">
+    <row r="858" spans="2:11" ht="12.5">
       <c r="B858" s="20"/>
       <c r="C858" s="20"/>
       <c r="D858" s="20"/>
@@ -9197,7 +9338,7 @@
       <c r="I858" s="20"/>
       <c r="K858" s="20"/>
     </row>
-    <row r="859" spans="2:11" ht="13">
+    <row r="859" spans="2:11" ht="12.5">
       <c r="B859" s="20"/>
       <c r="C859" s="20"/>
       <c r="D859" s="20"/>
@@ -9208,7 +9349,7 @@
       <c r="I859" s="20"/>
       <c r="K859" s="20"/>
     </row>
-    <row r="860" spans="2:11" ht="13">
+    <row r="860" spans="2:11" ht="12.5">
       <c r="B860" s="20"/>
       <c r="C860" s="20"/>
       <c r="D860" s="20"/>
@@ -9219,7 +9360,7 @@
       <c r="I860" s="20"/>
       <c r="K860" s="20"/>
     </row>
-    <row r="861" spans="2:11" ht="13">
+    <row r="861" spans="2:11" ht="12.5">
       <c r="B861" s="20"/>
       <c r="C861" s="20"/>
       <c r="D861" s="20"/>
@@ -9230,7 +9371,7 @@
       <c r="I861" s="20"/>
       <c r="K861" s="20"/>
     </row>
-    <row r="862" spans="2:11" ht="13">
+    <row r="862" spans="2:11" ht="12.5">
       <c r="B862" s="20"/>
       <c r="C862" s="20"/>
       <c r="D862" s="20"/>
@@ -9241,7 +9382,7 @@
       <c r="I862" s="20"/>
       <c r="K862" s="20"/>
     </row>
-    <row r="863" spans="2:11" ht="13">
+    <row r="863" spans="2:11" ht="12.5">
       <c r="B863" s="20"/>
       <c r="C863" s="20"/>
       <c r="D863" s="20"/>
@@ -9252,7 +9393,7 @@
       <c r="I863" s="20"/>
       <c r="K863" s="20"/>
     </row>
-    <row r="864" spans="2:11" ht="13">
+    <row r="864" spans="2:11" ht="12.5">
       <c r="B864" s="20"/>
       <c r="C864" s="20"/>
       <c r="D864" s="20"/>
@@ -9263,7 +9404,7 @@
       <c r="I864" s="20"/>
       <c r="K864" s="20"/>
     </row>
-    <row r="865" spans="2:11" ht="13">
+    <row r="865" spans="2:11" ht="12.5">
       <c r="B865" s="20"/>
       <c r="C865" s="20"/>
       <c r="D865" s="20"/>
@@ -9274,7 +9415,7 @@
       <c r="I865" s="20"/>
       <c r="K865" s="20"/>
     </row>
-    <row r="866" spans="2:11" ht="13">
+    <row r="866" spans="2:11" ht="12.5">
       <c r="B866" s="20"/>
       <c r="C866" s="20"/>
       <c r="D866" s="20"/>
@@ -9285,7 +9426,7 @@
       <c r="I866" s="20"/>
       <c r="K866" s="20"/>
     </row>
-    <row r="867" spans="2:11" ht="13">
+    <row r="867" spans="2:11" ht="12.5">
       <c r="B867" s="20"/>
       <c r="C867" s="20"/>
       <c r="D867" s="20"/>
@@ -9296,7 +9437,7 @@
       <c r="I867" s="20"/>
       <c r="K867" s="20"/>
     </row>
-    <row r="868" spans="2:11" ht="13">
+    <row r="868" spans="2:11" ht="12.5">
       <c r="B868" s="20"/>
       <c r="C868" s="20"/>
       <c r="D868" s="20"/>
@@ -9307,7 +9448,7 @@
       <c r="I868" s="20"/>
       <c r="K868" s="20"/>
     </row>
-    <row r="869" spans="2:11" ht="13">
+    <row r="869" spans="2:11" ht="12.5">
       <c r="B869" s="20"/>
       <c r="C869" s="20"/>
       <c r="D869" s="20"/>
@@ -9318,7 +9459,7 @@
       <c r="I869" s="20"/>
       <c r="K869" s="20"/>
     </row>
-    <row r="870" spans="2:11" ht="13">
+    <row r="870" spans="2:11" ht="12.5">
       <c r="B870" s="20"/>
       <c r="C870" s="20"/>
       <c r="D870" s="20"/>
@@ -9329,7 +9470,7 @@
       <c r="I870" s="20"/>
       <c r="K870" s="20"/>
     </row>
-    <row r="871" spans="2:11" ht="13">
+    <row r="871" spans="2:11" ht="12.5">
       <c r="B871" s="20"/>
       <c r="C871" s="20"/>
       <c r="D871" s="20"/>
@@ -9340,7 +9481,7 @@
       <c r="I871" s="20"/>
       <c r="K871" s="20"/>
     </row>
-    <row r="872" spans="2:11" ht="13">
+    <row r="872" spans="2:11" ht="12.5">
       <c r="B872" s="20"/>
       <c r="C872" s="20"/>
       <c r="D872" s="20"/>
@@ -9351,7 +9492,7 @@
       <c r="I872" s="20"/>
       <c r="K872" s="20"/>
     </row>
-    <row r="873" spans="2:11" ht="13">
+    <row r="873" spans="2:11" ht="12.5">
       <c r="B873" s="20"/>
       <c r="C873" s="20"/>
       <c r="D873" s="20"/>
@@ -9362,7 +9503,7 @@
       <c r="I873" s="20"/>
       <c r="K873" s="20"/>
     </row>
-    <row r="874" spans="2:11" ht="13">
+    <row r="874" spans="2:11" ht="12.5">
       <c r="B874" s="20"/>
       <c r="C874" s="20"/>
       <c r="D874" s="20"/>
@@ -9373,7 +9514,7 @@
       <c r="I874" s="20"/>
       <c r="K874" s="20"/>
     </row>
-    <row r="875" spans="2:11" ht="13">
+    <row r="875" spans="2:11" ht="12.5">
       <c r="B875" s="20"/>
       <c r="C875" s="20"/>
       <c r="D875" s="20"/>
@@ -9384,7 +9525,7 @@
       <c r="I875" s="20"/>
       <c r="K875" s="20"/>
     </row>
-    <row r="876" spans="2:11" ht="13">
+    <row r="876" spans="2:11" ht="12.5">
       <c r="B876" s="20"/>
       <c r="C876" s="20"/>
       <c r="D876" s="20"/>
@@ -9395,7 +9536,7 @@
       <c r="I876" s="20"/>
       <c r="K876" s="20"/>
     </row>
-    <row r="877" spans="2:11" ht="13">
+    <row r="877" spans="2:11" ht="12.5">
       <c r="B877" s="20"/>
       <c r="C877" s="20"/>
       <c r="D877" s="20"/>
@@ -9406,7 +9547,7 @@
       <c r="I877" s="20"/>
       <c r="K877" s="20"/>
     </row>
-    <row r="878" spans="2:11" ht="13">
+    <row r="878" spans="2:11" ht="12.5">
       <c r="B878" s="20"/>
       <c r="C878" s="20"/>
       <c r="D878" s="20"/>
@@ -9417,7 +9558,7 @@
       <c r="I878" s="20"/>
       <c r="K878" s="20"/>
     </row>
-    <row r="879" spans="2:11" ht="13">
+    <row r="879" spans="2:11" ht="12.5">
       <c r="B879" s="20"/>
       <c r="C879" s="20"/>
       <c r="D879" s="20"/>
@@ -9428,7 +9569,7 @@
       <c r="I879" s="20"/>
       <c r="K879" s="20"/>
     </row>
-    <row r="880" spans="2:11" ht="13">
+    <row r="880" spans="2:11" ht="12.5">
       <c r="B880" s="20"/>
       <c r="C880" s="20"/>
       <c r="D880" s="20"/>
@@ -9439,7 +9580,7 @@
       <c r="I880" s="20"/>
       <c r="K880" s="20"/>
     </row>
-    <row r="881" spans="2:11" ht="13">
+    <row r="881" spans="2:11" ht="12.5">
       <c r="B881" s="20"/>
       <c r="C881" s="20"/>
       <c r="D881" s="20"/>
@@ -9450,7 +9591,7 @@
       <c r="I881" s="20"/>
       <c r="K881" s="20"/>
     </row>
-    <row r="882" spans="2:11" ht="13">
+    <row r="882" spans="2:11" ht="12.5">
       <c r="B882" s="20"/>
       <c r="C882" s="20"/>
       <c r="D882" s="20"/>
@@ -9461,7 +9602,7 @@
       <c r="I882" s="20"/>
       <c r="K882" s="20"/>
     </row>
-    <row r="883" spans="2:11" ht="13">
+    <row r="883" spans="2:11" ht="12.5">
       <c r="B883" s="20"/>
       <c r="C883" s="20"/>
       <c r="D883" s="20"/>
@@ -9472,7 +9613,7 @@
       <c r="I883" s="20"/>
       <c r="K883" s="20"/>
     </row>
-    <row r="884" spans="2:11" ht="13">
+    <row r="884" spans="2:11" ht="12.5">
       <c r="B884" s="20"/>
       <c r="C884" s="20"/>
       <c r="D884" s="20"/>
@@ -9483,7 +9624,7 @@
       <c r="I884" s="20"/>
       <c r="K884" s="20"/>
     </row>
-    <row r="885" spans="2:11" ht="13">
+    <row r="885" spans="2:11" ht="12.5">
       <c r="B885" s="20"/>
       <c r="C885" s="20"/>
       <c r="D885" s="20"/>
@@ -9494,7 +9635,7 @@
       <c r="I885" s="20"/>
       <c r="K885" s="20"/>
     </row>
-    <row r="886" spans="2:11" ht="13">
+    <row r="886" spans="2:11" ht="12.5">
       <c r="B886" s="20"/>
       <c r="C886" s="20"/>
       <c r="D886" s="20"/>
@@ -9505,7 +9646,7 @@
       <c r="I886" s="20"/>
       <c r="K886" s="20"/>
     </row>
-    <row r="887" spans="2:11" ht="13">
+    <row r="887" spans="2:11" ht="12.5">
       <c r="B887" s="20"/>
       <c r="C887" s="20"/>
       <c r="D887" s="20"/>
@@ -9516,7 +9657,7 @@
       <c r="I887" s="20"/>
       <c r="K887" s="20"/>
     </row>
-    <row r="888" spans="2:11" ht="13">
+    <row r="888" spans="2:11" ht="12.5">
       <c r="B888" s="20"/>
       <c r="C888" s="20"/>
       <c r="D888" s="20"/>
@@ -9527,7 +9668,7 @@
       <c r="I888" s="20"/>
       <c r="K888" s="20"/>
     </row>
-    <row r="889" spans="2:11" ht="13">
+    <row r="889" spans="2:11" ht="12.5">
       <c r="B889" s="20"/>
       <c r="C889" s="20"/>
       <c r="D889" s="20"/>
@@ -9538,7 +9679,7 @@
       <c r="I889" s="20"/>
       <c r="K889" s="20"/>
     </row>
-    <row r="890" spans="2:11" ht="13">
+    <row r="890" spans="2:11" ht="12.5">
       <c r="B890" s="20"/>
       <c r="C890" s="20"/>
       <c r="D890" s="20"/>
@@ -9549,7 +9690,7 @@
       <c r="I890" s="20"/>
       <c r="K890" s="20"/>
     </row>
-    <row r="891" spans="2:11" ht="13">
+    <row r="891" spans="2:11" ht="12.5">
       <c r="B891" s="20"/>
       <c r="C891" s="20"/>
       <c r="D891" s="20"/>
@@ -9560,7 +9701,7 @@
       <c r="I891" s="20"/>
       <c r="K891" s="20"/>
     </row>
-    <row r="892" spans="2:11" ht="13">
+    <row r="892" spans="2:11" ht="12.5">
       <c r="B892" s="20"/>
       <c r="C892" s="20"/>
       <c r="D892" s="20"/>
@@ -9571,7 +9712,7 @@
       <c r="I892" s="20"/>
       <c r="K892" s="20"/>
     </row>
-    <row r="893" spans="2:11" ht="13">
+    <row r="893" spans="2:11" ht="12.5">
       <c r="B893" s="20"/>
       <c r="C893" s="20"/>
       <c r="D893" s="20"/>
@@ -9582,7 +9723,7 @@
       <c r="I893" s="20"/>
       <c r="K893" s="20"/>
     </row>
-    <row r="894" spans="2:11" ht="13">
+    <row r="894" spans="2:11" ht="12.5">
       <c r="B894" s="20"/>
       <c r="C894" s="20"/>
       <c r="D894" s="20"/>
@@ -9593,7 +9734,7 @@
       <c r="I894" s="20"/>
       <c r="K894" s="20"/>
     </row>
-    <row r="895" spans="2:11" ht="13">
+    <row r="895" spans="2:11" ht="12.5">
       <c r="B895" s="20"/>
       <c r="C895" s="20"/>
       <c r="D895" s="20"/>
@@ -9604,7 +9745,7 @@
       <c r="I895" s="20"/>
       <c r="K895" s="20"/>
     </row>
-    <row r="896" spans="2:11" ht="13">
+    <row r="896" spans="2:11" ht="12.5">
       <c r="B896" s="20"/>
       <c r="C896" s="20"/>
       <c r="D896" s="20"/>
@@ -9615,7 +9756,7 @@
       <c r="I896" s="20"/>
       <c r="K896" s="20"/>
     </row>
-    <row r="897" spans="2:11" ht="13">
+    <row r="897" spans="2:11" ht="12.5">
       <c r="B897" s="20"/>
       <c r="C897" s="20"/>
       <c r="D897" s="20"/>
@@ -9626,7 +9767,7 @@
       <c r="I897" s="20"/>
       <c r="K897" s="20"/>
     </row>
-    <row r="898" spans="2:11" ht="13">
+    <row r="898" spans="2:11" ht="12.5">
       <c r="B898" s="20"/>
       <c r="C898" s="20"/>
       <c r="D898" s="20"/>
@@ -9637,7 +9778,7 @@
       <c r="I898" s="20"/>
       <c r="K898" s="20"/>
     </row>
-    <row r="899" spans="2:11" ht="13">
+    <row r="899" spans="2:11" ht="12.5">
       <c r="B899" s="20"/>
       <c r="C899" s="20"/>
       <c r="D899" s="20"/>
@@ -9648,7 +9789,7 @@
       <c r="I899" s="20"/>
       <c r="K899" s="20"/>
     </row>
-    <row r="900" spans="2:11" ht="13">
+    <row r="900" spans="2:11" ht="12.5">
       <c r="B900" s="20"/>
       <c r="C900" s="20"/>
       <c r="D900" s="20"/>
@@ -9659,7 +9800,7 @@
       <c r="I900" s="20"/>
       <c r="K900" s="20"/>
     </row>
-    <row r="901" spans="2:11" ht="13">
+    <row r="901" spans="2:11" ht="12.5">
       <c r="B901" s="20"/>
       <c r="C901" s="20"/>
       <c r="D901" s="20"/>
@@ -9670,7 +9811,7 @@
       <c r="I901" s="20"/>
       <c r="K901" s="20"/>
     </row>
-    <row r="902" spans="2:11" ht="13">
+    <row r="902" spans="2:11" ht="12.5">
       <c r="B902" s="20"/>
       <c r="C902" s="20"/>
       <c r="D902" s="20"/>
@@ -9681,7 +9822,7 @@
       <c r="I902" s="20"/>
       <c r="K902" s="20"/>
     </row>
-    <row r="903" spans="2:11" ht="13">
+    <row r="903" spans="2:11" ht="12.5">
       <c r="B903" s="20"/>
       <c r="C903" s="20"/>
       <c r="D903" s="20"/>
@@ -9692,7 +9833,7 @@
       <c r="I903" s="20"/>
       <c r="K903" s="20"/>
     </row>
-    <row r="904" spans="2:11" ht="13">
+    <row r="904" spans="2:11" ht="12.5">
       <c r="B904" s="20"/>
       <c r="C904" s="20"/>
       <c r="D904" s="20"/>
@@ -9703,7 +9844,7 @@
       <c r="I904" s="20"/>
       <c r="K904" s="20"/>
     </row>
-    <row r="905" spans="2:11" ht="13">
+    <row r="905" spans="2:11" ht="12.5">
       <c r="B905" s="20"/>
       <c r="C905" s="20"/>
       <c r="D905" s="20"/>
@@ -9714,7 +9855,7 @@
       <c r="I905" s="20"/>
       <c r="K905" s="20"/>
     </row>
-    <row r="906" spans="2:11" ht="13">
+    <row r="906" spans="2:11" ht="12.5">
       <c r="B906" s="20"/>
       <c r="C906" s="20"/>
       <c r="D906" s="20"/>
@@ -9725,7 +9866,7 @@
       <c r="I906" s="20"/>
       <c r="K906" s="20"/>
     </row>
-    <row r="907" spans="2:11" ht="13">
+    <row r="907" spans="2:11" ht="12.5">
       <c r="B907" s="20"/>
       <c r="C907" s="20"/>
       <c r="D907" s="20"/>
@@ -9736,7 +9877,7 @@
       <c r="I907" s="20"/>
       <c r="K907" s="20"/>
     </row>
-    <row r="908" spans="2:11" ht="13">
+    <row r="908" spans="2:11" ht="12.5">
       <c r="B908" s="20"/>
       <c r="C908" s="20"/>
       <c r="D908" s="20"/>
@@ -9747,7 +9888,7 @@
       <c r="I908" s="20"/>
       <c r="K908" s="20"/>
     </row>
-    <row r="909" spans="2:11" ht="13">
+    <row r="909" spans="2:11" ht="12.5">
       <c r="B909" s="20"/>
       <c r="C909" s="20"/>
       <c r="D909" s="20"/>
@@ -9758,7 +9899,7 @@
       <c r="I909" s="20"/>
       <c r="K909" s="20"/>
     </row>
-    <row r="910" spans="2:11" ht="13">
+    <row r="910" spans="2:11" ht="12.5">
       <c r="B910" s="20"/>
       <c r="C910" s="20"/>
       <c r="D910" s="20"/>
@@ -9769,7 +9910,7 @@
       <c r="I910" s="20"/>
       <c r="K910" s="20"/>
     </row>
-    <row r="911" spans="2:11" ht="13">
+    <row r="911" spans="2:11" ht="12.5">
       <c r="B911" s="20"/>
       <c r="C911" s="20"/>
       <c r="D911" s="20"/>
@@ -9780,7 +9921,7 @@
       <c r="I911" s="20"/>
       <c r="K911" s="20"/>
     </row>
-    <row r="912" spans="2:11" ht="13">
+    <row r="912" spans="2:11" ht="12.5">
       <c r="B912" s="20"/>
       <c r="C912" s="20"/>
       <c r="D912" s="20"/>
@@ -9791,7 +9932,7 @@
       <c r="I912" s="20"/>
       <c r="K912" s="20"/>
     </row>
-    <row r="913" spans="2:11" ht="13">
+    <row r="913" spans="2:11" ht="12.5">
       <c r="B913" s="20"/>
       <c r="C913" s="20"/>
       <c r="D913" s="20"/>
@@ -9802,7 +9943,7 @@
       <c r="I913" s="20"/>
       <c r="K913" s="20"/>
     </row>
-    <row r="914" spans="2:11" ht="13">
+    <row r="914" spans="2:11" ht="12.5">
       <c r="B914" s="20"/>
       <c r="C914" s="20"/>
       <c r="D914" s="20"/>
@@ -9813,7 +9954,7 @@
       <c r="I914" s="20"/>
       <c r="K914" s="20"/>
     </row>
-    <row r="915" spans="2:11" ht="13">
+    <row r="915" spans="2:11" ht="12.5">
       <c r="B915" s="20"/>
       <c r="C915" s="20"/>
       <c r="D915" s="20"/>
@@ -9824,7 +9965,7 @@
       <c r="I915" s="20"/>
       <c r="K915" s="20"/>
     </row>
-    <row r="916" spans="2:11" ht="13">
+    <row r="916" spans="2:11" ht="12.5">
       <c r="B916" s="20"/>
       <c r="C916" s="20"/>
       <c r="D916" s="20"/>
@@ -9835,7 +9976,7 @@
       <c r="I916" s="20"/>
       <c r="K916" s="20"/>
     </row>
-    <row r="917" spans="2:11" ht="13">
+    <row r="917" spans="2:11" ht="12.5">
       <c r="B917" s="20"/>
       <c r="C917" s="20"/>
       <c r="D917" s="20"/>
@@ -9846,7 +9987,7 @@
       <c r="I917" s="20"/>
       <c r="K917" s="20"/>
     </row>
-    <row r="918" spans="2:11" ht="13">
+    <row r="918" spans="2:11" ht="12.5">
       <c r="B918" s="20"/>
       <c r="C918" s="20"/>
       <c r="D918" s="20"/>
@@ -9857,7 +9998,7 @@
       <c r="I918" s="20"/>
       <c r="K918" s="20"/>
     </row>
-    <row r="919" spans="2:11" ht="13">
+    <row r="919" spans="2:11" ht="12.5">
       <c r="B919" s="20"/>
       <c r="C919" s="20"/>
       <c r="D919" s="20"/>
@@ -9868,7 +10009,7 @@
       <c r="I919" s="20"/>
       <c r="K919" s="20"/>
     </row>
-    <row r="920" spans="2:11" ht="13">
+    <row r="920" spans="2:11" ht="12.5">
       <c r="B920" s="20"/>
       <c r="C920" s="20"/>
       <c r="D920" s="20"/>
@@ -9879,7 +10020,7 @@
       <c r="I920" s="20"/>
       <c r="K920" s="20"/>
     </row>
-    <row r="921" spans="2:11" ht="13">
+    <row r="921" spans="2:11" ht="12.5">
       <c r="B921" s="20"/>
       <c r="C921" s="20"/>
       <c r="D921" s="20"/>
@@ -9890,7 +10031,7 @@
       <c r="I921" s="20"/>
       <c r="K921" s="20"/>
     </row>
-    <row r="922" spans="2:11" ht="13">
+    <row r="922" spans="2:11" ht="12.5">
       <c r="B922" s="20"/>
       <c r="C922" s="20"/>
       <c r="D922" s="20"/>
@@ -9901,7 +10042,7 @@
       <c r="I922" s="20"/>
       <c r="K922" s="20"/>
     </row>
-    <row r="923" spans="2:11" ht="13">
+    <row r="923" spans="2:11" ht="12.5">
       <c r="B923" s="20"/>
       <c r="C923" s="20"/>
       <c r="D923" s="20"/>
@@ -9912,7 +10053,7 @@
       <c r="I923" s="20"/>
       <c r="K923" s="20"/>
     </row>
-    <row r="924" spans="2:11" ht="13">
+    <row r="924" spans="2:11" ht="12.5">
       <c r="B924" s="20"/>
       <c r="C924" s="20"/>
       <c r="D924" s="20"/>
@@ -9923,7 +10064,7 @@
       <c r="I924" s="20"/>
       <c r="K924" s="20"/>
     </row>
-    <row r="925" spans="2:11" ht="13">
+    <row r="925" spans="2:11" ht="12.5">
       <c r="B925" s="20"/>
       <c r="C925" s="20"/>
       <c r="D925" s="20"/>
@@ -9934,7 +10075,7 @@
       <c r="I925" s="20"/>
       <c r="K925" s="20"/>
     </row>
-    <row r="926" spans="2:11" ht="13">
+    <row r="926" spans="2:11" ht="12.5">
       <c r="B926" s="20"/>
       <c r="C926" s="20"/>
       <c r="D926" s="20"/>
@@ -9945,7 +10086,7 @@
       <c r="I926" s="20"/>
       <c r="K926" s="20"/>
     </row>
-    <row r="927" spans="2:11" ht="13">
+    <row r="927" spans="2:11" ht="12.5">
       <c r="B927" s="20"/>
       <c r="C927" s="20"/>
       <c r="D927" s="20"/>
@@ -9956,7 +10097,7 @@
       <c r="I927" s="20"/>
       <c r="K927" s="20"/>
     </row>
-    <row r="928" spans="2:11" ht="13">
+    <row r="928" spans="2:11" ht="12.5">
       <c r="B928" s="20"/>
       <c r="C928" s="20"/>
       <c r="D928" s="20"/>
@@ -9967,7 +10108,7 @@
       <c r="I928" s="20"/>
       <c r="K928" s="20"/>
     </row>
-    <row r="929" spans="2:11" ht="13">
+    <row r="929" spans="2:11" ht="12.5">
       <c r="B929" s="20"/>
       <c r="C929" s="20"/>
       <c r="D929" s="20"/>
@@ -9978,7 +10119,7 @@
       <c r="I929" s="20"/>
       <c r="K929" s="20"/>
     </row>
-    <row r="930" spans="2:11" ht="13">
+    <row r="930" spans="2:11" ht="12.5">
       <c r="B930" s="20"/>
       <c r="C930" s="20"/>
       <c r="D930" s="20"/>
@@ -9989,7 +10130,7 @@
       <c r="I930" s="20"/>
       <c r="K930" s="20"/>
     </row>
-    <row r="931" spans="2:11" ht="13">
+    <row r="931" spans="2:11" ht="12.5">
       <c r="B931" s="20"/>
       <c r="C931" s="20"/>
       <c r="D931" s="20"/>
@@ -10000,7 +10141,7 @@
       <c r="I931" s="20"/>
       <c r="K931" s="20"/>
     </row>
-    <row r="932" spans="2:11" ht="13">
+    <row r="932" spans="2:11" ht="12.5">
       <c r="B932" s="20"/>
       <c r="C932" s="20"/>
       <c r="D932" s="20"/>
@@ -10011,7 +10152,7 @@
       <c r="I932" s="20"/>
       <c r="K932" s="20"/>
     </row>
-    <row r="933" spans="2:11" ht="13">
+    <row r="933" spans="2:11" ht="12.5">
       <c r="B933" s="20"/>
       <c r="C933" s="20"/>
       <c r="D933" s="20"/>
@@ -10022,7 +10163,7 @@
       <c r="I933" s="20"/>
       <c r="K933" s="20"/>
     </row>
-    <row r="934" spans="2:11" ht="13">
+    <row r="934" spans="2:11" ht="12.5">
       <c r="B934" s="20"/>
       <c r="C934" s="20"/>
       <c r="D934" s="20"/>
@@ -10033,7 +10174,7 @@
       <c r="I934" s="20"/>
       <c r="K934" s="20"/>
     </row>
-    <row r="935" spans="2:11" ht="13">
+    <row r="935" spans="2:11" ht="12.5">
       <c r="B935" s="20"/>
       <c r="C935" s="20"/>
       <c r="D935" s="20"/>
@@ -10044,7 +10185,7 @@
       <c r="I935" s="20"/>
       <c r="K935" s="20"/>
     </row>
-    <row r="936" spans="2:11" ht="13">
+    <row r="936" spans="2:11" ht="12.5">
       <c r="B936" s="20"/>
       <c r="C936" s="20"/>
       <c r="D936" s="20"/>
@@ -10055,7 +10196,7 @@
       <c r="I936" s="20"/>
       <c r="K936" s="20"/>
     </row>
-    <row r="937" spans="2:11" ht="13">
+    <row r="937" spans="2:11" ht="12.5">
       <c r="B937" s="20"/>
       <c r="C937" s="20"/>
       <c r="D937" s="20"/>
@@ -10066,7 +10207,7 @@
       <c r="I937" s="20"/>
       <c r="K937" s="20"/>
     </row>
-    <row r="938" spans="2:11" ht="13">
+    <row r="938" spans="2:11" ht="12.5">
       <c r="B938" s="20"/>
       <c r="C938" s="20"/>
       <c r="D938" s="20"/>
@@ -10077,7 +10218,7 @@
       <c r="I938" s="20"/>
       <c r="K938" s="20"/>
     </row>
-    <row r="939" spans="2:11" ht="13">
+    <row r="939" spans="2:11" ht="12.5">
       <c r="B939" s="20"/>
       <c r="C939" s="20"/>
       <c r="D939" s="20"/>
@@ -10088,7 +10229,7 @@
       <c r="I939" s="20"/>
       <c r="K939" s="20"/>
     </row>
-    <row r="940" spans="2:11" ht="13">
+    <row r="940" spans="2:11" ht="12.5">
       <c r="B940" s="20"/>
       <c r="C940" s="20"/>
       <c r="D940" s="20"/>
@@ -10099,7 +10240,7 @@
       <c r="I940" s="20"/>
       <c r="K940" s="20"/>
     </row>
-    <row r="941" spans="2:11" ht="13">
+    <row r="941" spans="2:11" ht="12.5">
       <c r="B941" s="20"/>
       <c r="C941" s="20"/>
       <c r="D941" s="20"/>
@@ -10110,7 +10251,7 @@
       <c r="I941" s="20"/>
       <c r="K941" s="20"/>
     </row>
-    <row r="942" spans="2:11" ht="13">
+    <row r="942" spans="2:11" ht="12.5">
       <c r="B942" s="20"/>
       <c r="C942" s="20"/>
       <c r="D942" s="20"/>
@@ -10121,7 +10262,7 @@
       <c r="I942" s="20"/>
       <c r="K942" s="20"/>
     </row>
-    <row r="943" spans="2:11" ht="13">
+    <row r="943" spans="2:11" ht="12.5">
       <c r="B943" s="20"/>
       <c r="C943" s="20"/>
       <c r="D943" s="20"/>
@@ -10132,7 +10273,7 @@
       <c r="I943" s="20"/>
       <c r="K943" s="20"/>
     </row>
-    <row r="944" spans="2:11" ht="13">
+    <row r="944" spans="2:11" ht="12.5">
       <c r="B944" s="20"/>
       <c r="C944" s="20"/>
       <c r="D944" s="20"/>
@@ -10143,7 +10284,7 @@
       <c r="I944" s="20"/>
       <c r="K944" s="20"/>
     </row>
-    <row r="945" spans="2:11" ht="13">
+    <row r="945" spans="2:11" ht="12.5">
       <c r="B945" s="20"/>
       <c r="C945" s="20"/>
       <c r="D945" s="20"/>
@@ -10154,7 +10295,7 @@
       <c r="I945" s="20"/>
       <c r="K945" s="20"/>
     </row>
-    <row r="946" spans="2:11" ht="13">
+    <row r="946" spans="2:11" ht="12.5">
       <c r="B946" s="20"/>
       <c r="C946" s="20"/>
       <c r="D946" s="20"/>
@@ -10165,7 +10306,7 @@
       <c r="I946" s="20"/>
       <c r="K946" s="20"/>
     </row>
-    <row r="947" spans="2:11" ht="13">
+    <row r="947" spans="2:11" ht="12.5">
       <c r="B947" s="20"/>
       <c r="C947" s="20"/>
       <c r="D947" s="20"/>
@@ -10176,7 +10317,7 @@
       <c r="I947" s="20"/>
       <c r="K947" s="20"/>
     </row>
-    <row r="948" spans="2:11" ht="13">
+    <row r="948" spans="2:11" ht="12.5">
       <c r="B948" s="20"/>
       <c r="C948" s="20"/>
       <c r="D948" s="20"/>
@@ -10187,7 +10328,7 @@
       <c r="I948" s="20"/>
       <c r="K948" s="20"/>
     </row>
-    <row r="949" spans="2:11" ht="13">
+    <row r="949" spans="2:11" ht="12.5">
       <c r="B949" s="20"/>
       <c r="C949" s="20"/>
       <c r="D949" s="20"/>
@@ -10198,7 +10339,7 @@
       <c r="I949" s="20"/>
       <c r="K949" s="20"/>
     </row>
-    <row r="950" spans="2:11" ht="13">
+    <row r="950" spans="2:11" ht="12.5">
       <c r="B950" s="20"/>
       <c r="C950" s="20"/>
       <c r="D950" s="20"/>
@@ -10209,7 +10350,7 @@
       <c r="I950" s="20"/>
       <c r="K950" s="20"/>
     </row>
-    <row r="951" spans="2:11" ht="13">
+    <row r="951" spans="2:11" ht="12.5">
       <c r="B951" s="20"/>
       <c r="C951" s="20"/>
       <c r="D951" s="20"/>
@@ -10220,7 +10361,7 @@
       <c r="I951" s="20"/>
       <c r="K951" s="20"/>
     </row>
-    <row r="952" spans="2:11" ht="13">
+    <row r="952" spans="2:11" ht="12.5">
       <c r="B952" s="20"/>
       <c r="C952" s="20"/>
       <c r="D952" s="20"/>
@@ -10231,7 +10372,7 @@
       <c r="I952" s="20"/>
       <c r="K952" s="20"/>
     </row>
-    <row r="953" spans="2:11" ht="13">
+    <row r="953" spans="2:11" ht="12.5">
       <c r="B953" s="20"/>
       <c r="C953" s="20"/>
       <c r="D953" s="20"/>
@@ -10242,7 +10383,7 @@
       <c r="I953" s="20"/>
       <c r="K953" s="20"/>
     </row>
-    <row r="954" spans="2:11" ht="13">
+    <row r="954" spans="2:11" ht="12.5">
       <c r="B954" s="20"/>
       <c r="C954" s="20"/>
       <c r="D954" s="20"/>
@@ -10253,7 +10394,7 @@
       <c r="I954" s="20"/>
       <c r="K954" s="20"/>
     </row>
-    <row r="955" spans="2:11" ht="13">
+    <row r="955" spans="2:11" ht="12.5">
       <c r="B955" s="20"/>
       <c r="C955" s="20"/>
       <c r="D955" s="20"/>
@@ -10264,7 +10405,7 @@
       <c r="I955" s="20"/>
       <c r="K955" s="20"/>
     </row>
-    <row r="956" spans="2:11" ht="13">
+    <row r="956" spans="2:11" ht="12.5">
       <c r="B956" s="20"/>
       <c r="C956" s="20"/>
       <c r="D956" s="20"/>
@@ -10275,7 +10416,7 @@
       <c r="I956" s="20"/>
       <c r="K956" s="20"/>
     </row>
-    <row r="957" spans="2:11" ht="13">
+    <row r="957" spans="2:11" ht="12.5">
       <c r="B957" s="20"/>
       <c r="C957" s="20"/>
       <c r="D957" s="20"/>
@@ -10286,7 +10427,7 @@
       <c r="I957" s="20"/>
       <c r="K957" s="20"/>
     </row>
-    <row r="958" spans="2:11" ht="13">
+    <row r="958" spans="2:11" ht="12.5">
       <c r="B958" s="20"/>
       <c r="C958" s="20"/>
       <c r="D958" s="20"/>
@@ -10297,7 +10438,7 @@
       <c r="I958" s="20"/>
       <c r="K958" s="20"/>
     </row>
-    <row r="959" spans="2:11" ht="13">
+    <row r="959" spans="2:11" ht="12.5">
       <c r="B959" s="20"/>
       <c r="C959" s="20"/>
       <c r="D959" s="20"/>
@@ -10308,7 +10449,7 @@
       <c r="I959" s="20"/>
       <c r="K959" s="20"/>
     </row>
-    <row r="960" spans="2:11" ht="13">
+    <row r="960" spans="2:11" ht="12.5">
       <c r="B960" s="20"/>
       <c r="C960" s="20"/>
       <c r="D960" s="20"/>
@@ -10319,7 +10460,7 @@
       <c r="I960" s="20"/>
       <c r="K960" s="20"/>
     </row>
-    <row r="961" spans="2:11" ht="13">
+    <row r="961" spans="2:11" ht="12.5">
       <c r="B961" s="20"/>
       <c r="C961" s="20"/>
       <c r="D961" s="20"/>
@@ -10330,7 +10471,7 @@
       <c r="I961" s="20"/>
       <c r="K961" s="20"/>
     </row>
-    <row r="962" spans="2:11" ht="13">
+    <row r="962" spans="2:11" ht="12.5">
       <c r="B962" s="20"/>
       <c r="C962" s="20"/>
       <c r="D962" s="20"/>
@@ -10341,7 +10482,7 @@
       <c r="I962" s="20"/>
       <c r="K962" s="20"/>
     </row>
-    <row r="963" spans="2:11" ht="13">
+    <row r="963" spans="2:11" ht="12.5">
       <c r="B963" s="20"/>
       <c r="C963" s="20"/>
       <c r="D963" s="20"/>
@@ -10352,7 +10493,7 @@
       <c r="I963" s="20"/>
       <c r="K963" s="20"/>
     </row>
-    <row r="964" spans="2:11" ht="13">
+    <row r="964" spans="2:11" ht="12.5">
       <c r="B964" s="20"/>
       <c r="C964" s="20"/>
       <c r="D964" s="20"/>
@@ -10363,7 +10504,7 @@
       <c r="I964" s="20"/>
       <c r="K964" s="20"/>
     </row>
-    <row r="965" spans="2:11" ht="13">
+    <row r="965" spans="2:11" ht="12.5">
       <c r="B965" s="20"/>
       <c r="C965" s="20"/>
       <c r="D965" s="20"/>
@@ -10374,7 +10515,7 @@
       <c r="I965" s="20"/>
       <c r="K965" s="20"/>
     </row>
-    <row r="966" spans="2:11" ht="13">
+    <row r="966" spans="2:11" ht="12.5">
       <c r="B966" s="20"/>
       <c r="C966" s="20"/>
       <c r="D966" s="20"/>
@@ -10385,7 +10526,7 @@
       <c r="I966" s="20"/>
       <c r="K966" s="20"/>
     </row>
-    <row r="967" spans="2:11" ht="13">
+    <row r="967" spans="2:11" ht="12.5">
       <c r="B967" s="20"/>
       <c r="C967" s="20"/>
       <c r="D967" s="20"/>
@@ -10396,7 +10537,7 @@
       <c r="I967" s="20"/>
       <c r="K967" s="20"/>
     </row>
-    <row r="968" spans="2:11" ht="13">
+    <row r="968" spans="2:11" ht="12.5">
       <c r="B968" s="20"/>
       <c r="C968" s="20"/>
       <c r="D968" s="20"/>
@@ -10407,7 +10548,7 @@
       <c r="I968" s="20"/>
       <c r="K968" s="20"/>
     </row>
-    <row r="969" spans="2:11" ht="13">
+    <row r="969" spans="2:11" ht="12.5">
       <c r="B969" s="20"/>
       <c r="C969" s="20"/>
       <c r="D969" s="20"/>
@@ -10418,7 +10559,7 @@
       <c r="I969" s="20"/>
       <c r="K969" s="20"/>
     </row>
-    <row r="970" spans="2:11" ht="13">
+    <row r="970" spans="2:11" ht="12.5">
       <c r="B970" s="20"/>
       <c r="C970" s="20"/>
       <c r="D970" s="20"/>
@@ -10429,7 +10570,7 @@
       <c r="I970" s="20"/>
       <c r="K970" s="20"/>
     </row>
-    <row r="971" spans="2:11" ht="13">
+    <row r="971" spans="2:11" ht="12.5">
       <c r="B971" s="20"/>
       <c r="C971" s="20"/>
       <c r="D971" s="20"/>
@@ -10440,7 +10581,7 @@
       <c r="I971" s="20"/>
       <c r="K971" s="20"/>
     </row>
-    <row r="972" spans="2:11" ht="13">
+    <row r="972" spans="2:11" ht="12.5">
       <c r="B972" s="20"/>
       <c r="C972" s="20"/>
       <c r="D972" s="20"/>
@@ -10451,7 +10592,7 @@
       <c r="I972" s="20"/>
       <c r="K972" s="20"/>
     </row>
-    <row r="973" spans="2:11" ht="13">
+    <row r="973" spans="2:11" ht="12.5">
       <c r="B973" s="20"/>
       <c r="C973" s="20"/>
       <c r="D973" s="20"/>
@@ -10462,7 +10603,7 @@
       <c r="I973" s="20"/>
       <c r="K973" s="20"/>
     </row>
-    <row r="974" spans="2:11" ht="13">
+    <row r="974" spans="2:11" ht="12.5">
       <c r="B974" s="20"/>
       <c r="C974" s="20"/>
       <c r="D974" s="20"/>
@@ -10473,7 +10614,7 @@
       <c r="I974" s="20"/>
       <c r="K974" s="20"/>
     </row>
-    <row r="975" spans="2:11" ht="13">
+    <row r="975" spans="2:11" ht="12.5">
       <c r="B975" s="20"/>
       <c r="C975" s="20"/>
       <c r="D975" s="20"/>
@@ -10484,7 +10625,7 @@
       <c r="I975" s="20"/>
       <c r="K975" s="20"/>
     </row>
-    <row r="976" spans="2:11" ht="13">
+    <row r="976" spans="2:11" ht="12.5">
       <c r="B976" s="20"/>
       <c r="C976" s="20"/>
       <c r="D976" s="20"/>
@@ -10495,7 +10636,7 @@
       <c r="I976" s="20"/>
       <c r="K976" s="20"/>
     </row>
-    <row r="977" spans="2:11" ht="13">
+    <row r="977" spans="2:11" ht="12.5">
       <c r="B977" s="20"/>
       <c r="C977" s="20"/>
       <c r="D977" s="20"/>
@@ -10506,7 +10647,7 @@
       <c r="I977" s="20"/>
       <c r="K977" s="20"/>
     </row>
-    <row r="978" spans="2:11" ht="13">
+    <row r="978" spans="2:11" ht="12.5">
       <c r="B978" s="20"/>
       <c r="C978" s="20"/>
       <c r="D978" s="20"/>
@@ -10517,7 +10658,7 @@
       <c r="I978" s="20"/>
       <c r="K978" s="20"/>
     </row>
-    <row r="979" spans="2:11" ht="13">
+    <row r="979" spans="2:11" ht="12.5">
       <c r="B979" s="20"/>
       <c r="C979" s="20"/>
       <c r="D979" s="20"/>
@@ -10528,7 +10669,7 @@
       <c r="I979" s="20"/>
       <c r="K979" s="20"/>
     </row>
-    <row r="980" spans="2:11" ht="13">
+    <row r="980" spans="2:11" ht="12.5">
       <c r="B980" s="20"/>
       <c r="C980" s="20"/>
       <c r="D980" s="20"/>
@@ -10539,7 +10680,7 @@
       <c r="I980" s="20"/>
       <c r="K980" s="20"/>
     </row>
-    <row r="981" spans="2:11" ht="13">
+    <row r="981" spans="2:11" ht="12.5">
       <c r="B981" s="20"/>
       <c r="C981" s="20"/>
       <c r="D981" s="20"/>
@@ -10550,7 +10691,7 @@
       <c r="I981" s="20"/>
       <c r="K981" s="20"/>
     </row>
-    <row r="982" spans="2:11" ht="13">
+    <row r="982" spans="2:11" ht="12.5">
       <c r="B982" s="20"/>
       <c r="C982" s="20"/>
       <c r="D982" s="20"/>
@@ -10561,7 +10702,7 @@
       <c r="I982" s="20"/>
       <c r="K982" s="20"/>
     </row>
-    <row r="983" spans="2:11" ht="13">
+    <row r="983" spans="2:11" ht="12.5">
       <c r="B983" s="20"/>
       <c r="C983" s="20"/>
       <c r="D983" s="20"/>
@@ -10572,7 +10713,7 @@
       <c r="I983" s="20"/>
       <c r="K983" s="20"/>
     </row>
-    <row r="984" spans="2:11" ht="13">
+    <row r="984" spans="2:11" ht="12.5">
       <c r="B984" s="20"/>
       <c r="C984" s="20"/>
       <c r="D984" s="20"/>
@@ -10583,7 +10724,7 @@
       <c r="I984" s="20"/>
       <c r="K984" s="20"/>
     </row>
-    <row r="985" spans="2:11" ht="13">
+    <row r="985" spans="2:11" ht="12.5">
       <c r="B985" s="20"/>
       <c r="C985" s="20"/>
       <c r="D985" s="20"/>
@@ -10594,7 +10735,7 @@
       <c r="I985" s="20"/>
       <c r="K985" s="20"/>
     </row>
-    <row r="986" spans="2:11" ht="13">
+    <row r="986" spans="2:11" ht="12.5">
       <c r="B986" s="20"/>
       <c r="C986" s="20"/>
       <c r="D986" s="20"/>
@@ -10605,7 +10746,7 @@
       <c r="I986" s="20"/>
       <c r="K986" s="20"/>
     </row>
-    <row r="987" spans="2:11" ht="13">
+    <row r="987" spans="2:11" ht="12.5">
       <c r="B987" s="20"/>
       <c r="C987" s="20"/>
       <c r="D987" s="20"/>
@@ -10616,7 +10757,7 @@
       <c r="I987" s="20"/>
       <c r="K987" s="20"/>
     </row>
-    <row r="988" spans="2:11" ht="13">
+    <row r="988" spans="2:11" ht="12.5">
       <c r="B988" s="20"/>
       <c r="C988" s="20"/>
       <c r="D988" s="20"/>
@@ -10627,7 +10768,7 @@
       <c r="I988" s="20"/>
       <c r="K988" s="20"/>
     </row>
-    <row r="989" spans="2:11" ht="13">
+    <row r="989" spans="2:11" ht="12.5">
       <c r="B989" s="20"/>
       <c r="C989" s="20"/>
       <c r="D989" s="20"/>
@@ -10638,7 +10779,7 @@
       <c r="I989" s="20"/>
       <c r="K989" s="20"/>
     </row>
-    <row r="990" spans="2:11" ht="13">
+    <row r="990" spans="2:11" ht="12.5">
       <c r="B990" s="20"/>
       <c r="C990" s="20"/>
       <c r="D990" s="20"/>
@@ -10649,7 +10790,7 @@
       <c r="I990" s="20"/>
       <c r="K990" s="20"/>
     </row>
-    <row r="991" spans="2:11" ht="13">
+    <row r="991" spans="2:11" ht="12.5">
       <c r="B991" s="20"/>
       <c r="C991" s="20"/>
       <c r="D991" s="20"/>
@@ -10660,7 +10801,7 @@
       <c r="I991" s="20"/>
       <c r="K991" s="20"/>
     </row>
-    <row r="992" spans="2:11" ht="13">
+    <row r="992" spans="2:11" ht="12.5">
       <c r="B992" s="20"/>
       <c r="C992" s="20"/>
       <c r="D992" s="20"/>
@@ -10671,7 +10812,7 @@
       <c r="I992" s="20"/>
       <c r="K992" s="20"/>
     </row>
-    <row r="993" spans="2:11" ht="13">
+    <row r="993" spans="2:11" ht="12.5">
       <c r="B993" s="20"/>
       <c r="C993" s="20"/>
       <c r="D993" s="20"/>
@@ -10682,7 +10823,7 @@
       <c r="I993" s="20"/>
       <c r="K993" s="20"/>
     </row>
-    <row r="994" spans="2:11" ht="13">
+    <row r="994" spans="2:11" ht="12.5">
       <c r="B994" s="20"/>
       <c r="C994" s="20"/>
       <c r="D994" s="20"/>
@@ -10693,7 +10834,7 @@
       <c r="I994" s="20"/>
       <c r="K994" s="20"/>
     </row>
-    <row r="995" spans="2:11" ht="13">
+    <row r="995" spans="2:11" ht="12.5">
       <c r="B995" s="20"/>
       <c r="C995" s="20"/>
       <c r="D995" s="20"/>
@@ -10704,7 +10845,7 @@
       <c r="I995" s="20"/>
       <c r="K995" s="20"/>
     </row>
-    <row r="996" spans="2:11" ht="13">
+    <row r="996" spans="2:11" ht="12.5">
       <c r="B996" s="20"/>
       <c r="C996" s="20"/>
       <c r="D996" s="20"/>
@@ -10715,7 +10856,7 @@
       <c r="I996" s="20"/>
       <c r="K996" s="20"/>
     </row>
-    <row r="997" spans="2:11" ht="13">
+    <row r="997" spans="2:11" ht="12.5">
       <c r="B997" s="20"/>
       <c r="C997" s="20"/>
       <c r="D997" s="20"/>
@@ -10726,7 +10867,7 @@
       <c r="I997" s="20"/>
       <c r="K997" s="20"/>
     </row>
-    <row r="998" spans="2:11" ht="13">
+    <row r="998" spans="2:11" ht="12.5">
       <c r="B998" s="20"/>
       <c r="C998" s="20"/>
       <c r="D998" s="20"/>
@@ -10737,7 +10878,7 @@
       <c r="I998" s="20"/>
       <c r="K998" s="20"/>
     </row>
-    <row r="999" spans="2:11" ht="13">
+    <row r="999" spans="2:11" ht="12.5">
       <c r="B999" s="20"/>
       <c r="C999" s="20"/>
       <c r="D999" s="20"/>
@@ -10748,7 +10889,7 @@
       <c r="I999" s="20"/>
       <c r="K999" s="20"/>
     </row>
-    <row r="1000" spans="2:11" ht="13">
+    <row r="1000" spans="2:11" ht="12.5">
       <c r="B1000" s="20"/>
       <c r="C1000" s="20"/>
       <c r="D1000" s="20"/>
